--- a/proyectos/p-webs-adsense/fabrica/productos/kit-autonomo-2027/kit-autonomo-2027.xlsx
+++ b/proyectos/p-webs-adsense/fabrica/productos/kit-autonomo-2027/kit-autonomo-2027.xlsx
@@ -27,14 +27,14 @@
     <definedName name="IVA_REDUCIDO">'Parámetros'!$C$11</definedName>
     <definedName name="IVA_SUPERREDUCIDO">'Parámetros'!$C$12</definedName>
     <definedName name="PCT_130">'Parámetros'!$C$14</definedName>
-    <definedName name="MIN130_H1">'Parámetros'!$C$15</definedName>
-    <definedName name="MIN130_E1">'Parámetros'!$C$16</definedName>
-    <definedName name="MIN130_H2">'Parámetros'!$C$17</definedName>
-    <definedName name="MIN130_E2">'Parámetros'!$C$18</definedName>
-    <definedName name="MIN130_H3">'Parámetros'!$C$19</definedName>
-    <definedName name="MIN130_E3">'Parámetros'!$C$20</definedName>
-    <definedName name="MIN130_H4">'Parámetros'!$C$21</definedName>
-    <definedName name="MIN130_E4">'Parámetros'!$C$22</definedName>
+    <definedName name="MINOR_H1">'Parámetros'!$C$15</definedName>
+    <definedName name="MINOR_E1">'Parámetros'!$C$16</definedName>
+    <definedName name="MINOR_H2">'Parámetros'!$C$17</definedName>
+    <definedName name="MINOR_E2">'Parámetros'!$C$18</definedName>
+    <definedName name="MINOR_H3">'Parámetros'!$C$19</definedName>
+    <definedName name="MINOR_E3">'Parámetros'!$C$20</definedName>
+    <definedName name="MINOR_H4">'Parámetros'!$C$21</definedName>
+    <definedName name="MINOR_E4">'Parámetros'!$C$22</definedName>
     <definedName name="TIPO_RETA">'Parámetros'!$C$24</definedName>
     <definedName name="TARIFA_PLANA_EUR">'Parámetros'!$C$25</definedName>
     <definedName name="GASTOS_GENERICOS">'Parámetros'!$C$26</definedName>
@@ -79,22 +79,22 @@
     <definedName name="T_RMAX">'Cuota autónomos'!$D$44:$D$58</definedName>
     <definedName name="T_BMIN">'Cuota autónomos'!$E$44:$E$58</definedName>
     <definedName name="T_BMAX">'Cuota autónomos'!$F$44:$F$58</definedName>
-    <definedName name="RES303_1">'Modelo 303'!$D$19</definedName>
-    <definedName name="PAGO303_1">'Modelo 303'!$D$21</definedName>
-    <definedName name="RES303_2">'Modelo 303'!$E$19</definedName>
-    <definedName name="PAGO303_2">'Modelo 303'!$E$21</definedName>
-    <definedName name="RES303_3">'Modelo 303'!$F$19</definedName>
-    <definedName name="PAGO303_3">'Modelo 303'!$F$21</definedName>
-    <definedName name="RES303_4">'Modelo 303'!$G$19</definedName>
-    <definedName name="PAGO303_4">'Modelo 303'!$G$21</definedName>
-    <definedName name="RES130_1">'Modelo 130'!$D$16</definedName>
-    <definedName name="PAGO130_1">'Modelo 130'!$D$17</definedName>
-    <definedName name="RES130_2">'Modelo 130'!$E$16</definedName>
-    <definedName name="PAGO130_2">'Modelo 130'!$E$17</definedName>
-    <definedName name="RES130_3">'Modelo 130'!$F$16</definedName>
-    <definedName name="PAGO130_3">'Modelo 130'!$F$17</definedName>
-    <definedName name="RES130_4">'Modelo 130'!$G$16</definedName>
-    <definedName name="PAGO130_4">'Modelo 130'!$G$17</definedName>
+    <definedName name="RES_303_1">'Modelo 303'!$D$19</definedName>
+    <definedName name="PAGO_303_1">'Modelo 303'!$D$21</definedName>
+    <definedName name="RES_303_2">'Modelo 303'!$E$19</definedName>
+    <definedName name="PAGO_303_2">'Modelo 303'!$E$21</definedName>
+    <definedName name="RES_303_3">'Modelo 303'!$F$19</definedName>
+    <definedName name="PAGO_303_3">'Modelo 303'!$F$21</definedName>
+    <definedName name="RES_303_4">'Modelo 303'!$G$19</definedName>
+    <definedName name="PAGO_303_4">'Modelo 303'!$G$21</definedName>
+    <definedName name="RES_130_1">'Modelo 130'!$D$16</definedName>
+    <definedName name="PAGO_130_1">'Modelo 130'!$D$17</definedName>
+    <definedName name="RES_130_2">'Modelo 130'!$E$16</definedName>
+    <definedName name="PAGO_130_2">'Modelo 130'!$E$17</definedName>
+    <definedName name="RES_130_3">'Modelo 130'!$F$16</definedName>
+    <definedName name="PAGO_130_3">'Modelo 130'!$F$17</definedName>
+    <definedName name="RES_130_4">'Modelo 130'!$G$16</definedName>
+    <definedName name="PAGO_130_4">'Modelo 130'!$G$17</definedName>
     <definedName name="RENTA_TOTAL">'Renta 2027'!$C$25</definedName>
     <definedName name="RENTA_RESULTADO">'Renta 2027'!$C$31</definedName>
     <definedName name="RENTA_BASE">'Renta 2027'!$C$14</definedName>
@@ -117,7 +117,7 @@
     <numFmt numFmtId="169" formatCode="0.00&quot; %&quot;"/>
     <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -226,12 +226,18 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F3B57"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B1F17"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="000B1F17"/>
+      <color rgb="001F3B57"/>
       <sz val="10"/>
     </font>
     <font>
@@ -393,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -473,22 +479,21 @@
     <xf numFmtId="170" fontId="13" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="20" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -501,8 +506,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="20" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -522,10 +531,10 @@
     <xf numFmtId="169" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1596,7 +1605,7 @@
           <t>Bonificación (Ceuta y Melilla)</t>
         </is>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="44">
         <f>INDEX(CCAA_BONIF,MATCH(CCAA,CCAA_COD,0))</f>
         <v/>
       </c>
@@ -1618,7 +1627,7 @@
           <t>Tipo medio sobre la base</t>
         </is>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="45">
         <f>IF(C14&gt;0,C25/C14*100,0)</f>
         <v/>
       </c>
@@ -1650,7 +1659,7 @@
         </is>
       </c>
       <c r="C30" s="22">
-        <f>PAGO130_1+PAGO130_2+PAGO130_3+PAGO130_4</f>
+        <f>PAGO_130_1+PAGO_130_2+PAGO_130_3+PAGO_130_4</f>
         <v/>
       </c>
     </row>
@@ -1805,7 +1814,7 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="38" t="n">
+      <c r="B7" s="39" t="n">
         <v>46407</v>
       </c>
       <c r="C7" s="35" t="inlineStr">
@@ -1813,17 +1822,17 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="46" t="inlineStr">
         <is>
           <t>111, 115, 123, 216</t>
         </is>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" s="47" t="inlineStr">
         <is>
           <t>111: Retenciones de trabajadores y profesionales que pagas tú; 115: Retenciones del alquiler de tu local u oficina · 4T 2026 retenciones</t>
         </is>
       </c>
-      <c r="F7" s="30" t="n"/>
+      <c r="F7" s="38" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="B8" s="26" t="n">
@@ -1834,20 +1843,20 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E8" s="48" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de enero</t>
         </is>
       </c>
-      <c r="F8" s="30" t="n"/>
+      <c r="F8" s="38" t="n"/>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="B9" s="38" t="n">
+      <c r="B9" s="39" t="n">
         <v>46419</v>
       </c>
       <c r="C9" s="35" t="inlineStr">
@@ -1855,17 +1864,17 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D9" s="45" t="inlineStr">
+      <c r="D9" s="46" t="inlineStr">
         <is>
           <t>130, 131, 303, 349, 390, 180, 190, 193</t>
         </is>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E9" s="47" t="inlineStr">
         <is>
           <t>130: Pago fraccionado del IRPF (estimación directa); 303: Autoliquidación de IVA; 349: Operaciones intracomunitarias; 390: Resumen anual de IVA · Plazo del 30/31 de enero trasladado al lunes 1 de febrero por caer en fin de semana</t>
         </is>
       </c>
-      <c r="F9" s="30" t="n"/>
+      <c r="F9" s="38" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="B10" s="26" t="n">
@@ -1876,20 +1885,20 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D10" s="47" t="inlineStr">
+      <c r="D10" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E10" s="48" t="inlineStr">
+      <c r="E10" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de febrero</t>
         </is>
       </c>
-      <c r="F10" s="30" t="n"/>
+      <c r="F10" s="38" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="38" t="n">
+      <c r="B11" s="39" t="n">
         <v>46447</v>
       </c>
       <c r="C11" s="35" t="inlineStr">
@@ -1897,17 +1906,17 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D11" s="45" t="inlineStr">
+      <c r="D11" s="46" t="inlineStr">
         <is>
           <t>347</t>
         </is>
       </c>
-      <c r="E11" s="46" t="inlineStr">
+      <c r="E11" s="47" t="inlineStr">
         <is>
           <t>347: Operaciones con terceros de más de 3.005,06 € · Plazo de febrero; 28-2-2027 es domingo</t>
         </is>
       </c>
-      <c r="F11" s="30" t="n"/>
+      <c r="F11" s="38" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="B12" s="26" t="n">
@@ -1918,20 +1927,20 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D12" s="47" t="inlineStr">
+      <c r="D12" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E12" s="48" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de marzo</t>
         </is>
       </c>
-      <c r="F12" s="30" t="n"/>
+      <c r="F12" s="38" t="n"/>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="B13" s="38" t="n">
+      <c r="B13" s="39" t="n">
         <v>46497</v>
       </c>
       <c r="C13" s="35" t="inlineStr">
@@ -1939,17 +1948,17 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D13" s="45" t="inlineStr">
+      <c r="D13" s="46" t="inlineStr">
         <is>
           <t>111, 115, 123, 130, 131, 303, 349, 202</t>
         </is>
       </c>
-      <c r="E13" s="46" t="inlineStr">
+      <c r="E13" s="47" t="inlineStr">
         <is>
           <t>111: Retenciones de trabajadores y profesionales que pagas tú; 115: Retenciones del alquiler de tu local u oficina; 130: Pago fraccionado del IRPF (estimación directa); 303: Autoliquidación de IVA; 349: Operaciones intracomunitarias · 1T 2027 y primer pago fraccionado IS</t>
         </is>
       </c>
-      <c r="F13" s="30" t="n"/>
+      <c r="F13" s="38" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="B14" s="26" t="n">
@@ -1960,17 +1969,17 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E14" s="48" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de abril</t>
         </is>
       </c>
-      <c r="F14" s="30" t="n"/>
+      <c r="F14" s="38" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="B15" s="26" t="n">
@@ -1981,20 +1990,20 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D15" s="47" t="inlineStr">
+      <c r="D15" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E15" s="48" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de mayo</t>
         </is>
       </c>
-      <c r="F15" s="30" t="n"/>
+      <c r="F15" s="38" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="38" t="n">
+      <c r="B16" s="39" t="n">
         <v>46568</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
@@ -2002,17 +2011,17 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D16" s="45" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>100, 714</t>
         </is>
       </c>
-      <c r="E16" s="46" t="inlineStr">
+      <c r="E16" s="47" t="inlineStr">
         <is>
           <t>100: Declaración de la renta (IRPF) · Fin previsto campaña Renta y Patrimonio 2026 (pendiente de orden)</t>
         </is>
       </c>
-      <c r="F16" s="30" t="n"/>
+      <c r="F16" s="38" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="B17" s="26" t="n">
@@ -2023,20 +2032,20 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D17" s="47" t="inlineStr">
+      <c r="D17" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E17" s="48" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de junio</t>
         </is>
       </c>
-      <c r="F17" s="30" t="n"/>
+      <c r="F17" s="38" t="n"/>
     </row>
     <row r="18" ht="45" customHeight="1">
-      <c r="B18" s="38" t="n">
+      <c r="B18" s="39" t="n">
         <v>46588</v>
       </c>
       <c r="C18" s="35" t="inlineStr">
@@ -2044,20 +2053,20 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D18" s="45" t="inlineStr">
+      <c r="D18" s="46" t="inlineStr">
         <is>
           <t>111, 115, 123, 130, 131, 303, 349</t>
         </is>
       </c>
-      <c r="E18" s="46" t="inlineStr">
+      <c r="E18" s="47" t="inlineStr">
         <is>
           <t>111: Retenciones de trabajadores y profesionales que pagas tú; 115: Retenciones del alquiler de tu local u oficina; 130: Pago fraccionado del IRPF (estimación directa); 303: Autoliquidación de IVA; 349: Operaciones intracomunitarias · 2T 2027</t>
         </is>
       </c>
-      <c r="F18" s="30" t="n"/>
+      <c r="F18" s="38" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="38" t="n">
+      <c r="B19" s="39" t="n">
         <v>46594</v>
       </c>
       <c r="C19" s="35" t="inlineStr">
@@ -2065,17 +2074,17 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D19" s="45" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E19" s="46" t="inlineStr">
+      <c r="E19" s="47" t="inlineStr">
         <is>
           <t>200: Impuesto sobre Sociedades (solo sociedades) · IS ejercicio 2026 (25 de julio es domingo)</t>
         </is>
       </c>
-      <c r="F19" s="30" t="n"/>
+      <c r="F19" s="38" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="B20" s="26" t="n">
@@ -2086,17 +2095,17 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D20" s="47" t="inlineStr">
+      <c r="D20" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E20" s="48" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de julio</t>
         </is>
       </c>
-      <c r="F20" s="30" t="n"/>
+      <c r="F20" s="38" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="B21" s="26" t="n">
@@ -2107,17 +2116,17 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D21" s="47" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E21" s="48" t="inlineStr">
+      <c r="E21" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de agosto</t>
         </is>
       </c>
-      <c r="F21" s="30" t="n"/>
+      <c r="F21" s="38" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="B22" s="26" t="n">
@@ -2128,20 +2137,20 @@
           <t>jueves</t>
         </is>
       </c>
-      <c r="D22" s="47" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E22" s="48" t="inlineStr">
+      <c r="E22" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de septiembre</t>
         </is>
       </c>
-      <c r="F22" s="30" t="n"/>
+      <c r="F22" s="38" t="n"/>
     </row>
     <row r="23" ht="60" customHeight="1">
-      <c r="B23" s="38" t="n">
+      <c r="B23" s="39" t="n">
         <v>46680</v>
       </c>
       <c r="C23" s="35" t="inlineStr">
@@ -2149,17 +2158,17 @@
           <t>miércoles</t>
         </is>
       </c>
-      <c r="D23" s="45" t="inlineStr">
+      <c r="D23" s="46" t="inlineStr">
         <is>
           <t>111, 115, 123, 130, 131, 303, 349, 202</t>
         </is>
       </c>
-      <c r="E23" s="46" t="inlineStr">
+      <c r="E23" s="47" t="inlineStr">
         <is>
           <t>111: Retenciones de trabajadores y profesionales que pagas tú; 115: Retenciones del alquiler de tu local u oficina; 130: Pago fraccionado del IRPF (estimación directa); 303: Autoliquidación de IVA; 349: Operaciones intracomunitarias · 3T 2027 y segundo pago fraccionado IS</t>
         </is>
       </c>
-      <c r="F23" s="30" t="n"/>
+      <c r="F23" s="38" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="B24" s="26" t="n">
@@ -2170,17 +2179,17 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D24" s="47" t="inlineStr">
+      <c r="D24" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E24" s="48" t="inlineStr">
+      <c r="E24" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de octubre</t>
         </is>
       </c>
-      <c r="F24" s="30" t="n"/>
+      <c r="F24" s="38" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="B25" s="26" t="n">
@@ -2191,20 +2200,20 @@
           <t>martes</t>
         </is>
       </c>
-      <c r="D25" s="47" t="inlineStr">
+      <c r="D25" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E25" s="48" t="inlineStr">
+      <c r="E25" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de noviembre</t>
         </is>
       </c>
-      <c r="F25" s="30" t="n"/>
+      <c r="F25" s="38" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="38" t="n">
+      <c r="B26" s="39" t="n">
         <v>46741</v>
       </c>
       <c r="C26" s="35" t="inlineStr">
@@ -2212,17 +2221,17 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D26" s="45" t="inlineStr">
+      <c r="D26" s="46" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E26" s="46" t="inlineStr">
+      <c r="E26" s="47" t="inlineStr">
         <is>
           <t>202: Pago fraccionado de Sociedades (solo sociedades) · Tercer pago fraccionado IS</t>
         </is>
       </c>
-      <c r="F26" s="30" t="n"/>
+      <c r="F26" s="38" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="26" t="n">
@@ -2233,20 +2242,20 @@
           <t>viernes</t>
         </is>
       </c>
-      <c r="D27" s="47" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>RETA</t>
         </is>
       </c>
-      <c r="E27" s="48" t="inlineStr">
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t>Cargo de la cuota de autónomos de diciembre</t>
         </is>
       </c>
-      <c r="F27" s="30" t="n"/>
+      <c r="F27" s="38" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="B28" s="38" t="n">
+      <c r="B28" s="39" t="n">
         <v>46783</v>
       </c>
       <c r="C28" s="35" t="inlineStr">
@@ -2254,17 +2263,17 @@
           <t>lunes</t>
         </is>
       </c>
-      <c r="D28" s="45" t="inlineStr">
+      <c r="D28" s="46" t="inlineStr">
         <is>
           <t>303, 130, 390</t>
         </is>
       </c>
-      <c r="E28" s="46" t="inlineStr">
+      <c r="E28" s="47" t="inlineStr">
         <is>
           <t>4T de 2027: IVA, pago fraccionado y resumen anual de IVA</t>
         </is>
       </c>
-      <c r="F28" s="30" t="n"/>
+      <c r="F28" s="38" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="B30" s="12" t="inlineStr">
@@ -2389,15 +2398,15 @@
       <c r="D7" s="18" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="B8" s="49" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>Año del kit</t>
         </is>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="C8" s="51" t="n">
         <v>2027</v>
       </c>
-      <c r="D8" s="51" t="inlineStr">
+      <c r="D8" s="52" t="inlineStr">
         <is>
           <t>Ejercicio fiscal de los libros</t>
         </is>
@@ -2413,45 +2422,45 @@
       <c r="D9" s="18" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>Tipo general de IVA (%)</t>
         </is>
       </c>
-      <c r="C10" s="50" t="n">
+      <c r="C10" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="D10" s="52" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>Ley 37/1992 del IVA (BOE)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="B11" s="49" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>Tipo reducido de IVA (%)</t>
         </is>
       </c>
-      <c r="C11" s="50" t="n">
+      <c r="C11" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="52" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>Ley 37/1992 del IVA (BOE)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="B12" s="49" t="inlineStr">
+      <c r="B12" s="50" t="inlineStr">
         <is>
           <t>Tipo superreducido de IVA (%)</t>
         </is>
       </c>
-      <c r="C12" s="50" t="n">
+      <c r="C12" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="52" t="inlineStr">
+      <c r="D12" s="53" t="inlineStr">
         <is>
           <t>Ley 37/1992 del IVA (BOE)</t>
         </is>
@@ -2467,135 +2476,135 @@
       <c r="D13" s="18" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="B14" s="49" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>Pago fraccionado sobre el rendimiento neto acumulado (%)</t>
         </is>
       </c>
-      <c r="C14" s="50" t="n">
+      <c r="C14" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="D14" s="52" t="inlineStr">
+      <c r="D14" s="53" t="inlineStr">
         <is>
           <t>Ley 35/2006 del IRPF, art. 99; RIRPF art. 110</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="B15" s="49" t="inlineStr">
+      <c r="B15" s="50" t="inlineStr">
         <is>
           <t>Minoración: rendimiento del año anterior hasta (€), tramo 1</t>
         </is>
       </c>
-      <c r="C15" s="53" t="n">
+      <c r="C15" s="54" t="n">
         <v>9000</v>
       </c>
-      <c r="D15" s="52" t="inlineStr">
+      <c r="D15" s="53" t="inlineStr">
         <is>
           <t>Reglamento del IRPF (RD 439/2007), art. 110.3.c</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="B16" s="49" t="inlineStr">
+      <c r="B16" s="50" t="inlineStr">
         <is>
           <t>Minoración por trimestre (€), tramo 1</t>
         </is>
       </c>
-      <c r="C16" s="53" t="n">
+      <c r="C16" s="54" t="n">
         <v>100</v>
       </c>
-      <c r="D16" s="52" t="inlineStr">
+      <c r="D16" s="53" t="inlineStr">
         <is>
           <t>Reglamento del IRPF (RD 439/2007), art. 110.3.c</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="49" t="inlineStr">
+      <c r="B17" s="50" t="inlineStr">
         <is>
           <t>Minoración: rendimiento del año anterior hasta (€), tramo 2</t>
         </is>
       </c>
-      <c r="C17" s="53" t="n">
+      <c r="C17" s="54" t="n">
         <v>10000</v>
       </c>
-      <c r="D17" s="52" t="inlineStr">
+      <c r="D17" s="53" t="inlineStr">
         <is>
           <t>Reglamento del IRPF (RD 439/2007), art. 110.3.c</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="B18" s="49" t="inlineStr">
+      <c r="B18" s="50" t="inlineStr">
         <is>
           <t>Minoración por trimestre (€), tramo 2</t>
         </is>
       </c>
-      <c r="C18" s="53" t="n">
+      <c r="C18" s="54" t="n">
         <v>75</v>
       </c>
-      <c r="D18" s="52" t="inlineStr">
+      <c r="D18" s="53" t="inlineStr">
         <is>
           <t>Reglamento del IRPF (RD 439/2007), art. 110.3.c</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="49" t="inlineStr">
+      <c r="B19" s="50" t="inlineStr">
         <is>
           <t>Minoración: rendimiento del año anterior hasta (€), tramo 3</t>
         </is>
       </c>
-      <c r="C19" s="53" t="n">
+      <c r="C19" s="54" t="n">
         <v>11000</v>
       </c>
-      <c r="D19" s="52" t="inlineStr">
+      <c r="D19" s="53" t="inlineStr">
         <is>
           <t>Reglamento del IRPF (RD 439/2007), art. 110.3.c</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="B20" s="49" t="inlineStr">
+      <c r="B20" s="50" t="inlineStr">
         <is>
           <t>Minoración por trimestre (€), tramo 3</t>
         </is>
       </c>
-      <c r="C20" s="53" t="n">
+      <c r="C20" s="54" t="n">
         <v>50</v>
       </c>
-      <c r="D20" s="52" t="inlineStr">
+      <c r="D20" s="53" t="inlineStr">
         <is>
           <t>Reglamento del IRPF (RD 439/2007), art. 110.3.c</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="B21" s="49" t="inlineStr">
+      <c r="B21" s="50" t="inlineStr">
         <is>
           <t>Minoración: rendimiento del año anterior hasta (€), tramo 4</t>
         </is>
       </c>
-      <c r="C21" s="53" t="n">
+      <c r="C21" s="54" t="n">
         <v>12000</v>
       </c>
-      <c r="D21" s="52" t="inlineStr">
+      <c r="D21" s="53" t="inlineStr">
         <is>
           <t>Reglamento del IRPF (RD 439/2007), art. 110.3.c</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="49" t="inlineStr">
+      <c r="B22" s="50" t="inlineStr">
         <is>
           <t>Minoración por trimestre (€), tramo 4</t>
         </is>
       </c>
-      <c r="C22" s="53" t="n">
+      <c r="C22" s="54" t="n">
         <v>25</v>
       </c>
-      <c r="D22" s="52" t="inlineStr">
+      <c r="D22" s="53" t="inlineStr">
         <is>
           <t>Reglamento del IRPF (RD 439/2007), art. 110.3.c</t>
         </is>
@@ -2611,22 +2620,22 @@
       <c r="D23" s="18" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="B24" s="49" t="inlineStr">
+      <c r="B24" s="50" t="inlineStr">
         <is>
           <t>Tipo de cotización total (%)</t>
         </is>
       </c>
-      <c r="C24" s="50" t="n">
+      <c r="C24" s="51" t="n">
         <v>31.6</v>
       </c>
-      <c r="D24" s="52" t="inlineStr">
+      <c r="D24" s="53" t="inlineStr">
         <is>
           <t>Orden PJC/297/2026, de 30 de marzo, normas de cotización 2026 (BOE 31/03/2026, BOE-A-2026-7296); RDL 3/2026 art. 3 · provisional: tabla de 2026</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="B25" s="49" t="inlineStr">
+      <c r="B25" s="50" t="inlineStr">
         <is>
           <t>Tarifa plana (€ al mes)</t>
         </is>
@@ -2634,22 +2643,22 @@
       <c r="C25" s="22" t="n">
         <v>80</v>
       </c>
-      <c r="D25" s="52" t="inlineStr">
+      <c r="D25" s="53" t="inlineStr">
         <is>
           <t>Orden PJC/297/2026, de 30 de marzo, normas de cotización 2026 (BOE 31/03/2026, BOE-A-2026-7296); RDL 3/2026 art. 3</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="B26" s="49" t="inlineStr">
+      <c r="B26" s="50" t="inlineStr">
         <is>
           <t>Deducción por gastos genéricos para el tramo (%)</t>
         </is>
       </c>
-      <c r="C26" s="50" t="n">
+      <c r="C26" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="52" t="inlineStr">
+      <c r="D26" s="53" t="inlineStr">
         <is>
           <t>Orden PJC/297/2026, de 30 de marzo, normas de cotización 2026 (BOE 31/03/2026, BOE-A-2026-7296); RDL 3/2026 art. 3</t>
         </is>
@@ -2665,30 +2674,30 @@
       <c r="D27" s="18" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="49" t="inlineStr">
+      <c r="B28" s="50" t="inlineStr">
         <is>
           <t>Gastos de difícil justificación (%)</t>
         </is>
       </c>
-      <c r="C28" s="50" t="n">
+      <c r="C28" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="52" t="inlineStr">
+      <c r="D28" s="53" t="inlineStr">
         <is>
           <t>AEAT - Estimación directa simplificada</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="B29" s="49" t="inlineStr">
+      <c r="B29" s="50" t="inlineStr">
         <is>
           <t>Gastos de difícil justificación, máximo (€)</t>
         </is>
       </c>
-      <c r="C29" s="53" t="n">
+      <c r="C29" s="54" t="n">
         <v>2000</v>
       </c>
-      <c r="D29" s="52" t="inlineStr">
+      <c r="D29" s="53" t="inlineStr">
         <is>
           <t>AEAT - Estimación directa simplificada</t>
         </is>
@@ -2704,120 +2713,120 @@
       <c r="D30" s="18" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="49" t="inlineStr">
+      <c r="B31" s="50" t="inlineStr">
         <is>
           <t>Mínimo del contribuyente (€)</t>
         </is>
       </c>
-      <c r="C31" s="53" t="n">
+      <c r="C31" s="54" t="n">
         <v>5550</v>
       </c>
-      <c r="D31" s="52" t="inlineStr">
+      <c r="D31" s="53" t="inlineStr">
         <is>
           <t>AEAT Manual Renta 2025 - cuadro de mínimos estatal y autonómicos</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="B32" s="49" t="inlineStr">
+      <c r="B32" s="50" t="inlineStr">
         <is>
           <t>Incremento por edad: 65 años o más (€)</t>
         </is>
       </c>
-      <c r="C32" s="53" t="n">
+      <c r="C32" s="54" t="n">
         <v>1150</v>
       </c>
-      <c r="D32" s="52" t="inlineStr">
+      <c r="D32" s="53" t="inlineStr">
         <is>
           <t>AEAT Manual Renta 2025 - cuadro de mínimos estatal y autonómicos</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
-      <c r="B33" s="49" t="inlineStr">
+      <c r="B33" s="50" t="inlineStr">
         <is>
           <t>Incremento adicional: 75 años o más (€)</t>
         </is>
       </c>
-      <c r="C33" s="53" t="n">
+      <c r="C33" s="54" t="n">
         <v>1400</v>
       </c>
-      <c r="D33" s="52" t="inlineStr">
+      <c r="D33" s="53" t="inlineStr">
         <is>
           <t>AEAT Manual Renta 2025 - cuadro de mínimos estatal y autonómicos</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="B34" s="49" t="inlineStr">
+      <c r="B34" s="50" t="inlineStr">
         <is>
           <t>Mínimo por descendiente: 1.º (€)</t>
         </is>
       </c>
-      <c r="C34" s="53" t="n">
+      <c r="C34" s="54" t="n">
         <v>2400</v>
       </c>
-      <c r="D34" s="52" t="inlineStr">
+      <c r="D34" s="53" t="inlineStr">
         <is>
           <t>AEAT Manual Renta 2025 - cuadro de mínimos estatal y autonómicos</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
-      <c r="B35" s="49" t="inlineStr">
+      <c r="B35" s="50" t="inlineStr">
         <is>
           <t>Mínimo por descendiente: 2.º (€)</t>
         </is>
       </c>
-      <c r="C35" s="53" t="n">
+      <c r="C35" s="54" t="n">
         <v>2700</v>
       </c>
-      <c r="D35" s="52" t="inlineStr">
+      <c r="D35" s="53" t="inlineStr">
         <is>
           <t>AEAT Manual Renta 2025 - cuadro de mínimos estatal y autonómicos</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="B36" s="49" t="inlineStr">
+      <c r="B36" s="50" t="inlineStr">
         <is>
           <t>Mínimo por descendiente: 3.º (€)</t>
         </is>
       </c>
-      <c r="C36" s="53" t="n">
+      <c r="C36" s="54" t="n">
         <v>4000</v>
       </c>
-      <c r="D36" s="52" t="inlineStr">
+      <c r="D36" s="53" t="inlineStr">
         <is>
           <t>AEAT Manual Renta 2025 - cuadro de mínimos estatal y autonómicos</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="49" t="inlineStr">
+      <c r="B37" s="50" t="inlineStr">
         <is>
           <t>Mínimo por descendiente: 4.º y siguientes (€)</t>
         </is>
       </c>
-      <c r="C37" s="53" t="n">
+      <c r="C37" s="54" t="n">
         <v>4500</v>
       </c>
-      <c r="D37" s="52" t="inlineStr">
+      <c r="D37" s="53" t="inlineStr">
         <is>
           <t>AEAT Manual Renta 2025 - cuadro de mínimos estatal y autonómicos</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="B38" s="49" t="inlineStr">
+      <c r="B38" s="50" t="inlineStr">
         <is>
           <t>Incremento por descendiente menor de 3 años (€)</t>
         </is>
       </c>
-      <c r="C38" s="53" t="n">
+      <c r="C38" s="54" t="n">
         <v>2800</v>
       </c>
-      <c r="D38" s="52" t="inlineStr">
+      <c r="D38" s="53" t="inlineStr">
         <is>
           <t>AEAT Manual Renta 2025 - cuadro de mínimos estatal y autonómicos</t>
         </is>
@@ -3011,13 +3020,13 @@
           <t>Estatal</t>
         </is>
       </c>
-      <c r="D7" s="54" t="n">
+      <c r="D7" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="56">
         <f>E7</f>
         <v/>
       </c>
@@ -3031,10 +3040,10 @@
           <t>Andalucía</t>
         </is>
       </c>
-      <c r="J7" s="54" t="n">
+      <c r="J7" s="55" t="n">
         <v>5790</v>
       </c>
-      <c r="K7" s="55" t="n">
+      <c r="K7" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3049,13 +3058,13 @@
           <t>Estatal</t>
         </is>
       </c>
-      <c r="D8" s="54" t="n">
+      <c r="D8" s="55" t="n">
         <v>12450</v>
       </c>
-      <c r="E8" s="55" t="n">
+      <c r="E8" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="56">
         <f>E8-E7</f>
         <v/>
       </c>
@@ -3069,10 +3078,10 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="J8" s="54" t="n">
+      <c r="J8" s="55" t="n">
         <v>5550</v>
       </c>
-      <c r="K8" s="55" t="n">
+      <c r="K8" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3087,13 +3096,13 @@
           <t>Estatal</t>
         </is>
       </c>
-      <c r="D9" s="54" t="n">
+      <c r="D9" s="55" t="n">
         <v>20200</v>
       </c>
-      <c r="E9" s="55" t="n">
+      <c r="E9" s="56" t="n">
         <v>15</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="56">
         <f>E9-E8</f>
         <v/>
       </c>
@@ -3107,10 +3116,10 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="J9" s="54" t="n">
+      <c r="J9" s="55" t="n">
         <v>6105</v>
       </c>
-      <c r="K9" s="55" t="n">
+      <c r="K9" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3125,13 +3134,13 @@
           <t>Estatal</t>
         </is>
       </c>
-      <c r="D10" s="54" t="n">
+      <c r="D10" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E10" s="55" t="n">
+      <c r="E10" s="56" t="n">
         <v>18.5</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="56">
         <f>E10-E9</f>
         <v/>
       </c>
@@ -3145,10 +3154,10 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="J10" s="54" t="n">
+      <c r="J10" s="55" t="n">
         <v>6105</v>
       </c>
-      <c r="K10" s="55" t="n">
+      <c r="K10" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3163,13 +3172,13 @@
           <t>Estatal</t>
         </is>
       </c>
-      <c r="D11" s="54" t="n">
+      <c r="D11" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E11" s="55" t="n">
+      <c r="E11" s="56" t="n">
         <v>22.5</v>
       </c>
-      <c r="F11" s="55">
+      <c r="F11" s="56">
         <f>E11-E10</f>
         <v/>
       </c>
@@ -3183,10 +3192,10 @@
           <t>Canarias</t>
         </is>
       </c>
-      <c r="J11" s="54" t="n">
+      <c r="J11" s="55" t="n">
         <v>5606</v>
       </c>
-      <c r="K11" s="55" t="n">
+      <c r="K11" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3201,13 +3210,13 @@
           <t>Estatal</t>
         </is>
       </c>
-      <c r="D12" s="54" t="n">
+      <c r="D12" s="55" t="n">
         <v>300000</v>
       </c>
-      <c r="E12" s="55" t="n">
+      <c r="E12" s="56" t="n">
         <v>24.5</v>
       </c>
-      <c r="F12" s="55">
+      <c r="F12" s="56">
         <f>E12-E11</f>
         <v/>
       </c>
@@ -3221,10 +3230,10 @@
           <t>Cantabria</t>
         </is>
       </c>
-      <c r="J12" s="54" t="n">
+      <c r="J12" s="55" t="n">
         <v>5550</v>
       </c>
-      <c r="K12" s="55" t="n">
+      <c r="K12" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3239,13 +3248,13 @@
           <t>Andalucía</t>
         </is>
       </c>
-      <c r="D13" s="54" t="n">
+      <c r="D13" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="55" t="n">
+      <c r="E13" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="F13" s="55">
+      <c r="F13" s="56">
         <f>E13</f>
         <v/>
       </c>
@@ -3259,10 +3268,10 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="J13" s="54" t="n">
+      <c r="J13" s="55" t="n">
         <v>5550</v>
       </c>
-      <c r="K13" s="55" t="n">
+      <c r="K13" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3277,13 +3286,13 @@
           <t>Andalucía</t>
         </is>
       </c>
-      <c r="D14" s="54" t="n">
+      <c r="D14" s="55" t="n">
         <v>13000</v>
       </c>
-      <c r="E14" s="55" t="n">
+      <c r="E14" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="56">
         <f>E14-E13</f>
         <v/>
       </c>
@@ -3297,10 +3306,10 @@
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="J14" s="54" t="n">
+      <c r="J14" s="55" t="n">
         <v>5550</v>
       </c>
-      <c r="K14" s="55" t="n">
+      <c r="K14" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3315,13 +3324,13 @@
           <t>Andalucía</t>
         </is>
       </c>
-      <c r="D15" s="54" t="n">
+      <c r="D15" s="55" t="n">
         <v>21100</v>
       </c>
-      <c r="E15" s="55" t="n">
+      <c r="E15" s="56" t="n">
         <v>15</v>
       </c>
-      <c r="F15" s="55">
+      <c r="F15" s="56">
         <f>E15-E14</f>
         <v/>
       </c>
@@ -3335,10 +3344,10 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="J15" s="54" t="n">
+      <c r="J15" s="55" t="n">
         <v>5550</v>
       </c>
-      <c r="K15" s="55" t="n">
+      <c r="K15" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3353,13 +3362,13 @@
           <t>Andalucía</t>
         </is>
       </c>
-      <c r="D16" s="54" t="n">
+      <c r="D16" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E16" s="55" t="n">
+      <c r="E16" s="56" t="n">
         <v>18.5</v>
       </c>
-      <c r="F16" s="55">
+      <c r="F16" s="56">
         <f>E16-E15</f>
         <v/>
       </c>
@@ -3373,10 +3382,10 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="J16" s="54" t="n">
+      <c r="J16" s="55" t="n">
         <v>5550</v>
       </c>
-      <c r="K16" s="55" t="n">
+      <c r="K16" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3391,13 +3400,13 @@
           <t>Andalucía</t>
         </is>
       </c>
-      <c r="D17" s="54" t="n">
+      <c r="D17" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E17" s="55" t="n">
+      <c r="E17" s="56" t="n">
         <v>22.5</v>
       </c>
-      <c r="F17" s="55">
+      <c r="F17" s="56">
         <f>E17-E16</f>
         <v/>
       </c>
@@ -3411,10 +3420,10 @@
           <t>Galicia</t>
         </is>
       </c>
-      <c r="J17" s="54" t="n">
+      <c r="J17" s="55" t="n">
         <v>5789</v>
       </c>
-      <c r="K17" s="55" t="n">
+      <c r="K17" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3429,13 +3438,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D18" s="54" t="n">
+      <c r="D18" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E18" s="55" t="n">
+      <c r="E18" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="F18" s="55">
+      <c r="F18" s="56">
         <f>E18</f>
         <v/>
       </c>
@@ -3449,10 +3458,10 @@
           <t>Comunidad de Madrid</t>
         </is>
       </c>
-      <c r="J18" s="54" t="n">
+      <c r="J18" s="55" t="n">
         <v>5956.65</v>
       </c>
-      <c r="K18" s="55" t="n">
+      <c r="K18" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3467,13 +3476,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D19" s="54" t="n">
+      <c r="D19" s="55" t="n">
         <v>13072.5</v>
       </c>
-      <c r="E19" s="55" t="n">
+      <c r="E19" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="F19" s="55">
+      <c r="F19" s="56">
         <f>E19-E18</f>
         <v/>
       </c>
@@ -3487,10 +3496,10 @@
           <t>Región de Murcia</t>
         </is>
       </c>
-      <c r="J19" s="54" t="n">
+      <c r="J19" s="55" t="n">
         <v>5550</v>
       </c>
-      <c r="K19" s="55" t="n">
+      <c r="K19" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3505,13 +3514,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D20" s="54" t="n">
+      <c r="D20" s="55" t="n">
         <v>21210</v>
       </c>
-      <c r="E20" s="55" t="n">
+      <c r="E20" s="56" t="n">
         <v>15</v>
       </c>
-      <c r="F20" s="55">
+      <c r="F20" s="56">
         <f>E20-E19</f>
         <v/>
       </c>
@@ -3525,10 +3534,10 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="J20" s="54" t="n">
+      <c r="J20" s="55" t="n">
         <v>5550</v>
       </c>
-      <c r="K20" s="55" t="n">
+      <c r="K20" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3543,13 +3552,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D21" s="54" t="n">
+      <c r="D21" s="55" t="n">
         <v>36960</v>
       </c>
-      <c r="E21" s="55" t="n">
+      <c r="E21" s="56" t="n">
         <v>18.5</v>
       </c>
-      <c r="F21" s="55">
+      <c r="F21" s="56">
         <f>E21-E20</f>
         <v/>
       </c>
@@ -3563,10 +3572,10 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="J21" s="54" t="n">
+      <c r="J21" s="55" t="n">
         <v>6105</v>
       </c>
-      <c r="K21" s="55" t="n">
+      <c r="K21" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3581,13 +3590,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D22" s="54" t="n">
+      <c r="D22" s="55" t="n">
         <v>52500</v>
       </c>
-      <c r="E22" s="55" t="n">
+      <c r="E22" s="56" t="n">
         <v>20.5</v>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="56">
         <f>E22-E21</f>
         <v/>
       </c>
@@ -3601,11 +3610,11 @@
           <t>Ceuta y Melilla</t>
         </is>
       </c>
-      <c r="J22" s="54">
+      <c r="J22" s="55">
         <f>MIN_PERSONAL</f>
         <v/>
       </c>
-      <c r="K22" s="55" t="n">
+      <c r="K22" s="56" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3620,13 +3629,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D23" s="54" t="n">
+      <c r="D23" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E23" s="55" t="n">
+      <c r="E23" s="56" t="n">
         <v>23</v>
       </c>
-      <c r="F23" s="55">
+      <c r="F23" s="56">
         <f>E23-E22</f>
         <v/>
       </c>
@@ -3642,13 +3651,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D24" s="54" t="n">
+      <c r="D24" s="55" t="n">
         <v>80000</v>
       </c>
-      <c r="E24" s="55" t="n">
+      <c r="E24" s="56" t="n">
         <v>24</v>
       </c>
-      <c r="F24" s="55">
+      <c r="F24" s="56">
         <f>E24-E23</f>
         <v/>
       </c>
@@ -3669,13 +3678,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D25" s="54" t="n">
+      <c r="D25" s="55" t="n">
         <v>90000</v>
       </c>
-      <c r="E25" s="55" t="n">
+      <c r="E25" s="56" t="n">
         <v>25</v>
       </c>
-      <c r="F25" s="55">
+      <c r="F25" s="56">
         <f>E25-E24</f>
         <v/>
       </c>
@@ -3691,13 +3700,13 @@
           <t>Aragón</t>
         </is>
       </c>
-      <c r="D26" s="54" t="n">
+      <c r="D26" s="55" t="n">
         <v>130000</v>
       </c>
-      <c r="E26" s="55" t="n">
+      <c r="E26" s="56" t="n">
         <v>25.5</v>
       </c>
-      <c r="F26" s="55">
+      <c r="F26" s="56">
         <f>E26-E25</f>
         <v/>
       </c>
@@ -3713,13 +3722,13 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="D27" s="54" t="n">
+      <c r="D27" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="55" t="n">
+      <c r="E27" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F27" s="55">
+      <c r="F27" s="56">
         <f>E27</f>
         <v/>
       </c>
@@ -3735,13 +3744,13 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="D28" s="54" t="n">
+      <c r="D28" s="55" t="n">
         <v>12450</v>
       </c>
-      <c r="E28" s="55" t="n">
+      <c r="E28" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="F28" s="55">
+      <c r="F28" s="56">
         <f>E28-E27</f>
         <v/>
       </c>
@@ -3757,13 +3766,13 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="D29" s="54" t="n">
+      <c r="D29" s="55" t="n">
         <v>17707.2</v>
       </c>
-      <c r="E29" s="55" t="n">
+      <c r="E29" s="56" t="n">
         <v>14</v>
       </c>
-      <c r="F29" s="55">
+      <c r="F29" s="56">
         <f>E29-E28</f>
         <v/>
       </c>
@@ -3779,13 +3788,13 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="D30" s="54" t="n">
+      <c r="D30" s="55" t="n">
         <v>33007.2</v>
       </c>
-      <c r="E30" s="55" t="n">
+      <c r="E30" s="56" t="n">
         <v>19.2</v>
       </c>
-      <c r="F30" s="55">
+      <c r="F30" s="56">
         <f>E30-E29</f>
         <v/>
       </c>
@@ -3801,13 +3810,13 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="D31" s="54" t="n">
+      <c r="D31" s="55" t="n">
         <v>53407.2</v>
       </c>
-      <c r="E31" s="55" t="n">
+      <c r="E31" s="56" t="n">
         <v>21.5</v>
       </c>
-      <c r="F31" s="55">
+      <c r="F31" s="56">
         <f>E31-E30</f>
         <v/>
       </c>
@@ -3823,13 +3832,13 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="D32" s="54" t="n">
+      <c r="D32" s="55" t="n">
         <v>70000</v>
       </c>
-      <c r="E32" s="55" t="n">
+      <c r="E32" s="56" t="n">
         <v>22.5</v>
       </c>
-      <c r="F32" s="55">
+      <c r="F32" s="56">
         <f>E32-E31</f>
         <v/>
       </c>
@@ -3845,13 +3854,13 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="D33" s="54" t="n">
+      <c r="D33" s="55" t="n">
         <v>90000</v>
       </c>
-      <c r="E33" s="55" t="n">
+      <c r="E33" s="56" t="n">
         <v>25</v>
       </c>
-      <c r="F33" s="55">
+      <c r="F33" s="56">
         <f>E33-E32</f>
         <v/>
       </c>
@@ -3867,13 +3876,13 @@
           <t>Principado de Asturias</t>
         </is>
       </c>
-      <c r="D34" s="54" t="n">
+      <c r="D34" s="55" t="n">
         <v>175000</v>
       </c>
-      <c r="E34" s="55" t="n">
+      <c r="E34" s="56" t="n">
         <v>26</v>
       </c>
-      <c r="F34" s="55">
+      <c r="F34" s="56">
         <f>E34-E33</f>
         <v/>
       </c>
@@ -3889,13 +3898,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D35" s="54" t="n">
+      <c r="D35" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="55" t="n">
+      <c r="E35" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F35" s="55">
+      <c r="F35" s="56">
         <f>E35</f>
         <v/>
       </c>
@@ -3911,13 +3920,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D36" s="54" t="n">
+      <c r="D36" s="55" t="n">
         <v>10000</v>
       </c>
-      <c r="E36" s="55" t="n">
+      <c r="E36" s="56" t="n">
         <v>11.25</v>
       </c>
-      <c r="F36" s="55">
+      <c r="F36" s="56">
         <f>E36-E35</f>
         <v/>
       </c>
@@ -3933,13 +3942,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D37" s="54" t="n">
+      <c r="D37" s="55" t="n">
         <v>18000</v>
       </c>
-      <c r="E37" s="55" t="n">
+      <c r="E37" s="56" t="n">
         <v>14.25</v>
       </c>
-      <c r="F37" s="55">
+      <c r="F37" s="56">
         <f>E37-E36</f>
         <v/>
       </c>
@@ -3955,13 +3964,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D38" s="54" t="n">
+      <c r="D38" s="55" t="n">
         <v>30000</v>
       </c>
-      <c r="E38" s="55" t="n">
+      <c r="E38" s="56" t="n">
         <v>17.5</v>
       </c>
-      <c r="F38" s="55">
+      <c r="F38" s="56">
         <f>E38-E37</f>
         <v/>
       </c>
@@ -3977,13 +3986,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D39" s="54" t="n">
+      <c r="D39" s="55" t="n">
         <v>48000</v>
       </c>
-      <c r="E39" s="55" t="n">
+      <c r="E39" s="56" t="n">
         <v>19</v>
       </c>
-      <c r="F39" s="55">
+      <c r="F39" s="56">
         <f>E39-E38</f>
         <v/>
       </c>
@@ -3999,13 +4008,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D40" s="54" t="n">
+      <c r="D40" s="55" t="n">
         <v>70000</v>
       </c>
-      <c r="E40" s="55" t="n">
+      <c r="E40" s="56" t="n">
         <v>21.75</v>
       </c>
-      <c r="F40" s="55">
+      <c r="F40" s="56">
         <f>E40-E39</f>
         <v/>
       </c>
@@ -4021,13 +4030,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D41" s="54" t="n">
+      <c r="D41" s="55" t="n">
         <v>90000</v>
       </c>
-      <c r="E41" s="55" t="n">
+      <c r="E41" s="56" t="n">
         <v>22.75</v>
       </c>
-      <c r="F41" s="55">
+      <c r="F41" s="56">
         <f>E41-E40</f>
         <v/>
       </c>
@@ -4043,13 +4052,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D42" s="54" t="n">
+      <c r="D42" s="55" t="n">
         <v>120000</v>
       </c>
-      <c r="E42" s="55" t="n">
+      <c r="E42" s="56" t="n">
         <v>23.75</v>
       </c>
-      <c r="F42" s="55">
+      <c r="F42" s="56">
         <f>E42-E41</f>
         <v/>
       </c>
@@ -4065,13 +4074,13 @@
           <t>Illes Balears</t>
         </is>
       </c>
-      <c r="D43" s="54" t="n">
+      <c r="D43" s="55" t="n">
         <v>175000</v>
       </c>
-      <c r="E43" s="55" t="n">
+      <c r="E43" s="56" t="n">
         <v>24.75</v>
       </c>
-      <c r="F43" s="55">
+      <c r="F43" s="56">
         <f>E43-E42</f>
         <v/>
       </c>
@@ -4087,13 +4096,13 @@
           <t>Canarias</t>
         </is>
       </c>
-      <c r="D44" s="54" t="n">
+      <c r="D44" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="55" t="n">
+      <c r="E44" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F44" s="55">
+      <c r="F44" s="56">
         <f>E44</f>
         <v/>
       </c>
@@ -4109,13 +4118,13 @@
           <t>Canarias</t>
         </is>
       </c>
-      <c r="D45" s="54" t="n">
+      <c r="D45" s="55" t="n">
         <v>13748</v>
       </c>
-      <c r="E45" s="55" t="n">
+      <c r="E45" s="56" t="n">
         <v>11.5</v>
       </c>
-      <c r="F45" s="55">
+      <c r="F45" s="56">
         <f>E45-E44</f>
         <v/>
       </c>
@@ -4131,13 +4140,13 @@
           <t>Canarias</t>
         </is>
       </c>
-      <c r="D46" s="54" t="n">
+      <c r="D46" s="55" t="n">
         <v>19422</v>
       </c>
-      <c r="E46" s="55" t="n">
+      <c r="E46" s="56" t="n">
         <v>14</v>
       </c>
-      <c r="F46" s="55">
+      <c r="F46" s="56">
         <f>E46-E45</f>
         <v/>
       </c>
@@ -4153,13 +4162,13 @@
           <t>Canarias</t>
         </is>
       </c>
-      <c r="D47" s="54" t="n">
+      <c r="D47" s="55" t="n">
         <v>35924</v>
       </c>
-      <c r="E47" s="55" t="n">
+      <c r="E47" s="56" t="n">
         <v>18.5</v>
       </c>
-      <c r="F47" s="55">
+      <c r="F47" s="56">
         <f>E47-E46</f>
         <v/>
       </c>
@@ -4175,13 +4184,13 @@
           <t>Canarias</t>
         </is>
       </c>
-      <c r="D48" s="54" t="n">
+      <c r="D48" s="55" t="n">
         <v>57566</v>
       </c>
-      <c r="E48" s="55" t="n">
+      <c r="E48" s="56" t="n">
         <v>23.5</v>
       </c>
-      <c r="F48" s="55">
+      <c r="F48" s="56">
         <f>E48-E47</f>
         <v/>
       </c>
@@ -4197,13 +4206,13 @@
           <t>Canarias</t>
         </is>
       </c>
-      <c r="D49" s="54" t="n">
+      <c r="D49" s="55" t="n">
         <v>93268</v>
       </c>
-      <c r="E49" s="55" t="n">
+      <c r="E49" s="56" t="n">
         <v>25</v>
       </c>
-      <c r="F49" s="55">
+      <c r="F49" s="56">
         <f>E49-E48</f>
         <v/>
       </c>
@@ -4219,13 +4228,13 @@
           <t>Canarias</t>
         </is>
       </c>
-      <c r="D50" s="54" t="n">
+      <c r="D50" s="55" t="n">
         <v>123745</v>
       </c>
-      <c r="E50" s="55" t="n">
+      <c r="E50" s="56" t="n">
         <v>26</v>
       </c>
-      <c r="F50" s="55">
+      <c r="F50" s="56">
         <f>E50-E49</f>
         <v/>
       </c>
@@ -4241,13 +4250,13 @@
           <t>Cantabria</t>
         </is>
       </c>
-      <c r="D51" s="54" t="n">
+      <c r="D51" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="55" t="n">
+      <c r="E51" s="56" t="n">
         <v>8.5</v>
       </c>
-      <c r="F51" s="55">
+      <c r="F51" s="56">
         <f>E51</f>
         <v/>
       </c>
@@ -4263,13 +4272,13 @@
           <t>Cantabria</t>
         </is>
       </c>
-      <c r="D52" s="54" t="n">
+      <c r="D52" s="55" t="n">
         <v>13000</v>
       </c>
-      <c r="E52" s="55" t="n">
+      <c r="E52" s="56" t="n">
         <v>11</v>
       </c>
-      <c r="F52" s="55">
+      <c r="F52" s="56">
         <f>E52-E51</f>
         <v/>
       </c>
@@ -4285,13 +4294,13 @@
           <t>Cantabria</t>
         </is>
       </c>
-      <c r="D53" s="54" t="n">
+      <c r="D53" s="55" t="n">
         <v>21000</v>
       </c>
-      <c r="E53" s="55" t="n">
+      <c r="E53" s="56" t="n">
         <v>14.5</v>
       </c>
-      <c r="F53" s="55">
+      <c r="F53" s="56">
         <f>E53-E52</f>
         <v/>
       </c>
@@ -4307,13 +4316,13 @@
           <t>Cantabria</t>
         </is>
       </c>
-      <c r="D54" s="54" t="n">
+      <c r="D54" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E54" s="55" t="n">
+      <c r="E54" s="56" t="n">
         <v>18</v>
       </c>
-      <c r="F54" s="55">
+      <c r="F54" s="56">
         <f>E54-E53</f>
         <v/>
       </c>
@@ -4329,13 +4338,13 @@
           <t>Cantabria</t>
         </is>
       </c>
-      <c r="D55" s="54" t="n">
+      <c r="D55" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E55" s="55" t="n">
+      <c r="E55" s="56" t="n">
         <v>22.5</v>
       </c>
-      <c r="F55" s="55">
+      <c r="F55" s="56">
         <f>E55-E54</f>
         <v/>
       </c>
@@ -4351,13 +4360,13 @@
           <t>Cantabria</t>
         </is>
       </c>
-      <c r="D56" s="54" t="n">
+      <c r="D56" s="55" t="n">
         <v>90000</v>
       </c>
-      <c r="E56" s="55" t="n">
+      <c r="E56" s="56" t="n">
         <v>24.5</v>
       </c>
-      <c r="F56" s="55">
+      <c r="F56" s="56">
         <f>E56-E55</f>
         <v/>
       </c>
@@ -4373,13 +4382,13 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="D57" s="54" t="n">
+      <c r="D57" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="55" t="n">
+      <c r="E57" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F57" s="55">
+      <c r="F57" s="56">
         <f>E57</f>
         <v/>
       </c>
@@ -4395,13 +4404,13 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="D58" s="54" t="n">
+      <c r="D58" s="55" t="n">
         <v>12450</v>
       </c>
-      <c r="E58" s="55" t="n">
+      <c r="E58" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="F58" s="55">
+      <c r="F58" s="56">
         <f>E58-E57</f>
         <v/>
       </c>
@@ -4417,13 +4426,13 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="D59" s="54" t="n">
+      <c r="D59" s="55" t="n">
         <v>20200</v>
       </c>
-      <c r="E59" s="55" t="n">
+      <c r="E59" s="56" t="n">
         <v>14</v>
       </c>
-      <c r="F59" s="55">
+      <c r="F59" s="56">
         <f>E59-E58</f>
         <v/>
       </c>
@@ -4439,13 +4448,13 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="D60" s="54" t="n">
+      <c r="D60" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E60" s="55" t="n">
+      <c r="E60" s="56" t="n">
         <v>18.5</v>
       </c>
-      <c r="F60" s="55">
+      <c r="F60" s="56">
         <f>E60-E59</f>
         <v/>
       </c>
@@ -4461,13 +4470,13 @@
           <t>Castilla y León</t>
         </is>
       </c>
-      <c r="D61" s="54" t="n">
+      <c r="D61" s="55" t="n">
         <v>53407.2</v>
       </c>
-      <c r="E61" s="55" t="n">
+      <c r="E61" s="56" t="n">
         <v>21.5</v>
       </c>
-      <c r="F61" s="55">
+      <c r="F61" s="56">
         <f>E61-E60</f>
         <v/>
       </c>
@@ -4483,13 +4492,13 @@
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="D62" s="54" t="n">
+      <c r="D62" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="55" t="n">
+      <c r="E62" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="F62" s="55">
+      <c r="F62" s="56">
         <f>E62</f>
         <v/>
       </c>
@@ -4505,13 +4514,13 @@
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="D63" s="54" t="n">
+      <c r="D63" s="55" t="n">
         <v>12450</v>
       </c>
-      <c r="E63" s="55" t="n">
+      <c r="E63" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="F63" s="55">
+      <c r="F63" s="56">
         <f>E63-E62</f>
         <v/>
       </c>
@@ -4527,13 +4536,13 @@
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="D64" s="54" t="n">
+      <c r="D64" s="55" t="n">
         <v>20200</v>
       </c>
-      <c r="E64" s="55" t="n">
+      <c r="E64" s="56" t="n">
         <v>15</v>
       </c>
-      <c r="F64" s="55">
+      <c r="F64" s="56">
         <f>E64-E63</f>
         <v/>
       </c>
@@ -4549,13 +4558,13 @@
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="D65" s="54" t="n">
+      <c r="D65" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E65" s="55" t="n">
+      <c r="E65" s="56" t="n">
         <v>18.5</v>
       </c>
-      <c r="F65" s="55">
+      <c r="F65" s="56">
         <f>E65-E64</f>
         <v/>
       </c>
@@ -4571,13 +4580,13 @@
           <t>Castilla-La Mancha</t>
         </is>
       </c>
-      <c r="D66" s="54" t="n">
+      <c r="D66" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E66" s="55" t="n">
+      <c r="E66" s="56" t="n">
         <v>22.5</v>
       </c>
-      <c r="F66" s="55">
+      <c r="F66" s="56">
         <f>E66-E65</f>
         <v/>
       </c>
@@ -4593,13 +4602,13 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="D67" s="54" t="n">
+      <c r="D67" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="55" t="n">
+      <c r="E67" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="F67" s="55">
+      <c r="F67" s="56">
         <f>E67</f>
         <v/>
       </c>
@@ -4615,13 +4624,13 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="D68" s="54" t="n">
+      <c r="D68" s="55" t="n">
         <v>12500</v>
       </c>
-      <c r="E68" s="55" t="n">
+      <c r="E68" s="56" t="n">
         <v>12.5</v>
       </c>
-      <c r="F68" s="55">
+      <c r="F68" s="56">
         <f>E68-E67</f>
         <v/>
       </c>
@@ -4637,13 +4646,13 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="D69" s="54" t="n">
+      <c r="D69" s="55" t="n">
         <v>22000</v>
       </c>
-      <c r="E69" s="55" t="n">
+      <c r="E69" s="56" t="n">
         <v>16</v>
       </c>
-      <c r="F69" s="55">
+      <c r="F69" s="56">
         <f>E69-E68</f>
         <v/>
       </c>
@@ -4659,13 +4668,13 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="D70" s="54" t="n">
+      <c r="D70" s="55" t="n">
         <v>33000</v>
       </c>
-      <c r="E70" s="55" t="n">
+      <c r="E70" s="56" t="n">
         <v>19</v>
       </c>
-      <c r="F70" s="55">
+      <c r="F70" s="56">
         <f>E70-E69</f>
         <v/>
       </c>
@@ -4681,13 +4690,13 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="D71" s="54" t="n">
+      <c r="D71" s="55" t="n">
         <v>53000</v>
       </c>
-      <c r="E71" s="55" t="n">
+      <c r="E71" s="56" t="n">
         <v>21.5</v>
       </c>
-      <c r="F71" s="55">
+      <c r="F71" s="56">
         <f>E71-E70</f>
         <v/>
       </c>
@@ -4703,13 +4712,13 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="D72" s="54" t="n">
+      <c r="D72" s="55" t="n">
         <v>90000</v>
       </c>
-      <c r="E72" s="55" t="n">
+      <c r="E72" s="56" t="n">
         <v>23.5</v>
       </c>
-      <c r="F72" s="55">
+      <c r="F72" s="56">
         <f>E72-E71</f>
         <v/>
       </c>
@@ -4725,13 +4734,13 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="D73" s="54" t="n">
+      <c r="D73" s="55" t="n">
         <v>120000</v>
       </c>
-      <c r="E73" s="55" t="n">
+      <c r="E73" s="56" t="n">
         <v>24.5</v>
       </c>
-      <c r="F73" s="55">
+      <c r="F73" s="56">
         <f>E73-E72</f>
         <v/>
       </c>
@@ -4747,13 +4756,13 @@
           <t>Cataluña</t>
         </is>
       </c>
-      <c r="D74" s="54" t="n">
+      <c r="D74" s="55" t="n">
         <v>175000</v>
       </c>
-      <c r="E74" s="55" t="n">
+      <c r="E74" s="56" t="n">
         <v>25.5</v>
       </c>
-      <c r="F74" s="55">
+      <c r="F74" s="56">
         <f>E74-E73</f>
         <v/>
       </c>
@@ -4769,13 +4778,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D75" s="54" t="n">
+      <c r="D75" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="55" t="n">
+      <c r="E75" s="56" t="n">
         <v>7.75</v>
       </c>
-      <c r="F75" s="55">
+      <c r="F75" s="56">
         <f>E75</f>
         <v/>
       </c>
@@ -4791,13 +4800,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D76" s="54" t="n">
+      <c r="D76" s="55" t="n">
         <v>12450</v>
       </c>
-      <c r="E76" s="55" t="n">
+      <c r="E76" s="56" t="n">
         <v>9.75</v>
       </c>
-      <c r="F76" s="55">
+      <c r="F76" s="56">
         <f>E76-E75</f>
         <v/>
       </c>
@@ -4813,13 +4822,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D77" s="54" t="n">
+      <c r="D77" s="55" t="n">
         <v>20200</v>
       </c>
-      <c r="E77" s="55" t="n">
+      <c r="E77" s="56" t="n">
         <v>16</v>
       </c>
-      <c r="F77" s="55">
+      <c r="F77" s="56">
         <f>E77-E76</f>
         <v/>
       </c>
@@ -4835,13 +4844,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D78" s="54" t="n">
+      <c r="D78" s="55" t="n">
         <v>24200</v>
       </c>
-      <c r="E78" s="55" t="n">
+      <c r="E78" s="56" t="n">
         <v>17.5</v>
       </c>
-      <c r="F78" s="55">
+      <c r="F78" s="56">
         <f>E78-E77</f>
         <v/>
       </c>
@@ -4857,13 +4866,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D79" s="54" t="n">
+      <c r="D79" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E79" s="55" t="n">
+      <c r="E79" s="56" t="n">
         <v>21</v>
       </c>
-      <c r="F79" s="55">
+      <c r="F79" s="56">
         <f>E79-E78</f>
         <v/>
       </c>
@@ -4879,13 +4888,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D80" s="54" t="n">
+      <c r="D80" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E80" s="55" t="n">
+      <c r="E80" s="56" t="n">
         <v>23.5</v>
       </c>
-      <c r="F80" s="55">
+      <c r="F80" s="56">
         <f>E80-E79</f>
         <v/>
       </c>
@@ -4901,13 +4910,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D81" s="54" t="n">
+      <c r="D81" s="55" t="n">
         <v>80200</v>
       </c>
-      <c r="E81" s="55" t="n">
+      <c r="E81" s="56" t="n">
         <v>24</v>
       </c>
-      <c r="F81" s="55">
+      <c r="F81" s="56">
         <f>E81-E80</f>
         <v/>
       </c>
@@ -4923,13 +4932,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D82" s="54" t="n">
+      <c r="D82" s="55" t="n">
         <v>99200</v>
       </c>
-      <c r="E82" s="55" t="n">
+      <c r="E82" s="56" t="n">
         <v>24.5</v>
       </c>
-      <c r="F82" s="55">
+      <c r="F82" s="56">
         <f>E82-E81</f>
         <v/>
       </c>
@@ -4945,13 +4954,13 @@
           <t>Extremadura</t>
         </is>
       </c>
-      <c r="D83" s="54" t="n">
+      <c r="D83" s="55" t="n">
         <v>120200</v>
       </c>
-      <c r="E83" s="55" t="n">
+      <c r="E83" s="56" t="n">
         <v>25</v>
       </c>
-      <c r="F83" s="55">
+      <c r="F83" s="56">
         <f>E83-E82</f>
         <v/>
       </c>
@@ -4967,13 +4976,13 @@
           <t>Galicia</t>
         </is>
       </c>
-      <c r="D84" s="54" t="n">
+      <c r="D84" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="55" t="n">
+      <c r="E84" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="F84" s="55">
+      <c r="F84" s="56">
         <f>E84</f>
         <v/>
       </c>
@@ -4989,13 +4998,13 @@
           <t>Galicia</t>
         </is>
       </c>
-      <c r="D85" s="54" t="n">
+      <c r="D85" s="55" t="n">
         <v>12985.35</v>
       </c>
-      <c r="E85" s="55" t="n">
+      <c r="E85" s="56" t="n">
         <v>11.65</v>
       </c>
-      <c r="F85" s="55">
+      <c r="F85" s="56">
         <f>E85-E84</f>
         <v/>
       </c>
@@ -5011,13 +5020,13 @@
           <t>Galicia</t>
         </is>
       </c>
-      <c r="D86" s="54" t="n">
+      <c r="D86" s="55" t="n">
         <v>21068.6</v>
       </c>
-      <c r="E86" s="55" t="n">
+      <c r="E86" s="56" t="n">
         <v>14.9</v>
       </c>
-      <c r="F86" s="55">
+      <c r="F86" s="56">
         <f>E86-E85</f>
         <v/>
       </c>
@@ -5033,13 +5042,13 @@
           <t>Galicia</t>
         </is>
       </c>
-      <c r="D87" s="54" t="n">
+      <c r="D87" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E87" s="55" t="n">
+      <c r="E87" s="56" t="n">
         <v>18.4</v>
       </c>
-      <c r="F87" s="55">
+      <c r="F87" s="56">
         <f>E87-E86</f>
         <v/>
       </c>
@@ -5055,13 +5064,13 @@
           <t>Galicia</t>
         </is>
       </c>
-      <c r="D88" s="54" t="n">
+      <c r="D88" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E88" s="55" t="n">
+      <c r="E88" s="56" t="n">
         <v>22.5</v>
       </c>
-      <c r="F88" s="55">
+      <c r="F88" s="56">
         <f>E88-E87</f>
         <v/>
       </c>
@@ -5077,13 +5086,13 @@
           <t>Comunidad de Madrid</t>
         </is>
       </c>
-      <c r="D89" s="54" t="n">
+      <c r="D89" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="55" t="n">
+      <c r="E89" s="56" t="n">
         <v>8.5</v>
       </c>
-      <c r="F89" s="55">
+      <c r="F89" s="56">
         <f>E89</f>
         <v/>
       </c>
@@ -5099,13 +5108,13 @@
           <t>Comunidad de Madrid</t>
         </is>
       </c>
-      <c r="D90" s="54" t="n">
+      <c r="D90" s="55" t="n">
         <v>13362.22</v>
       </c>
-      <c r="E90" s="55" t="n">
+      <c r="E90" s="56" t="n">
         <v>10.7</v>
       </c>
-      <c r="F90" s="55">
+      <c r="F90" s="56">
         <f>E90-E89</f>
         <v/>
       </c>
@@ -5121,13 +5130,13 @@
           <t>Comunidad de Madrid</t>
         </is>
       </c>
-      <c r="D91" s="54" t="n">
+      <c r="D91" s="55" t="n">
         <v>19004.63</v>
       </c>
-      <c r="E91" s="55" t="n">
+      <c r="E91" s="56" t="n">
         <v>12.8</v>
       </c>
-      <c r="F91" s="55">
+      <c r="F91" s="56">
         <f>E91-E90</f>
         <v/>
       </c>
@@ -5143,13 +5152,13 @@
           <t>Comunidad de Madrid</t>
         </is>
       </c>
-      <c r="D92" s="54" t="n">
+      <c r="D92" s="55" t="n">
         <v>35425.68</v>
       </c>
-      <c r="E92" s="55" t="n">
+      <c r="E92" s="56" t="n">
         <v>17.4</v>
       </c>
-      <c r="F92" s="55">
+      <c r="F92" s="56">
         <f>E92-E91</f>
         <v/>
       </c>
@@ -5165,13 +5174,13 @@
           <t>Comunidad de Madrid</t>
         </is>
       </c>
-      <c r="D93" s="54" t="n">
+      <c r="D93" s="55" t="n">
         <v>57320.4</v>
       </c>
-      <c r="E93" s="55" t="n">
+      <c r="E93" s="56" t="n">
         <v>20.5</v>
       </c>
-      <c r="F93" s="55">
+      <c r="F93" s="56">
         <f>E93-E92</f>
         <v/>
       </c>
@@ -5187,13 +5196,13 @@
           <t>Región de Murcia</t>
         </is>
       </c>
-      <c r="D94" s="54" t="n">
+      <c r="D94" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E94" s="55" t="n">
+      <c r="E94" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="F94" s="55">
+      <c r="F94" s="56">
         <f>E94</f>
         <v/>
       </c>
@@ -5209,13 +5218,13 @@
           <t>Región de Murcia</t>
         </is>
       </c>
-      <c r="D95" s="54" t="n">
+      <c r="D95" s="55" t="n">
         <v>12450</v>
       </c>
-      <c r="E95" s="55" t="n">
+      <c r="E95" s="56" t="n">
         <v>11.2</v>
       </c>
-      <c r="F95" s="55">
+      <c r="F95" s="56">
         <f>E95-E94</f>
         <v/>
       </c>
@@ -5231,13 +5240,13 @@
           <t>Región de Murcia</t>
         </is>
       </c>
-      <c r="D96" s="54" t="n">
+      <c r="D96" s="55" t="n">
         <v>20200</v>
       </c>
-      <c r="E96" s="55" t="n">
+      <c r="E96" s="56" t="n">
         <v>13.3</v>
       </c>
-      <c r="F96" s="55">
+      <c r="F96" s="56">
         <f>E96-E95</f>
         <v/>
       </c>
@@ -5253,13 +5262,13 @@
           <t>Región de Murcia</t>
         </is>
       </c>
-      <c r="D97" s="54" t="n">
+      <c r="D97" s="55" t="n">
         <v>34000</v>
       </c>
-      <c r="E97" s="55" t="n">
+      <c r="E97" s="56" t="n">
         <v>17.9</v>
       </c>
-      <c r="F97" s="55">
+      <c r="F97" s="56">
         <f>E97-E96</f>
         <v/>
       </c>
@@ -5275,13 +5284,13 @@
           <t>Región de Murcia</t>
         </is>
       </c>
-      <c r="D98" s="54" t="n">
+      <c r="D98" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E98" s="55" t="n">
+      <c r="E98" s="56" t="n">
         <v>22.5</v>
       </c>
-      <c r="F98" s="55">
+      <c r="F98" s="56">
         <f>E98-E97</f>
         <v/>
       </c>
@@ -5297,13 +5306,13 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="D99" s="54" t="n">
+      <c r="D99" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="55" t="n">
+      <c r="E99" s="56" t="n">
         <v>8</v>
       </c>
-      <c r="F99" s="55">
+      <c r="F99" s="56">
         <f>E99</f>
         <v/>
       </c>
@@ -5319,13 +5328,13 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="D100" s="54" t="n">
+      <c r="D100" s="55" t="n">
         <v>12450</v>
       </c>
-      <c r="E100" s="55" t="n">
+      <c r="E100" s="56" t="n">
         <v>10.6</v>
       </c>
-      <c r="F100" s="55">
+      <c r="F100" s="56">
         <f>E100-E99</f>
         <v/>
       </c>
@@ -5341,13 +5350,13 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="D101" s="54" t="n">
+      <c r="D101" s="55" t="n">
         <v>20200</v>
       </c>
-      <c r="E101" s="55" t="n">
+      <c r="E101" s="56" t="n">
         <v>13.6</v>
       </c>
-      <c r="F101" s="55">
+      <c r="F101" s="56">
         <f>E101-E100</f>
         <v/>
       </c>
@@ -5363,13 +5372,13 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="D102" s="54" t="n">
+      <c r="D102" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E102" s="55" t="n">
+      <c r="E102" s="56" t="n">
         <v>17.8</v>
       </c>
-      <c r="F102" s="55">
+      <c r="F102" s="56">
         <f>E102-E101</f>
         <v/>
       </c>
@@ -5385,13 +5394,13 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="D103" s="54" t="n">
+      <c r="D103" s="55" t="n">
         <v>40000</v>
       </c>
-      <c r="E103" s="55" t="n">
+      <c r="E103" s="56" t="n">
         <v>18.3</v>
       </c>
-      <c r="F103" s="55">
+      <c r="F103" s="56">
         <f>E103-E102</f>
         <v/>
       </c>
@@ -5407,13 +5416,13 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="D104" s="54" t="n">
+      <c r="D104" s="55" t="n">
         <v>50000</v>
       </c>
-      <c r="E104" s="55" t="n">
+      <c r="E104" s="56" t="n">
         <v>19</v>
       </c>
-      <c r="F104" s="55">
+      <c r="F104" s="56">
         <f>E104-E103</f>
         <v/>
       </c>
@@ -5429,13 +5438,13 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="D105" s="54" t="n">
+      <c r="D105" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E105" s="55" t="n">
+      <c r="E105" s="56" t="n">
         <v>24.5</v>
       </c>
-      <c r="F105" s="55">
+      <c r="F105" s="56">
         <f>E105-E104</f>
         <v/>
       </c>
@@ -5451,13 +5460,13 @@
           <t>La Rioja</t>
         </is>
       </c>
-      <c r="D106" s="54" t="n">
+      <c r="D106" s="55" t="n">
         <v>120000</v>
       </c>
-      <c r="E106" s="55" t="n">
+      <c r="E106" s="56" t="n">
         <v>27</v>
       </c>
-      <c r="F106" s="55">
+      <c r="F106" s="56">
         <f>E106-E105</f>
         <v/>
       </c>
@@ -5473,13 +5482,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D107" s="54" t="n">
+      <c r="D107" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="55" t="n">
+      <c r="E107" s="56" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="F107" s="55">
+      <c r="F107" s="56">
         <f>E107</f>
         <v/>
       </c>
@@ -5495,13 +5504,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D108" s="54" t="n">
+      <c r="D108" s="55" t="n">
         <v>12000</v>
       </c>
-      <c r="E108" s="55" t="n">
+      <c r="E108" s="56" t="n">
         <v>11.6</v>
       </c>
-      <c r="F108" s="55">
+      <c r="F108" s="56">
         <f>E108-E107</f>
         <v/>
       </c>
@@ -5517,13 +5526,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D109" s="54" t="n">
+      <c r="D109" s="55" t="n">
         <v>22000</v>
       </c>
-      <c r="E109" s="55" t="n">
+      <c r="E109" s="56" t="n">
         <v>14.5</v>
       </c>
-      <c r="F109" s="55">
+      <c r="F109" s="56">
         <f>E109-E108</f>
         <v/>
       </c>
@@ -5539,13 +5548,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D110" s="54" t="n">
+      <c r="D110" s="55" t="n">
         <v>32000</v>
       </c>
-      <c r="E110" s="55" t="n">
+      <c r="E110" s="56" t="n">
         <v>16.9</v>
       </c>
-      <c r="F110" s="55">
+      <c r="F110" s="56">
         <f>E110-E109</f>
         <v/>
       </c>
@@ -5561,13 +5570,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D111" s="54" t="n">
+      <c r="D111" s="55" t="n">
         <v>42000</v>
       </c>
-      <c r="E111" s="55" t="n">
+      <c r="E111" s="56" t="n">
         <v>19.3</v>
       </c>
-      <c r="F111" s="55">
+      <c r="F111" s="56">
         <f>E111-E110</f>
         <v/>
       </c>
@@ -5583,13 +5592,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D112" s="54" t="n">
+      <c r="D112" s="55" t="n">
         <v>52000</v>
       </c>
-      <c r="E112" s="55" t="n">
+      <c r="E112" s="56" t="n">
         <v>21.8</v>
       </c>
-      <c r="F112" s="55">
+      <c r="F112" s="56">
         <f>E112-E111</f>
         <v/>
       </c>
@@ -5605,13 +5614,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D113" s="54" t="n">
+      <c r="D113" s="55" t="n">
         <v>62000</v>
       </c>
-      <c r="E113" s="55" t="n">
+      <c r="E113" s="56" t="n">
         <v>24.3</v>
       </c>
-      <c r="F113" s="55">
+      <c r="F113" s="56">
         <f>E113-E112</f>
         <v/>
       </c>
@@ -5627,13 +5636,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D114" s="54" t="n">
+      <c r="D114" s="55" t="n">
         <v>72000</v>
       </c>
-      <c r="E114" s="55" t="n">
+      <c r="E114" s="56" t="n">
         <v>26</v>
       </c>
-      <c r="F114" s="55">
+      <c r="F114" s="56">
         <f>E114-E113</f>
         <v/>
       </c>
@@ -5649,13 +5658,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D115" s="54" t="n">
+      <c r="D115" s="55" t="n">
         <v>100000</v>
       </c>
-      <c r="E115" s="55" t="n">
+      <c r="E115" s="56" t="n">
         <v>27.25</v>
       </c>
-      <c r="F115" s="55">
+      <c r="F115" s="56">
         <f>E115-E114</f>
         <v/>
       </c>
@@ -5671,13 +5680,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D116" s="54" t="n">
+      <c r="D116" s="55" t="n">
         <v>150000</v>
       </c>
-      <c r="E116" s="55" t="n">
+      <c r="E116" s="56" t="n">
         <v>28.25</v>
       </c>
-      <c r="F116" s="55">
+      <c r="F116" s="56">
         <f>E116-E115</f>
         <v/>
       </c>
@@ -5693,13 +5702,13 @@
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="D117" s="54" t="n">
+      <c r="D117" s="55" t="n">
         <v>200000</v>
       </c>
-      <c r="E117" s="55" t="n">
+      <c r="E117" s="56" t="n">
         <v>29.25</v>
       </c>
-      <c r="F117" s="55">
+      <c r="F117" s="56">
         <f>E117-E116</f>
         <v/>
       </c>
@@ -5715,13 +5724,13 @@
           <t>Ceuta y Melilla</t>
         </is>
       </c>
-      <c r="D118" s="54" t="n">
+      <c r="D118" s="55" t="n">
         <v>0</v>
       </c>
-      <c r="E118" s="55" t="n">
+      <c r="E118" s="56" t="n">
         <v>9.5</v>
       </c>
-      <c r="F118" s="55">
+      <c r="F118" s="56">
         <f>E118</f>
         <v/>
       </c>
@@ -5737,13 +5746,13 @@
           <t>Ceuta y Melilla</t>
         </is>
       </c>
-      <c r="D119" s="54" t="n">
+      <c r="D119" s="55" t="n">
         <v>12450</v>
       </c>
-      <c r="E119" s="55" t="n">
+      <c r="E119" s="56" t="n">
         <v>12</v>
       </c>
-      <c r="F119" s="55">
+      <c r="F119" s="56">
         <f>E119-E118</f>
         <v/>
       </c>
@@ -5759,13 +5768,13 @@
           <t>Ceuta y Melilla</t>
         </is>
       </c>
-      <c r="D120" s="54" t="n">
+      <c r="D120" s="55" t="n">
         <v>20200</v>
       </c>
-      <c r="E120" s="55" t="n">
+      <c r="E120" s="56" t="n">
         <v>15</v>
       </c>
-      <c r="F120" s="55">
+      <c r="F120" s="56">
         <f>E120-E119</f>
         <v/>
       </c>
@@ -5781,13 +5790,13 @@
           <t>Ceuta y Melilla</t>
         </is>
       </c>
-      <c r="D121" s="54" t="n">
+      <c r="D121" s="55" t="n">
         <v>35200</v>
       </c>
-      <c r="E121" s="55" t="n">
+      <c r="E121" s="56" t="n">
         <v>18.5</v>
       </c>
-      <c r="F121" s="55">
+      <c r="F121" s="56">
         <f>E121-E120</f>
         <v/>
       </c>
@@ -5803,13 +5812,13 @@
           <t>Ceuta y Melilla</t>
         </is>
       </c>
-      <c r="D122" s="54" t="n">
+      <c r="D122" s="55" t="n">
         <v>60000</v>
       </c>
-      <c r="E122" s="55" t="n">
+      <c r="E122" s="56" t="n">
         <v>22.5</v>
       </c>
-      <c r="F122" s="55">
+      <c r="F122" s="56">
         <f>E122-E121</f>
         <v/>
       </c>
@@ -5825,13 +5834,13 @@
           <t>Ceuta y Melilla</t>
         </is>
       </c>
-      <c r="D123" s="54" t="n">
+      <c r="D123" s="55" t="n">
         <v>300000</v>
       </c>
-      <c r="E123" s="55" t="n">
+      <c r="E123" s="56" t="n">
         <v>24.5</v>
       </c>
-      <c r="F123" s="55">
+      <c r="F123" s="56">
         <f>E123-E122</f>
         <v/>
       </c>
@@ -6268,19 +6277,19 @@
         </is>
       </c>
       <c r="C8" s="22">
-        <f>PAGO303_1</f>
+        <f>PAGO_303_1</f>
         <v/>
       </c>
       <c r="D8" s="22">
-        <f>PAGO303_2</f>
+        <f>PAGO_303_2</f>
         <v/>
       </c>
       <c r="E8" s="22">
-        <f>PAGO303_3</f>
+        <f>PAGO_303_3</f>
         <v/>
       </c>
       <c r="F8" s="22">
-        <f>PAGO303_4</f>
+        <f>PAGO_303_4</f>
         <v/>
       </c>
       <c r="G8" s="23">
@@ -6295,19 +6304,19 @@
         </is>
       </c>
       <c r="C9" s="22">
-        <f>PAGO130_1</f>
+        <f>PAGO_130_1</f>
         <v/>
       </c>
       <c r="D9" s="22">
-        <f>PAGO130_2</f>
+        <f>PAGO_130_2</f>
         <v/>
       </c>
       <c r="E9" s="22">
-        <f>PAGO130_3</f>
+        <f>PAGO_130_3</f>
         <v/>
       </c>
       <c r="F9" s="22">
-        <f>PAGO130_4</f>
+        <f>PAGO_130_4</f>
         <v/>
       </c>
       <c r="G9" s="23">
@@ -6399,10 +6408,6 @@
           <t>Importe</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr"/>
-      <c r="E14" s="21" t="inlineStr"/>
-      <c r="F14" s="21" t="inlineStr"/>
-      <c r="G14" s="21" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="9" t="inlineStr">
@@ -6588,15 +6593,10 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Escribe tú en las celdas amarillas. Las demás se calculan solas: no hace falta tocarlas.</t>
+          <t>✎  Las celdas amarillas las rellenas tú; el resto se calcula solo.</t>
         </is>
       </c>
     </row>
@@ -6946,15 +6946,10 @@
       <c r="M4" s="6" t="n"/>
       <c r="N4" s="6" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="20" customHeight="1">
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Escribe tú en las celdas amarillas. Las demás se calculan solas: no hace falta tocarlas.</t>
+          <t>✎  Las celdas amarillas las rellenas tú; el resto se calcula solo.</t>
         </is>
       </c>
       <c r="F5" s="36">
@@ -19204,15 +19199,10 @@
       <c r="O4" s="6" t="n"/>
       <c r="P4" s="6" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="20" customHeight="1">
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Escribe tú en las celdas amarillas. Las demás se calculan solas: no hace falta tocarlas.</t>
+          <t>✎  Las celdas amarillas las rellenas tú; el resto se calcula solo.</t>
         </is>
       </c>
     </row>
@@ -19325,7 +19315,7 @@
         <f>IF(H8="","",ROUND(H8*N(I8)/100,2))</f>
         <v/>
       </c>
-      <c r="K8" s="30" t="n"/>
+      <c r="K8" s="38" t="n"/>
       <c r="L8" s="32" t="n"/>
       <c r="M8" s="22">
         <f>IF(H8="","",IF(K8="No",0,H8*N(I8)/100*IF(L8="",100,L8)/100))</f>
@@ -19357,7 +19347,7 @@
         <f>IF(H9="","",ROUND(H9*N(I9)/100,2))</f>
         <v/>
       </c>
-      <c r="K9" s="30" t="n"/>
+      <c r="K9" s="38" t="n"/>
       <c r="L9" s="32" t="n"/>
       <c r="M9" s="22">
         <f>IF(H9="","",IF(K9="No",0,H9*N(I9)/100*IF(L9="",100,L9)/100))</f>
@@ -19389,7 +19379,7 @@
         <f>IF(H10="","",ROUND(H10*N(I10)/100,2))</f>
         <v/>
       </c>
-      <c r="K10" s="30" t="n"/>
+      <c r="K10" s="38" t="n"/>
       <c r="L10" s="32" t="n"/>
       <c r="M10" s="22">
         <f>IF(H10="","",IF(K10="No",0,H10*N(I10)/100*IF(L10="",100,L10)/100))</f>
@@ -19421,7 +19411,7 @@
         <f>IF(H11="","",ROUND(H11*N(I11)/100,2))</f>
         <v/>
       </c>
-      <c r="K11" s="30" t="n"/>
+      <c r="K11" s="38" t="n"/>
       <c r="L11" s="32" t="n"/>
       <c r="M11" s="22">
         <f>IF(H11="","",IF(K11="No",0,H11*N(I11)/100*IF(L11="",100,L11)/100))</f>
@@ -19453,7 +19443,7 @@
         <f>IF(H12="","",ROUND(H12*N(I12)/100,2))</f>
         <v/>
       </c>
-      <c r="K12" s="30" t="n"/>
+      <c r="K12" s="38" t="n"/>
       <c r="L12" s="32" t="n"/>
       <c r="M12" s="22">
         <f>IF(H12="","",IF(K12="No",0,H12*N(I12)/100*IF(L12="",100,L12)/100))</f>
@@ -19485,7 +19475,7 @@
         <f>IF(H13="","",ROUND(H13*N(I13)/100,2))</f>
         <v/>
       </c>
-      <c r="K13" s="30" t="n"/>
+      <c r="K13" s="38" t="n"/>
       <c r="L13" s="32" t="n"/>
       <c r="M13" s="22">
         <f>IF(H13="","",IF(K13="No",0,H13*N(I13)/100*IF(L13="",100,L13)/100))</f>
@@ -19517,7 +19507,7 @@
         <f>IF(H14="","",ROUND(H14*N(I14)/100,2))</f>
         <v/>
       </c>
-      <c r="K14" s="30" t="n"/>
+      <c r="K14" s="38" t="n"/>
       <c r="L14" s="32" t="n"/>
       <c r="M14" s="22">
         <f>IF(H14="","",IF(K14="No",0,H14*N(I14)/100*IF(L14="",100,L14)/100))</f>
@@ -19549,7 +19539,7 @@
         <f>IF(H15="","",ROUND(H15*N(I15)/100,2))</f>
         <v/>
       </c>
-      <c r="K15" s="30" t="n"/>
+      <c r="K15" s="38" t="n"/>
       <c r="L15" s="32" t="n"/>
       <c r="M15" s="22">
         <f>IF(H15="","",IF(K15="No",0,H15*N(I15)/100*IF(L15="",100,L15)/100))</f>
@@ -19581,7 +19571,7 @@
         <f>IF(H16="","",ROUND(H16*N(I16)/100,2))</f>
         <v/>
       </c>
-      <c r="K16" s="30" t="n"/>
+      <c r="K16" s="38" t="n"/>
       <c r="L16" s="32" t="n"/>
       <c r="M16" s="22">
         <f>IF(H16="","",IF(K16="No",0,H16*N(I16)/100*IF(L16="",100,L16)/100))</f>
@@ -19613,7 +19603,7 @@
         <f>IF(H17="","",ROUND(H17*N(I17)/100,2))</f>
         <v/>
       </c>
-      <c r="K17" s="30" t="n"/>
+      <c r="K17" s="38" t="n"/>
       <c r="L17" s="32" t="n"/>
       <c r="M17" s="22">
         <f>IF(H17="","",IF(K17="No",0,H17*N(I17)/100*IF(L17="",100,L17)/100))</f>
@@ -19645,7 +19635,7 @@
         <f>IF(H18="","",ROUND(H18*N(I18)/100,2))</f>
         <v/>
       </c>
-      <c r="K18" s="30" t="n"/>
+      <c r="K18" s="38" t="n"/>
       <c r="L18" s="32" t="n"/>
       <c r="M18" s="22">
         <f>IF(H18="","",IF(K18="No",0,H18*N(I18)/100*IF(L18="",100,L18)/100))</f>
@@ -19677,7 +19667,7 @@
         <f>IF(H19="","",ROUND(H19*N(I19)/100,2))</f>
         <v/>
       </c>
-      <c r="K19" s="30" t="n"/>
+      <c r="K19" s="38" t="n"/>
       <c r="L19" s="32" t="n"/>
       <c r="M19" s="22">
         <f>IF(H19="","",IF(K19="No",0,H19*N(I19)/100*IF(L19="",100,L19)/100))</f>
@@ -19709,7 +19699,7 @@
         <f>IF(H20="","",ROUND(H20*N(I20)/100,2))</f>
         <v/>
       </c>
-      <c r="K20" s="30" t="n"/>
+      <c r="K20" s="38" t="n"/>
       <c r="L20" s="32" t="n"/>
       <c r="M20" s="22">
         <f>IF(H20="","",IF(K20="No",0,H20*N(I20)/100*IF(L20="",100,L20)/100))</f>
@@ -19741,7 +19731,7 @@
         <f>IF(H21="","",ROUND(H21*N(I21)/100,2))</f>
         <v/>
       </c>
-      <c r="K21" s="30" t="n"/>
+      <c r="K21" s="38" t="n"/>
       <c r="L21" s="32" t="n"/>
       <c r="M21" s="22">
         <f>IF(H21="","",IF(K21="No",0,H21*N(I21)/100*IF(L21="",100,L21)/100))</f>
@@ -19773,7 +19763,7 @@
         <f>IF(H22="","",ROUND(H22*N(I22)/100,2))</f>
         <v/>
       </c>
-      <c r="K22" s="30" t="n"/>
+      <c r="K22" s="38" t="n"/>
       <c r="L22" s="32" t="n"/>
       <c r="M22" s="22">
         <f>IF(H22="","",IF(K22="No",0,H22*N(I22)/100*IF(L22="",100,L22)/100))</f>
@@ -19805,7 +19795,7 @@
         <f>IF(H23="","",ROUND(H23*N(I23)/100,2))</f>
         <v/>
       </c>
-      <c r="K23" s="30" t="n"/>
+      <c r="K23" s="38" t="n"/>
       <c r="L23" s="32" t="n"/>
       <c r="M23" s="22">
         <f>IF(H23="","",IF(K23="No",0,H23*N(I23)/100*IF(L23="",100,L23)/100))</f>
@@ -19837,7 +19827,7 @@
         <f>IF(H24="","",ROUND(H24*N(I24)/100,2))</f>
         <v/>
       </c>
-      <c r="K24" s="30" t="n"/>
+      <c r="K24" s="38" t="n"/>
       <c r="L24" s="32" t="n"/>
       <c r="M24" s="22">
         <f>IF(H24="","",IF(K24="No",0,H24*N(I24)/100*IF(L24="",100,L24)/100))</f>
@@ -19869,7 +19859,7 @@
         <f>IF(H25="","",ROUND(H25*N(I25)/100,2))</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="38" t="n"/>
       <c r="L25" s="32" t="n"/>
       <c r="M25" s="22">
         <f>IF(H25="","",IF(K25="No",0,H25*N(I25)/100*IF(L25="",100,L25)/100))</f>
@@ -19901,7 +19891,7 @@
         <f>IF(H26="","",ROUND(H26*N(I26)/100,2))</f>
         <v/>
       </c>
-      <c r="K26" s="30" t="n"/>
+      <c r="K26" s="38" t="n"/>
       <c r="L26" s="32" t="n"/>
       <c r="M26" s="22">
         <f>IF(H26="","",IF(K26="No",0,H26*N(I26)/100*IF(L26="",100,L26)/100))</f>
@@ -19933,7 +19923,7 @@
         <f>IF(H27="","",ROUND(H27*N(I27)/100,2))</f>
         <v/>
       </c>
-      <c r="K27" s="30" t="n"/>
+      <c r="K27" s="38" t="n"/>
       <c r="L27" s="32" t="n"/>
       <c r="M27" s="22">
         <f>IF(H27="","",IF(K27="No",0,H27*N(I27)/100*IF(L27="",100,L27)/100))</f>
@@ -19965,7 +19955,7 @@
         <f>IF(H28="","",ROUND(H28*N(I28)/100,2))</f>
         <v/>
       </c>
-      <c r="K28" s="30" t="n"/>
+      <c r="K28" s="38" t="n"/>
       <c r="L28" s="32" t="n"/>
       <c r="M28" s="22">
         <f>IF(H28="","",IF(K28="No",0,H28*N(I28)/100*IF(L28="",100,L28)/100))</f>
@@ -19997,7 +19987,7 @@
         <f>IF(H29="","",ROUND(H29*N(I29)/100,2))</f>
         <v/>
       </c>
-      <c r="K29" s="30" t="n"/>
+      <c r="K29" s="38" t="n"/>
       <c r="L29" s="32" t="n"/>
       <c r="M29" s="22">
         <f>IF(H29="","",IF(K29="No",0,H29*N(I29)/100*IF(L29="",100,L29)/100))</f>
@@ -20029,7 +20019,7 @@
         <f>IF(H30="","",ROUND(H30*N(I30)/100,2))</f>
         <v/>
       </c>
-      <c r="K30" s="30" t="n"/>
+      <c r="K30" s="38" t="n"/>
       <c r="L30" s="32" t="n"/>
       <c r="M30" s="22">
         <f>IF(H30="","",IF(K30="No",0,H30*N(I30)/100*IF(L30="",100,L30)/100))</f>
@@ -20061,7 +20051,7 @@
         <f>IF(H31="","",ROUND(H31*N(I31)/100,2))</f>
         <v/>
       </c>
-      <c r="K31" s="30" t="n"/>
+      <c r="K31" s="38" t="n"/>
       <c r="L31" s="32" t="n"/>
       <c r="M31" s="22">
         <f>IF(H31="","",IF(K31="No",0,H31*N(I31)/100*IF(L31="",100,L31)/100))</f>
@@ -20093,7 +20083,7 @@
         <f>IF(H32="","",ROUND(H32*N(I32)/100,2))</f>
         <v/>
       </c>
-      <c r="K32" s="30" t="n"/>
+      <c r="K32" s="38" t="n"/>
       <c r="L32" s="32" t="n"/>
       <c r="M32" s="22">
         <f>IF(H32="","",IF(K32="No",0,H32*N(I32)/100*IF(L32="",100,L32)/100))</f>
@@ -20125,7 +20115,7 @@
         <f>IF(H33="","",ROUND(H33*N(I33)/100,2))</f>
         <v/>
       </c>
-      <c r="K33" s="30" t="n"/>
+      <c r="K33" s="38" t="n"/>
       <c r="L33" s="32" t="n"/>
       <c r="M33" s="22">
         <f>IF(H33="","",IF(K33="No",0,H33*N(I33)/100*IF(L33="",100,L33)/100))</f>
@@ -20157,7 +20147,7 @@
         <f>IF(H34="","",ROUND(H34*N(I34)/100,2))</f>
         <v/>
       </c>
-      <c r="K34" s="30" t="n"/>
+      <c r="K34" s="38" t="n"/>
       <c r="L34" s="32" t="n"/>
       <c r="M34" s="22">
         <f>IF(H34="","",IF(K34="No",0,H34*N(I34)/100*IF(L34="",100,L34)/100))</f>
@@ -20189,7 +20179,7 @@
         <f>IF(H35="","",ROUND(H35*N(I35)/100,2))</f>
         <v/>
       </c>
-      <c r="K35" s="30" t="n"/>
+      <c r="K35" s="38" t="n"/>
       <c r="L35" s="32" t="n"/>
       <c r="M35" s="22">
         <f>IF(H35="","",IF(K35="No",0,H35*N(I35)/100*IF(L35="",100,L35)/100))</f>
@@ -20221,7 +20211,7 @@
         <f>IF(H36="","",ROUND(H36*N(I36)/100,2))</f>
         <v/>
       </c>
-      <c r="K36" s="30" t="n"/>
+      <c r="K36" s="38" t="n"/>
       <c r="L36" s="32" t="n"/>
       <c r="M36" s="22">
         <f>IF(H36="","",IF(K36="No",0,H36*N(I36)/100*IF(L36="",100,L36)/100))</f>
@@ -20253,7 +20243,7 @@
         <f>IF(H37="","",ROUND(H37*N(I37)/100,2))</f>
         <v/>
       </c>
-      <c r="K37" s="30" t="n"/>
+      <c r="K37" s="38" t="n"/>
       <c r="L37" s="32" t="n"/>
       <c r="M37" s="22">
         <f>IF(H37="","",IF(K37="No",0,H37*N(I37)/100*IF(L37="",100,L37)/100))</f>
@@ -20285,7 +20275,7 @@
         <f>IF(H38="","",ROUND(H38*N(I38)/100,2))</f>
         <v/>
       </c>
-      <c r="K38" s="30" t="n"/>
+      <c r="K38" s="38" t="n"/>
       <c r="L38" s="32" t="n"/>
       <c r="M38" s="22">
         <f>IF(H38="","",IF(K38="No",0,H38*N(I38)/100*IF(L38="",100,L38)/100))</f>
@@ -20317,7 +20307,7 @@
         <f>IF(H39="","",ROUND(H39*N(I39)/100,2))</f>
         <v/>
       </c>
-      <c r="K39" s="30" t="n"/>
+      <c r="K39" s="38" t="n"/>
       <c r="L39" s="32" t="n"/>
       <c r="M39" s="22">
         <f>IF(H39="","",IF(K39="No",0,H39*N(I39)/100*IF(L39="",100,L39)/100))</f>
@@ -20349,7 +20339,7 @@
         <f>IF(H40="","",ROUND(H40*N(I40)/100,2))</f>
         <v/>
       </c>
-      <c r="K40" s="30" t="n"/>
+      <c r="K40" s="38" t="n"/>
       <c r="L40" s="32" t="n"/>
       <c r="M40" s="22">
         <f>IF(H40="","",IF(K40="No",0,H40*N(I40)/100*IF(L40="",100,L40)/100))</f>
@@ -20381,7 +20371,7 @@
         <f>IF(H41="","",ROUND(H41*N(I41)/100,2))</f>
         <v/>
       </c>
-      <c r="K41" s="30" t="n"/>
+      <c r="K41" s="38" t="n"/>
       <c r="L41" s="32" t="n"/>
       <c r="M41" s="22">
         <f>IF(H41="","",IF(K41="No",0,H41*N(I41)/100*IF(L41="",100,L41)/100))</f>
@@ -20413,7 +20403,7 @@
         <f>IF(H42="","",ROUND(H42*N(I42)/100,2))</f>
         <v/>
       </c>
-      <c r="K42" s="30" t="n"/>
+      <c r="K42" s="38" t="n"/>
       <c r="L42" s="32" t="n"/>
       <c r="M42" s="22">
         <f>IF(H42="","",IF(K42="No",0,H42*N(I42)/100*IF(L42="",100,L42)/100))</f>
@@ -20445,7 +20435,7 @@
         <f>IF(H43="","",ROUND(H43*N(I43)/100,2))</f>
         <v/>
       </c>
-      <c r="K43" s="30" t="n"/>
+      <c r="K43" s="38" t="n"/>
       <c r="L43" s="32" t="n"/>
       <c r="M43" s="22">
         <f>IF(H43="","",IF(K43="No",0,H43*N(I43)/100*IF(L43="",100,L43)/100))</f>
@@ -20477,7 +20467,7 @@
         <f>IF(H44="","",ROUND(H44*N(I44)/100,2))</f>
         <v/>
       </c>
-      <c r="K44" s="30" t="n"/>
+      <c r="K44" s="38" t="n"/>
       <c r="L44" s="32" t="n"/>
       <c r="M44" s="22">
         <f>IF(H44="","",IF(K44="No",0,H44*N(I44)/100*IF(L44="",100,L44)/100))</f>
@@ -20509,7 +20499,7 @@
         <f>IF(H45="","",ROUND(H45*N(I45)/100,2))</f>
         <v/>
       </c>
-      <c r="K45" s="30" t="n"/>
+      <c r="K45" s="38" t="n"/>
       <c r="L45" s="32" t="n"/>
       <c r="M45" s="22">
         <f>IF(H45="","",IF(K45="No",0,H45*N(I45)/100*IF(L45="",100,L45)/100))</f>
@@ -20541,7 +20531,7 @@
         <f>IF(H46="","",ROUND(H46*N(I46)/100,2))</f>
         <v/>
       </c>
-      <c r="K46" s="30" t="n"/>
+      <c r="K46" s="38" t="n"/>
       <c r="L46" s="32" t="n"/>
       <c r="M46" s="22">
         <f>IF(H46="","",IF(K46="No",0,H46*N(I46)/100*IF(L46="",100,L46)/100))</f>
@@ -20573,7 +20563,7 @@
         <f>IF(H47="","",ROUND(H47*N(I47)/100,2))</f>
         <v/>
       </c>
-      <c r="K47" s="30" t="n"/>
+      <c r="K47" s="38" t="n"/>
       <c r="L47" s="32" t="n"/>
       <c r="M47" s="22">
         <f>IF(H47="","",IF(K47="No",0,H47*N(I47)/100*IF(L47="",100,L47)/100))</f>
@@ -20605,7 +20595,7 @@
         <f>IF(H48="","",ROUND(H48*N(I48)/100,2))</f>
         <v/>
       </c>
-      <c r="K48" s="30" t="n"/>
+      <c r="K48" s="38" t="n"/>
       <c r="L48" s="32" t="n"/>
       <c r="M48" s="22">
         <f>IF(H48="","",IF(K48="No",0,H48*N(I48)/100*IF(L48="",100,L48)/100))</f>
@@ -20637,7 +20627,7 @@
         <f>IF(H49="","",ROUND(H49*N(I49)/100,2))</f>
         <v/>
       </c>
-      <c r="K49" s="30" t="n"/>
+      <c r="K49" s="38" t="n"/>
       <c r="L49" s="32" t="n"/>
       <c r="M49" s="22">
         <f>IF(H49="","",IF(K49="No",0,H49*N(I49)/100*IF(L49="",100,L49)/100))</f>
@@ -20669,7 +20659,7 @@
         <f>IF(H50="","",ROUND(H50*N(I50)/100,2))</f>
         <v/>
       </c>
-      <c r="K50" s="30" t="n"/>
+      <c r="K50" s="38" t="n"/>
       <c r="L50" s="32" t="n"/>
       <c r="M50" s="22">
         <f>IF(H50="","",IF(K50="No",0,H50*N(I50)/100*IF(L50="",100,L50)/100))</f>
@@ -20701,7 +20691,7 @@
         <f>IF(H51="","",ROUND(H51*N(I51)/100,2))</f>
         <v/>
       </c>
-      <c r="K51" s="30" t="n"/>
+      <c r="K51" s="38" t="n"/>
       <c r="L51" s="32" t="n"/>
       <c r="M51" s="22">
         <f>IF(H51="","",IF(K51="No",0,H51*N(I51)/100*IF(L51="",100,L51)/100))</f>
@@ -20733,7 +20723,7 @@
         <f>IF(H52="","",ROUND(H52*N(I52)/100,2))</f>
         <v/>
       </c>
-      <c r="K52" s="30" t="n"/>
+      <c r="K52" s="38" t="n"/>
       <c r="L52" s="32" t="n"/>
       <c r="M52" s="22">
         <f>IF(H52="","",IF(K52="No",0,H52*N(I52)/100*IF(L52="",100,L52)/100))</f>
@@ -20765,7 +20755,7 @@
         <f>IF(H53="","",ROUND(H53*N(I53)/100,2))</f>
         <v/>
       </c>
-      <c r="K53" s="30" t="n"/>
+      <c r="K53" s="38" t="n"/>
       <c r="L53" s="32" t="n"/>
       <c r="M53" s="22">
         <f>IF(H53="","",IF(K53="No",0,H53*N(I53)/100*IF(L53="",100,L53)/100))</f>
@@ -20797,7 +20787,7 @@
         <f>IF(H54="","",ROUND(H54*N(I54)/100,2))</f>
         <v/>
       </c>
-      <c r="K54" s="30" t="n"/>
+      <c r="K54" s="38" t="n"/>
       <c r="L54" s="32" t="n"/>
       <c r="M54" s="22">
         <f>IF(H54="","",IF(K54="No",0,H54*N(I54)/100*IF(L54="",100,L54)/100))</f>
@@ -20829,7 +20819,7 @@
         <f>IF(H55="","",ROUND(H55*N(I55)/100,2))</f>
         <v/>
       </c>
-      <c r="K55" s="30" t="n"/>
+      <c r="K55" s="38" t="n"/>
       <c r="L55" s="32" t="n"/>
       <c r="M55" s="22">
         <f>IF(H55="","",IF(K55="No",0,H55*N(I55)/100*IF(L55="",100,L55)/100))</f>
@@ -20861,7 +20851,7 @@
         <f>IF(H56="","",ROUND(H56*N(I56)/100,2))</f>
         <v/>
       </c>
-      <c r="K56" s="30" t="n"/>
+      <c r="K56" s="38" t="n"/>
       <c r="L56" s="32" t="n"/>
       <c r="M56" s="22">
         <f>IF(H56="","",IF(K56="No",0,H56*N(I56)/100*IF(L56="",100,L56)/100))</f>
@@ -20893,7 +20883,7 @@
         <f>IF(H57="","",ROUND(H57*N(I57)/100,2))</f>
         <v/>
       </c>
-      <c r="K57" s="30" t="n"/>
+      <c r="K57" s="38" t="n"/>
       <c r="L57" s="32" t="n"/>
       <c r="M57" s="22">
         <f>IF(H57="","",IF(K57="No",0,H57*N(I57)/100*IF(L57="",100,L57)/100))</f>
@@ -20925,7 +20915,7 @@
         <f>IF(H58="","",ROUND(H58*N(I58)/100,2))</f>
         <v/>
       </c>
-      <c r="K58" s="30" t="n"/>
+      <c r="K58" s="38" t="n"/>
       <c r="L58" s="32" t="n"/>
       <c r="M58" s="22">
         <f>IF(H58="","",IF(K58="No",0,H58*N(I58)/100*IF(L58="",100,L58)/100))</f>
@@ -20957,7 +20947,7 @@
         <f>IF(H59="","",ROUND(H59*N(I59)/100,2))</f>
         <v/>
       </c>
-      <c r="K59" s="30" t="n"/>
+      <c r="K59" s="38" t="n"/>
       <c r="L59" s="32" t="n"/>
       <c r="M59" s="22">
         <f>IF(H59="","",IF(K59="No",0,H59*N(I59)/100*IF(L59="",100,L59)/100))</f>
@@ -20989,7 +20979,7 @@
         <f>IF(H60="","",ROUND(H60*N(I60)/100,2))</f>
         <v/>
       </c>
-      <c r="K60" s="30" t="n"/>
+      <c r="K60" s="38" t="n"/>
       <c r="L60" s="32" t="n"/>
       <c r="M60" s="22">
         <f>IF(H60="","",IF(K60="No",0,H60*N(I60)/100*IF(L60="",100,L60)/100))</f>
@@ -21021,7 +21011,7 @@
         <f>IF(H61="","",ROUND(H61*N(I61)/100,2))</f>
         <v/>
       </c>
-      <c r="K61" s="30" t="n"/>
+      <c r="K61" s="38" t="n"/>
       <c r="L61" s="32" t="n"/>
       <c r="M61" s="22">
         <f>IF(H61="","",IF(K61="No",0,H61*N(I61)/100*IF(L61="",100,L61)/100))</f>
@@ -21053,7 +21043,7 @@
         <f>IF(H62="","",ROUND(H62*N(I62)/100,2))</f>
         <v/>
       </c>
-      <c r="K62" s="30" t="n"/>
+      <c r="K62" s="38" t="n"/>
       <c r="L62" s="32" t="n"/>
       <c r="M62" s="22">
         <f>IF(H62="","",IF(K62="No",0,H62*N(I62)/100*IF(L62="",100,L62)/100))</f>
@@ -21085,7 +21075,7 @@
         <f>IF(H63="","",ROUND(H63*N(I63)/100,2))</f>
         <v/>
       </c>
-      <c r="K63" s="30" t="n"/>
+      <c r="K63" s="38" t="n"/>
       <c r="L63" s="32" t="n"/>
       <c r="M63" s="22">
         <f>IF(H63="","",IF(K63="No",0,H63*N(I63)/100*IF(L63="",100,L63)/100))</f>
@@ -21117,7 +21107,7 @@
         <f>IF(H64="","",ROUND(H64*N(I64)/100,2))</f>
         <v/>
       </c>
-      <c r="K64" s="30" t="n"/>
+      <c r="K64" s="38" t="n"/>
       <c r="L64" s="32" t="n"/>
       <c r="M64" s="22">
         <f>IF(H64="","",IF(K64="No",0,H64*N(I64)/100*IF(L64="",100,L64)/100))</f>
@@ -21149,7 +21139,7 @@
         <f>IF(H65="","",ROUND(H65*N(I65)/100,2))</f>
         <v/>
       </c>
-      <c r="K65" s="30" t="n"/>
+      <c r="K65" s="38" t="n"/>
       <c r="L65" s="32" t="n"/>
       <c r="M65" s="22">
         <f>IF(H65="","",IF(K65="No",0,H65*N(I65)/100*IF(L65="",100,L65)/100))</f>
@@ -21181,7 +21171,7 @@
         <f>IF(H66="","",ROUND(H66*N(I66)/100,2))</f>
         <v/>
       </c>
-      <c r="K66" s="30" t="n"/>
+      <c r="K66" s="38" t="n"/>
       <c r="L66" s="32" t="n"/>
       <c r="M66" s="22">
         <f>IF(H66="","",IF(K66="No",0,H66*N(I66)/100*IF(L66="",100,L66)/100))</f>
@@ -21213,7 +21203,7 @@
         <f>IF(H67="","",ROUND(H67*N(I67)/100,2))</f>
         <v/>
       </c>
-      <c r="K67" s="30" t="n"/>
+      <c r="K67" s="38" t="n"/>
       <c r="L67" s="32" t="n"/>
       <c r="M67" s="22">
         <f>IF(H67="","",IF(K67="No",0,H67*N(I67)/100*IF(L67="",100,L67)/100))</f>
@@ -21245,7 +21235,7 @@
         <f>IF(H68="","",ROUND(H68*N(I68)/100,2))</f>
         <v/>
       </c>
-      <c r="K68" s="30" t="n"/>
+      <c r="K68" s="38" t="n"/>
       <c r="L68" s="32" t="n"/>
       <c r="M68" s="22">
         <f>IF(H68="","",IF(K68="No",0,H68*N(I68)/100*IF(L68="",100,L68)/100))</f>
@@ -21277,7 +21267,7 @@
         <f>IF(H69="","",ROUND(H69*N(I69)/100,2))</f>
         <v/>
       </c>
-      <c r="K69" s="30" t="n"/>
+      <c r="K69" s="38" t="n"/>
       <c r="L69" s="32" t="n"/>
       <c r="M69" s="22">
         <f>IF(H69="","",IF(K69="No",0,H69*N(I69)/100*IF(L69="",100,L69)/100))</f>
@@ -21309,7 +21299,7 @@
         <f>IF(H70="","",ROUND(H70*N(I70)/100,2))</f>
         <v/>
       </c>
-      <c r="K70" s="30" t="n"/>
+      <c r="K70" s="38" t="n"/>
       <c r="L70" s="32" t="n"/>
       <c r="M70" s="22">
         <f>IF(H70="","",IF(K70="No",0,H70*N(I70)/100*IF(L70="",100,L70)/100))</f>
@@ -21341,7 +21331,7 @@
         <f>IF(H71="","",ROUND(H71*N(I71)/100,2))</f>
         <v/>
       </c>
-      <c r="K71" s="30" t="n"/>
+      <c r="K71" s="38" t="n"/>
       <c r="L71" s="32" t="n"/>
       <c r="M71" s="22">
         <f>IF(H71="","",IF(K71="No",0,H71*N(I71)/100*IF(L71="",100,L71)/100))</f>
@@ -21373,7 +21363,7 @@
         <f>IF(H72="","",ROUND(H72*N(I72)/100,2))</f>
         <v/>
       </c>
-      <c r="K72" s="30" t="n"/>
+      <c r="K72" s="38" t="n"/>
       <c r="L72" s="32" t="n"/>
       <c r="M72" s="22">
         <f>IF(H72="","",IF(K72="No",0,H72*N(I72)/100*IF(L72="",100,L72)/100))</f>
@@ -21405,7 +21395,7 @@
         <f>IF(H73="","",ROUND(H73*N(I73)/100,2))</f>
         <v/>
       </c>
-      <c r="K73" s="30" t="n"/>
+      <c r="K73" s="38" t="n"/>
       <c r="L73" s="32" t="n"/>
       <c r="M73" s="22">
         <f>IF(H73="","",IF(K73="No",0,H73*N(I73)/100*IF(L73="",100,L73)/100))</f>
@@ -21437,7 +21427,7 @@
         <f>IF(H74="","",ROUND(H74*N(I74)/100,2))</f>
         <v/>
       </c>
-      <c r="K74" s="30" t="n"/>
+      <c r="K74" s="38" t="n"/>
       <c r="L74" s="32" t="n"/>
       <c r="M74" s="22">
         <f>IF(H74="","",IF(K74="No",0,H74*N(I74)/100*IF(L74="",100,L74)/100))</f>
@@ -21469,7 +21459,7 @@
         <f>IF(H75="","",ROUND(H75*N(I75)/100,2))</f>
         <v/>
       </c>
-      <c r="K75" s="30" t="n"/>
+      <c r="K75" s="38" t="n"/>
       <c r="L75" s="32" t="n"/>
       <c r="M75" s="22">
         <f>IF(H75="","",IF(K75="No",0,H75*N(I75)/100*IF(L75="",100,L75)/100))</f>
@@ -21501,7 +21491,7 @@
         <f>IF(H76="","",ROUND(H76*N(I76)/100,2))</f>
         <v/>
       </c>
-      <c r="K76" s="30" t="n"/>
+      <c r="K76" s="38" t="n"/>
       <c r="L76" s="32" t="n"/>
       <c r="M76" s="22">
         <f>IF(H76="","",IF(K76="No",0,H76*N(I76)/100*IF(L76="",100,L76)/100))</f>
@@ -21533,7 +21523,7 @@
         <f>IF(H77="","",ROUND(H77*N(I77)/100,2))</f>
         <v/>
       </c>
-      <c r="K77" s="30" t="n"/>
+      <c r="K77" s="38" t="n"/>
       <c r="L77" s="32" t="n"/>
       <c r="M77" s="22">
         <f>IF(H77="","",IF(K77="No",0,H77*N(I77)/100*IF(L77="",100,L77)/100))</f>
@@ -21565,7 +21555,7 @@
         <f>IF(H78="","",ROUND(H78*N(I78)/100,2))</f>
         <v/>
       </c>
-      <c r="K78" s="30" t="n"/>
+      <c r="K78" s="38" t="n"/>
       <c r="L78" s="32" t="n"/>
       <c r="M78" s="22">
         <f>IF(H78="","",IF(K78="No",0,H78*N(I78)/100*IF(L78="",100,L78)/100))</f>
@@ -21597,7 +21587,7 @@
         <f>IF(H79="","",ROUND(H79*N(I79)/100,2))</f>
         <v/>
       </c>
-      <c r="K79" s="30" t="n"/>
+      <c r="K79" s="38" t="n"/>
       <c r="L79" s="32" t="n"/>
       <c r="M79" s="22">
         <f>IF(H79="","",IF(K79="No",0,H79*N(I79)/100*IF(L79="",100,L79)/100))</f>
@@ -21629,7 +21619,7 @@
         <f>IF(H80="","",ROUND(H80*N(I80)/100,2))</f>
         <v/>
       </c>
-      <c r="K80" s="30" t="n"/>
+      <c r="K80" s="38" t="n"/>
       <c r="L80" s="32" t="n"/>
       <c r="M80" s="22">
         <f>IF(H80="","",IF(K80="No",0,H80*N(I80)/100*IF(L80="",100,L80)/100))</f>
@@ -21661,7 +21651,7 @@
         <f>IF(H81="","",ROUND(H81*N(I81)/100,2))</f>
         <v/>
       </c>
-      <c r="K81" s="30" t="n"/>
+      <c r="K81" s="38" t="n"/>
       <c r="L81" s="32" t="n"/>
       <c r="M81" s="22">
         <f>IF(H81="","",IF(K81="No",0,H81*N(I81)/100*IF(L81="",100,L81)/100))</f>
@@ -21693,7 +21683,7 @@
         <f>IF(H82="","",ROUND(H82*N(I82)/100,2))</f>
         <v/>
       </c>
-      <c r="K82" s="30" t="n"/>
+      <c r="K82" s="38" t="n"/>
       <c r="L82" s="32" t="n"/>
       <c r="M82" s="22">
         <f>IF(H82="","",IF(K82="No",0,H82*N(I82)/100*IF(L82="",100,L82)/100))</f>
@@ -21725,7 +21715,7 @@
         <f>IF(H83="","",ROUND(H83*N(I83)/100,2))</f>
         <v/>
       </c>
-      <c r="K83" s="30" t="n"/>
+      <c r="K83" s="38" t="n"/>
       <c r="L83" s="32" t="n"/>
       <c r="M83" s="22">
         <f>IF(H83="","",IF(K83="No",0,H83*N(I83)/100*IF(L83="",100,L83)/100))</f>
@@ -21757,7 +21747,7 @@
         <f>IF(H84="","",ROUND(H84*N(I84)/100,2))</f>
         <v/>
       </c>
-      <c r="K84" s="30" t="n"/>
+      <c r="K84" s="38" t="n"/>
       <c r="L84" s="32" t="n"/>
       <c r="M84" s="22">
         <f>IF(H84="","",IF(K84="No",0,H84*N(I84)/100*IF(L84="",100,L84)/100))</f>
@@ -21789,7 +21779,7 @@
         <f>IF(H85="","",ROUND(H85*N(I85)/100,2))</f>
         <v/>
       </c>
-      <c r="K85" s="30" t="n"/>
+      <c r="K85" s="38" t="n"/>
       <c r="L85" s="32" t="n"/>
       <c r="M85" s="22">
         <f>IF(H85="","",IF(K85="No",0,H85*N(I85)/100*IF(L85="",100,L85)/100))</f>
@@ -21821,7 +21811,7 @@
         <f>IF(H86="","",ROUND(H86*N(I86)/100,2))</f>
         <v/>
       </c>
-      <c r="K86" s="30" t="n"/>
+      <c r="K86" s="38" t="n"/>
       <c r="L86" s="32" t="n"/>
       <c r="M86" s="22">
         <f>IF(H86="","",IF(K86="No",0,H86*N(I86)/100*IF(L86="",100,L86)/100))</f>
@@ -21853,7 +21843,7 @@
         <f>IF(H87="","",ROUND(H87*N(I87)/100,2))</f>
         <v/>
       </c>
-      <c r="K87" s="30" t="n"/>
+      <c r="K87" s="38" t="n"/>
       <c r="L87" s="32" t="n"/>
       <c r="M87" s="22">
         <f>IF(H87="","",IF(K87="No",0,H87*N(I87)/100*IF(L87="",100,L87)/100))</f>
@@ -21885,7 +21875,7 @@
         <f>IF(H88="","",ROUND(H88*N(I88)/100,2))</f>
         <v/>
       </c>
-      <c r="K88" s="30" t="n"/>
+      <c r="K88" s="38" t="n"/>
       <c r="L88" s="32" t="n"/>
       <c r="M88" s="22">
         <f>IF(H88="","",IF(K88="No",0,H88*N(I88)/100*IF(L88="",100,L88)/100))</f>
@@ -21917,7 +21907,7 @@
         <f>IF(H89="","",ROUND(H89*N(I89)/100,2))</f>
         <v/>
       </c>
-      <c r="K89" s="30" t="n"/>
+      <c r="K89" s="38" t="n"/>
       <c r="L89" s="32" t="n"/>
       <c r="M89" s="22">
         <f>IF(H89="","",IF(K89="No",0,H89*N(I89)/100*IF(L89="",100,L89)/100))</f>
@@ -21949,7 +21939,7 @@
         <f>IF(H90="","",ROUND(H90*N(I90)/100,2))</f>
         <v/>
       </c>
-      <c r="K90" s="30" t="n"/>
+      <c r="K90" s="38" t="n"/>
       <c r="L90" s="32" t="n"/>
       <c r="M90" s="22">
         <f>IF(H90="","",IF(K90="No",0,H90*N(I90)/100*IF(L90="",100,L90)/100))</f>
@@ -21981,7 +21971,7 @@
         <f>IF(H91="","",ROUND(H91*N(I91)/100,2))</f>
         <v/>
       </c>
-      <c r="K91" s="30" t="n"/>
+      <c r="K91" s="38" t="n"/>
       <c r="L91" s="32" t="n"/>
       <c r="M91" s="22">
         <f>IF(H91="","",IF(K91="No",0,H91*N(I91)/100*IF(L91="",100,L91)/100))</f>
@@ -22013,7 +22003,7 @@
         <f>IF(H92="","",ROUND(H92*N(I92)/100,2))</f>
         <v/>
       </c>
-      <c r="K92" s="30" t="n"/>
+      <c r="K92" s="38" t="n"/>
       <c r="L92" s="32" t="n"/>
       <c r="M92" s="22">
         <f>IF(H92="","",IF(K92="No",0,H92*N(I92)/100*IF(L92="",100,L92)/100))</f>
@@ -22045,7 +22035,7 @@
         <f>IF(H93="","",ROUND(H93*N(I93)/100,2))</f>
         <v/>
       </c>
-      <c r="K93" s="30" t="n"/>
+      <c r="K93" s="38" t="n"/>
       <c r="L93" s="32" t="n"/>
       <c r="M93" s="22">
         <f>IF(H93="","",IF(K93="No",0,H93*N(I93)/100*IF(L93="",100,L93)/100))</f>
@@ -22077,7 +22067,7 @@
         <f>IF(H94="","",ROUND(H94*N(I94)/100,2))</f>
         <v/>
       </c>
-      <c r="K94" s="30" t="n"/>
+      <c r="K94" s="38" t="n"/>
       <c r="L94" s="32" t="n"/>
       <c r="M94" s="22">
         <f>IF(H94="","",IF(K94="No",0,H94*N(I94)/100*IF(L94="",100,L94)/100))</f>
@@ -22109,7 +22099,7 @@
         <f>IF(H95="","",ROUND(H95*N(I95)/100,2))</f>
         <v/>
       </c>
-      <c r="K95" s="30" t="n"/>
+      <c r="K95" s="38" t="n"/>
       <c r="L95" s="32" t="n"/>
       <c r="M95" s="22">
         <f>IF(H95="","",IF(K95="No",0,H95*N(I95)/100*IF(L95="",100,L95)/100))</f>
@@ -22141,7 +22131,7 @@
         <f>IF(H96="","",ROUND(H96*N(I96)/100,2))</f>
         <v/>
       </c>
-      <c r="K96" s="30" t="n"/>
+      <c r="K96" s="38" t="n"/>
       <c r="L96" s="32" t="n"/>
       <c r="M96" s="22">
         <f>IF(H96="","",IF(K96="No",0,H96*N(I96)/100*IF(L96="",100,L96)/100))</f>
@@ -22173,7 +22163,7 @@
         <f>IF(H97="","",ROUND(H97*N(I97)/100,2))</f>
         <v/>
       </c>
-      <c r="K97" s="30" t="n"/>
+      <c r="K97" s="38" t="n"/>
       <c r="L97" s="32" t="n"/>
       <c r="M97" s="22">
         <f>IF(H97="","",IF(K97="No",0,H97*N(I97)/100*IF(L97="",100,L97)/100))</f>
@@ -22205,7 +22195,7 @@
         <f>IF(H98="","",ROUND(H98*N(I98)/100,2))</f>
         <v/>
       </c>
-      <c r="K98" s="30" t="n"/>
+      <c r="K98" s="38" t="n"/>
       <c r="L98" s="32" t="n"/>
       <c r="M98" s="22">
         <f>IF(H98="","",IF(K98="No",0,H98*N(I98)/100*IF(L98="",100,L98)/100))</f>
@@ -22237,7 +22227,7 @@
         <f>IF(H99="","",ROUND(H99*N(I99)/100,2))</f>
         <v/>
       </c>
-      <c r="K99" s="30" t="n"/>
+      <c r="K99" s="38" t="n"/>
       <c r="L99" s="32" t="n"/>
       <c r="M99" s="22">
         <f>IF(H99="","",IF(K99="No",0,H99*N(I99)/100*IF(L99="",100,L99)/100))</f>
@@ -22269,7 +22259,7 @@
         <f>IF(H100="","",ROUND(H100*N(I100)/100,2))</f>
         <v/>
       </c>
-      <c r="K100" s="30" t="n"/>
+      <c r="K100" s="38" t="n"/>
       <c r="L100" s="32" t="n"/>
       <c r="M100" s="22">
         <f>IF(H100="","",IF(K100="No",0,H100*N(I100)/100*IF(L100="",100,L100)/100))</f>
@@ -22301,7 +22291,7 @@
         <f>IF(H101="","",ROUND(H101*N(I101)/100,2))</f>
         <v/>
       </c>
-      <c r="K101" s="30" t="n"/>
+      <c r="K101" s="38" t="n"/>
       <c r="L101" s="32" t="n"/>
       <c r="M101" s="22">
         <f>IF(H101="","",IF(K101="No",0,H101*N(I101)/100*IF(L101="",100,L101)/100))</f>
@@ -22333,7 +22323,7 @@
         <f>IF(H102="","",ROUND(H102*N(I102)/100,2))</f>
         <v/>
       </c>
-      <c r="K102" s="30" t="n"/>
+      <c r="K102" s="38" t="n"/>
       <c r="L102" s="32" t="n"/>
       <c r="M102" s="22">
         <f>IF(H102="","",IF(K102="No",0,H102*N(I102)/100*IF(L102="",100,L102)/100))</f>
@@ -22365,7 +22355,7 @@
         <f>IF(H103="","",ROUND(H103*N(I103)/100,2))</f>
         <v/>
       </c>
-      <c r="K103" s="30" t="n"/>
+      <c r="K103" s="38" t="n"/>
       <c r="L103" s="32" t="n"/>
       <c r="M103" s="22">
         <f>IF(H103="","",IF(K103="No",0,H103*N(I103)/100*IF(L103="",100,L103)/100))</f>
@@ -22397,7 +22387,7 @@
         <f>IF(H104="","",ROUND(H104*N(I104)/100,2))</f>
         <v/>
       </c>
-      <c r="K104" s="30" t="n"/>
+      <c r="K104" s="38" t="n"/>
       <c r="L104" s="32" t="n"/>
       <c r="M104" s="22">
         <f>IF(H104="","",IF(K104="No",0,H104*N(I104)/100*IF(L104="",100,L104)/100))</f>
@@ -22429,7 +22419,7 @@
         <f>IF(H105="","",ROUND(H105*N(I105)/100,2))</f>
         <v/>
       </c>
-      <c r="K105" s="30" t="n"/>
+      <c r="K105" s="38" t="n"/>
       <c r="L105" s="32" t="n"/>
       <c r="M105" s="22">
         <f>IF(H105="","",IF(K105="No",0,H105*N(I105)/100*IF(L105="",100,L105)/100))</f>
@@ -22461,7 +22451,7 @@
         <f>IF(H106="","",ROUND(H106*N(I106)/100,2))</f>
         <v/>
       </c>
-      <c r="K106" s="30" t="n"/>
+      <c r="K106" s="38" t="n"/>
       <c r="L106" s="32" t="n"/>
       <c r="M106" s="22">
         <f>IF(H106="","",IF(K106="No",0,H106*N(I106)/100*IF(L106="",100,L106)/100))</f>
@@ -22493,7 +22483,7 @@
         <f>IF(H107="","",ROUND(H107*N(I107)/100,2))</f>
         <v/>
       </c>
-      <c r="K107" s="30" t="n"/>
+      <c r="K107" s="38" t="n"/>
       <c r="L107" s="32" t="n"/>
       <c r="M107" s="22">
         <f>IF(H107="","",IF(K107="No",0,H107*N(I107)/100*IF(L107="",100,L107)/100))</f>
@@ -22525,7 +22515,7 @@
         <f>IF(H108="","",ROUND(H108*N(I108)/100,2))</f>
         <v/>
       </c>
-      <c r="K108" s="30" t="n"/>
+      <c r="K108" s="38" t="n"/>
       <c r="L108" s="32" t="n"/>
       <c r="M108" s="22">
         <f>IF(H108="","",IF(K108="No",0,H108*N(I108)/100*IF(L108="",100,L108)/100))</f>
@@ -22557,7 +22547,7 @@
         <f>IF(H109="","",ROUND(H109*N(I109)/100,2))</f>
         <v/>
       </c>
-      <c r="K109" s="30" t="n"/>
+      <c r="K109" s="38" t="n"/>
       <c r="L109" s="32" t="n"/>
       <c r="M109" s="22">
         <f>IF(H109="","",IF(K109="No",0,H109*N(I109)/100*IF(L109="",100,L109)/100))</f>
@@ -22589,7 +22579,7 @@
         <f>IF(H110="","",ROUND(H110*N(I110)/100,2))</f>
         <v/>
       </c>
-      <c r="K110" s="30" t="n"/>
+      <c r="K110" s="38" t="n"/>
       <c r="L110" s="32" t="n"/>
       <c r="M110" s="22">
         <f>IF(H110="","",IF(K110="No",0,H110*N(I110)/100*IF(L110="",100,L110)/100))</f>
@@ -22621,7 +22611,7 @@
         <f>IF(H111="","",ROUND(H111*N(I111)/100,2))</f>
         <v/>
       </c>
-      <c r="K111" s="30" t="n"/>
+      <c r="K111" s="38" t="n"/>
       <c r="L111" s="32" t="n"/>
       <c r="M111" s="22">
         <f>IF(H111="","",IF(K111="No",0,H111*N(I111)/100*IF(L111="",100,L111)/100))</f>
@@ -22653,7 +22643,7 @@
         <f>IF(H112="","",ROUND(H112*N(I112)/100,2))</f>
         <v/>
       </c>
-      <c r="K112" s="30" t="n"/>
+      <c r="K112" s="38" t="n"/>
       <c r="L112" s="32" t="n"/>
       <c r="M112" s="22">
         <f>IF(H112="","",IF(K112="No",0,H112*N(I112)/100*IF(L112="",100,L112)/100))</f>
@@ -22685,7 +22675,7 @@
         <f>IF(H113="","",ROUND(H113*N(I113)/100,2))</f>
         <v/>
       </c>
-      <c r="K113" s="30" t="n"/>
+      <c r="K113" s="38" t="n"/>
       <c r="L113" s="32" t="n"/>
       <c r="M113" s="22">
         <f>IF(H113="","",IF(K113="No",0,H113*N(I113)/100*IF(L113="",100,L113)/100))</f>
@@ -22717,7 +22707,7 @@
         <f>IF(H114="","",ROUND(H114*N(I114)/100,2))</f>
         <v/>
       </c>
-      <c r="K114" s="30" t="n"/>
+      <c r="K114" s="38" t="n"/>
       <c r="L114" s="32" t="n"/>
       <c r="M114" s="22">
         <f>IF(H114="","",IF(K114="No",0,H114*N(I114)/100*IF(L114="",100,L114)/100))</f>
@@ -22749,7 +22739,7 @@
         <f>IF(H115="","",ROUND(H115*N(I115)/100,2))</f>
         <v/>
       </c>
-      <c r="K115" s="30" t="n"/>
+      <c r="K115" s="38" t="n"/>
       <c r="L115" s="32" t="n"/>
       <c r="M115" s="22">
         <f>IF(H115="","",IF(K115="No",0,H115*N(I115)/100*IF(L115="",100,L115)/100))</f>
@@ -22781,7 +22771,7 @@
         <f>IF(H116="","",ROUND(H116*N(I116)/100,2))</f>
         <v/>
       </c>
-      <c r="K116" s="30" t="n"/>
+      <c r="K116" s="38" t="n"/>
       <c r="L116" s="32" t="n"/>
       <c r="M116" s="22">
         <f>IF(H116="","",IF(K116="No",0,H116*N(I116)/100*IF(L116="",100,L116)/100))</f>
@@ -22813,7 +22803,7 @@
         <f>IF(H117="","",ROUND(H117*N(I117)/100,2))</f>
         <v/>
       </c>
-      <c r="K117" s="30" t="n"/>
+      <c r="K117" s="38" t="n"/>
       <c r="L117" s="32" t="n"/>
       <c r="M117" s="22">
         <f>IF(H117="","",IF(K117="No",0,H117*N(I117)/100*IF(L117="",100,L117)/100))</f>
@@ -22845,7 +22835,7 @@
         <f>IF(H118="","",ROUND(H118*N(I118)/100,2))</f>
         <v/>
       </c>
-      <c r="K118" s="30" t="n"/>
+      <c r="K118" s="38" t="n"/>
       <c r="L118" s="32" t="n"/>
       <c r="M118" s="22">
         <f>IF(H118="","",IF(K118="No",0,H118*N(I118)/100*IF(L118="",100,L118)/100))</f>
@@ -22877,7 +22867,7 @@
         <f>IF(H119="","",ROUND(H119*N(I119)/100,2))</f>
         <v/>
       </c>
-      <c r="K119" s="30" t="n"/>
+      <c r="K119" s="38" t="n"/>
       <c r="L119" s="32" t="n"/>
       <c r="M119" s="22">
         <f>IF(H119="","",IF(K119="No",0,H119*N(I119)/100*IF(L119="",100,L119)/100))</f>
@@ -22909,7 +22899,7 @@
         <f>IF(H120="","",ROUND(H120*N(I120)/100,2))</f>
         <v/>
       </c>
-      <c r="K120" s="30" t="n"/>
+      <c r="K120" s="38" t="n"/>
       <c r="L120" s="32" t="n"/>
       <c r="M120" s="22">
         <f>IF(H120="","",IF(K120="No",0,H120*N(I120)/100*IF(L120="",100,L120)/100))</f>
@@ -22941,7 +22931,7 @@
         <f>IF(H121="","",ROUND(H121*N(I121)/100,2))</f>
         <v/>
       </c>
-      <c r="K121" s="30" t="n"/>
+      <c r="K121" s="38" t="n"/>
       <c r="L121" s="32" t="n"/>
       <c r="M121" s="22">
         <f>IF(H121="","",IF(K121="No",0,H121*N(I121)/100*IF(L121="",100,L121)/100))</f>
@@ -22973,7 +22963,7 @@
         <f>IF(H122="","",ROUND(H122*N(I122)/100,2))</f>
         <v/>
       </c>
-      <c r="K122" s="30" t="n"/>
+      <c r="K122" s="38" t="n"/>
       <c r="L122" s="32" t="n"/>
       <c r="M122" s="22">
         <f>IF(H122="","",IF(K122="No",0,H122*N(I122)/100*IF(L122="",100,L122)/100))</f>
@@ -23005,7 +22995,7 @@
         <f>IF(H123="","",ROUND(H123*N(I123)/100,2))</f>
         <v/>
       </c>
-      <c r="K123" s="30" t="n"/>
+      <c r="K123" s="38" t="n"/>
       <c r="L123" s="32" t="n"/>
       <c r="M123" s="22">
         <f>IF(H123="","",IF(K123="No",0,H123*N(I123)/100*IF(L123="",100,L123)/100))</f>
@@ -23037,7 +23027,7 @@
         <f>IF(H124="","",ROUND(H124*N(I124)/100,2))</f>
         <v/>
       </c>
-      <c r="K124" s="30" t="n"/>
+      <c r="K124" s="38" t="n"/>
       <c r="L124" s="32" t="n"/>
       <c r="M124" s="22">
         <f>IF(H124="","",IF(K124="No",0,H124*N(I124)/100*IF(L124="",100,L124)/100))</f>
@@ -23069,7 +23059,7 @@
         <f>IF(H125="","",ROUND(H125*N(I125)/100,2))</f>
         <v/>
       </c>
-      <c r="K125" s="30" t="n"/>
+      <c r="K125" s="38" t="n"/>
       <c r="L125" s="32" t="n"/>
       <c r="M125" s="22">
         <f>IF(H125="","",IF(K125="No",0,H125*N(I125)/100*IF(L125="",100,L125)/100))</f>
@@ -23101,7 +23091,7 @@
         <f>IF(H126="","",ROUND(H126*N(I126)/100,2))</f>
         <v/>
       </c>
-      <c r="K126" s="30" t="n"/>
+      <c r="K126" s="38" t="n"/>
       <c r="L126" s="32" t="n"/>
       <c r="M126" s="22">
         <f>IF(H126="","",IF(K126="No",0,H126*N(I126)/100*IF(L126="",100,L126)/100))</f>
@@ -23133,7 +23123,7 @@
         <f>IF(H127="","",ROUND(H127*N(I127)/100,2))</f>
         <v/>
       </c>
-      <c r="K127" s="30" t="n"/>
+      <c r="K127" s="38" t="n"/>
       <c r="L127" s="32" t="n"/>
       <c r="M127" s="22">
         <f>IF(H127="","",IF(K127="No",0,H127*N(I127)/100*IF(L127="",100,L127)/100))</f>
@@ -23165,7 +23155,7 @@
         <f>IF(H128="","",ROUND(H128*N(I128)/100,2))</f>
         <v/>
       </c>
-      <c r="K128" s="30" t="n"/>
+      <c r="K128" s="38" t="n"/>
       <c r="L128" s="32" t="n"/>
       <c r="M128" s="22">
         <f>IF(H128="","",IF(K128="No",0,H128*N(I128)/100*IF(L128="",100,L128)/100))</f>
@@ -23197,7 +23187,7 @@
         <f>IF(H129="","",ROUND(H129*N(I129)/100,2))</f>
         <v/>
       </c>
-      <c r="K129" s="30" t="n"/>
+      <c r="K129" s="38" t="n"/>
       <c r="L129" s="32" t="n"/>
       <c r="M129" s="22">
         <f>IF(H129="","",IF(K129="No",0,H129*N(I129)/100*IF(L129="",100,L129)/100))</f>
@@ -23229,7 +23219,7 @@
         <f>IF(H130="","",ROUND(H130*N(I130)/100,2))</f>
         <v/>
       </c>
-      <c r="K130" s="30" t="n"/>
+      <c r="K130" s="38" t="n"/>
       <c r="L130" s="32" t="n"/>
       <c r="M130" s="22">
         <f>IF(H130="","",IF(K130="No",0,H130*N(I130)/100*IF(L130="",100,L130)/100))</f>
@@ -23261,7 +23251,7 @@
         <f>IF(H131="","",ROUND(H131*N(I131)/100,2))</f>
         <v/>
       </c>
-      <c r="K131" s="30" t="n"/>
+      <c r="K131" s="38" t="n"/>
       <c r="L131" s="32" t="n"/>
       <c r="M131" s="22">
         <f>IF(H131="","",IF(K131="No",0,H131*N(I131)/100*IF(L131="",100,L131)/100))</f>
@@ -23293,7 +23283,7 @@
         <f>IF(H132="","",ROUND(H132*N(I132)/100,2))</f>
         <v/>
       </c>
-      <c r="K132" s="30" t="n"/>
+      <c r="K132" s="38" t="n"/>
       <c r="L132" s="32" t="n"/>
       <c r="M132" s="22">
         <f>IF(H132="","",IF(K132="No",0,H132*N(I132)/100*IF(L132="",100,L132)/100))</f>
@@ -23325,7 +23315,7 @@
         <f>IF(H133="","",ROUND(H133*N(I133)/100,2))</f>
         <v/>
       </c>
-      <c r="K133" s="30" t="n"/>
+      <c r="K133" s="38" t="n"/>
       <c r="L133" s="32" t="n"/>
       <c r="M133" s="22">
         <f>IF(H133="","",IF(K133="No",0,H133*N(I133)/100*IF(L133="",100,L133)/100))</f>
@@ -23357,7 +23347,7 @@
         <f>IF(H134="","",ROUND(H134*N(I134)/100,2))</f>
         <v/>
       </c>
-      <c r="K134" s="30" t="n"/>
+      <c r="K134" s="38" t="n"/>
       <c r="L134" s="32" t="n"/>
       <c r="M134" s="22">
         <f>IF(H134="","",IF(K134="No",0,H134*N(I134)/100*IF(L134="",100,L134)/100))</f>
@@ -23389,7 +23379,7 @@
         <f>IF(H135="","",ROUND(H135*N(I135)/100,2))</f>
         <v/>
       </c>
-      <c r="K135" s="30" t="n"/>
+      <c r="K135" s="38" t="n"/>
       <c r="L135" s="32" t="n"/>
       <c r="M135" s="22">
         <f>IF(H135="","",IF(K135="No",0,H135*N(I135)/100*IF(L135="",100,L135)/100))</f>
@@ -23421,7 +23411,7 @@
         <f>IF(H136="","",ROUND(H136*N(I136)/100,2))</f>
         <v/>
       </c>
-      <c r="K136" s="30" t="n"/>
+      <c r="K136" s="38" t="n"/>
       <c r="L136" s="32" t="n"/>
       <c r="M136" s="22">
         <f>IF(H136="","",IF(K136="No",0,H136*N(I136)/100*IF(L136="",100,L136)/100))</f>
@@ -23453,7 +23443,7 @@
         <f>IF(H137="","",ROUND(H137*N(I137)/100,2))</f>
         <v/>
       </c>
-      <c r="K137" s="30" t="n"/>
+      <c r="K137" s="38" t="n"/>
       <c r="L137" s="32" t="n"/>
       <c r="M137" s="22">
         <f>IF(H137="","",IF(K137="No",0,H137*N(I137)/100*IF(L137="",100,L137)/100))</f>
@@ -23485,7 +23475,7 @@
         <f>IF(H138="","",ROUND(H138*N(I138)/100,2))</f>
         <v/>
       </c>
-      <c r="K138" s="30" t="n"/>
+      <c r="K138" s="38" t="n"/>
       <c r="L138" s="32" t="n"/>
       <c r="M138" s="22">
         <f>IF(H138="","",IF(K138="No",0,H138*N(I138)/100*IF(L138="",100,L138)/100))</f>
@@ -23517,7 +23507,7 @@
         <f>IF(H139="","",ROUND(H139*N(I139)/100,2))</f>
         <v/>
       </c>
-      <c r="K139" s="30" t="n"/>
+      <c r="K139" s="38" t="n"/>
       <c r="L139" s="32" t="n"/>
       <c r="M139" s="22">
         <f>IF(H139="","",IF(K139="No",0,H139*N(I139)/100*IF(L139="",100,L139)/100))</f>
@@ -23549,7 +23539,7 @@
         <f>IF(H140="","",ROUND(H140*N(I140)/100,2))</f>
         <v/>
       </c>
-      <c r="K140" s="30" t="n"/>
+      <c r="K140" s="38" t="n"/>
       <c r="L140" s="32" t="n"/>
       <c r="M140" s="22">
         <f>IF(H140="","",IF(K140="No",0,H140*N(I140)/100*IF(L140="",100,L140)/100))</f>
@@ -23581,7 +23571,7 @@
         <f>IF(H141="","",ROUND(H141*N(I141)/100,2))</f>
         <v/>
       </c>
-      <c r="K141" s="30" t="n"/>
+      <c r="K141" s="38" t="n"/>
       <c r="L141" s="32" t="n"/>
       <c r="M141" s="22">
         <f>IF(H141="","",IF(K141="No",0,H141*N(I141)/100*IF(L141="",100,L141)/100))</f>
@@ -23613,7 +23603,7 @@
         <f>IF(H142="","",ROUND(H142*N(I142)/100,2))</f>
         <v/>
       </c>
-      <c r="K142" s="30" t="n"/>
+      <c r="K142" s="38" t="n"/>
       <c r="L142" s="32" t="n"/>
       <c r="M142" s="22">
         <f>IF(H142="","",IF(K142="No",0,H142*N(I142)/100*IF(L142="",100,L142)/100))</f>
@@ -23645,7 +23635,7 @@
         <f>IF(H143="","",ROUND(H143*N(I143)/100,2))</f>
         <v/>
       </c>
-      <c r="K143" s="30" t="n"/>
+      <c r="K143" s="38" t="n"/>
       <c r="L143" s="32" t="n"/>
       <c r="M143" s="22">
         <f>IF(H143="","",IF(K143="No",0,H143*N(I143)/100*IF(L143="",100,L143)/100))</f>
@@ -23677,7 +23667,7 @@
         <f>IF(H144="","",ROUND(H144*N(I144)/100,2))</f>
         <v/>
       </c>
-      <c r="K144" s="30" t="n"/>
+      <c r="K144" s="38" t="n"/>
       <c r="L144" s="32" t="n"/>
       <c r="M144" s="22">
         <f>IF(H144="","",IF(K144="No",0,H144*N(I144)/100*IF(L144="",100,L144)/100))</f>
@@ -23709,7 +23699,7 @@
         <f>IF(H145="","",ROUND(H145*N(I145)/100,2))</f>
         <v/>
       </c>
-      <c r="K145" s="30" t="n"/>
+      <c r="K145" s="38" t="n"/>
       <c r="L145" s="32" t="n"/>
       <c r="M145" s="22">
         <f>IF(H145="","",IF(K145="No",0,H145*N(I145)/100*IF(L145="",100,L145)/100))</f>
@@ -23741,7 +23731,7 @@
         <f>IF(H146="","",ROUND(H146*N(I146)/100,2))</f>
         <v/>
       </c>
-      <c r="K146" s="30" t="n"/>
+      <c r="K146" s="38" t="n"/>
       <c r="L146" s="32" t="n"/>
       <c r="M146" s="22">
         <f>IF(H146="","",IF(K146="No",0,H146*N(I146)/100*IF(L146="",100,L146)/100))</f>
@@ -23773,7 +23763,7 @@
         <f>IF(H147="","",ROUND(H147*N(I147)/100,2))</f>
         <v/>
       </c>
-      <c r="K147" s="30" t="n"/>
+      <c r="K147" s="38" t="n"/>
       <c r="L147" s="32" t="n"/>
       <c r="M147" s="22">
         <f>IF(H147="","",IF(K147="No",0,H147*N(I147)/100*IF(L147="",100,L147)/100))</f>
@@ -23805,7 +23795,7 @@
         <f>IF(H148="","",ROUND(H148*N(I148)/100,2))</f>
         <v/>
       </c>
-      <c r="K148" s="30" t="n"/>
+      <c r="K148" s="38" t="n"/>
       <c r="L148" s="32" t="n"/>
       <c r="M148" s="22">
         <f>IF(H148="","",IF(K148="No",0,H148*N(I148)/100*IF(L148="",100,L148)/100))</f>
@@ -23837,7 +23827,7 @@
         <f>IF(H149="","",ROUND(H149*N(I149)/100,2))</f>
         <v/>
       </c>
-      <c r="K149" s="30" t="n"/>
+      <c r="K149" s="38" t="n"/>
       <c r="L149" s="32" t="n"/>
       <c r="M149" s="22">
         <f>IF(H149="","",IF(K149="No",0,H149*N(I149)/100*IF(L149="",100,L149)/100))</f>
@@ -23869,7 +23859,7 @@
         <f>IF(H150="","",ROUND(H150*N(I150)/100,2))</f>
         <v/>
       </c>
-      <c r="K150" s="30" t="n"/>
+      <c r="K150" s="38" t="n"/>
       <c r="L150" s="32" t="n"/>
       <c r="M150" s="22">
         <f>IF(H150="","",IF(K150="No",0,H150*N(I150)/100*IF(L150="",100,L150)/100))</f>
@@ -23901,7 +23891,7 @@
         <f>IF(H151="","",ROUND(H151*N(I151)/100,2))</f>
         <v/>
       </c>
-      <c r="K151" s="30" t="n"/>
+      <c r="K151" s="38" t="n"/>
       <c r="L151" s="32" t="n"/>
       <c r="M151" s="22">
         <f>IF(H151="","",IF(K151="No",0,H151*N(I151)/100*IF(L151="",100,L151)/100))</f>
@@ -23933,7 +23923,7 @@
         <f>IF(H152="","",ROUND(H152*N(I152)/100,2))</f>
         <v/>
       </c>
-      <c r="K152" s="30" t="n"/>
+      <c r="K152" s="38" t="n"/>
       <c r="L152" s="32" t="n"/>
       <c r="M152" s="22">
         <f>IF(H152="","",IF(K152="No",0,H152*N(I152)/100*IF(L152="",100,L152)/100))</f>
@@ -23965,7 +23955,7 @@
         <f>IF(H153="","",ROUND(H153*N(I153)/100,2))</f>
         <v/>
       </c>
-      <c r="K153" s="30" t="n"/>
+      <c r="K153" s="38" t="n"/>
       <c r="L153" s="32" t="n"/>
       <c r="M153" s="22">
         <f>IF(H153="","",IF(K153="No",0,H153*N(I153)/100*IF(L153="",100,L153)/100))</f>
@@ -23997,7 +23987,7 @@
         <f>IF(H154="","",ROUND(H154*N(I154)/100,2))</f>
         <v/>
       </c>
-      <c r="K154" s="30" t="n"/>
+      <c r="K154" s="38" t="n"/>
       <c r="L154" s="32" t="n"/>
       <c r="M154" s="22">
         <f>IF(H154="","",IF(K154="No",0,H154*N(I154)/100*IF(L154="",100,L154)/100))</f>
@@ -24029,7 +24019,7 @@
         <f>IF(H155="","",ROUND(H155*N(I155)/100,2))</f>
         <v/>
       </c>
-      <c r="K155" s="30" t="n"/>
+      <c r="K155" s="38" t="n"/>
       <c r="L155" s="32" t="n"/>
       <c r="M155" s="22">
         <f>IF(H155="","",IF(K155="No",0,H155*N(I155)/100*IF(L155="",100,L155)/100))</f>
@@ -24061,7 +24051,7 @@
         <f>IF(H156="","",ROUND(H156*N(I156)/100,2))</f>
         <v/>
       </c>
-      <c r="K156" s="30" t="n"/>
+      <c r="K156" s="38" t="n"/>
       <c r="L156" s="32" t="n"/>
       <c r="M156" s="22">
         <f>IF(H156="","",IF(K156="No",0,H156*N(I156)/100*IF(L156="",100,L156)/100))</f>
@@ -24093,7 +24083,7 @@
         <f>IF(H157="","",ROUND(H157*N(I157)/100,2))</f>
         <v/>
       </c>
-      <c r="K157" s="30" t="n"/>
+      <c r="K157" s="38" t="n"/>
       <c r="L157" s="32" t="n"/>
       <c r="M157" s="22">
         <f>IF(H157="","",IF(K157="No",0,H157*N(I157)/100*IF(L157="",100,L157)/100))</f>
@@ -24125,7 +24115,7 @@
         <f>IF(H158="","",ROUND(H158*N(I158)/100,2))</f>
         <v/>
       </c>
-      <c r="K158" s="30" t="n"/>
+      <c r="K158" s="38" t="n"/>
       <c r="L158" s="32" t="n"/>
       <c r="M158" s="22">
         <f>IF(H158="","",IF(K158="No",0,H158*N(I158)/100*IF(L158="",100,L158)/100))</f>
@@ -24157,7 +24147,7 @@
         <f>IF(H159="","",ROUND(H159*N(I159)/100,2))</f>
         <v/>
       </c>
-      <c r="K159" s="30" t="n"/>
+      <c r="K159" s="38" t="n"/>
       <c r="L159" s="32" t="n"/>
       <c r="M159" s="22">
         <f>IF(H159="","",IF(K159="No",0,H159*N(I159)/100*IF(L159="",100,L159)/100))</f>
@@ -24189,7 +24179,7 @@
         <f>IF(H160="","",ROUND(H160*N(I160)/100,2))</f>
         <v/>
       </c>
-      <c r="K160" s="30" t="n"/>
+      <c r="K160" s="38" t="n"/>
       <c r="L160" s="32" t="n"/>
       <c r="M160" s="22">
         <f>IF(H160="","",IF(K160="No",0,H160*N(I160)/100*IF(L160="",100,L160)/100))</f>
@@ -24221,7 +24211,7 @@
         <f>IF(H161="","",ROUND(H161*N(I161)/100,2))</f>
         <v/>
       </c>
-      <c r="K161" s="30" t="n"/>
+      <c r="K161" s="38" t="n"/>
       <c r="L161" s="32" t="n"/>
       <c r="M161" s="22">
         <f>IF(H161="","",IF(K161="No",0,H161*N(I161)/100*IF(L161="",100,L161)/100))</f>
@@ -24253,7 +24243,7 @@
         <f>IF(H162="","",ROUND(H162*N(I162)/100,2))</f>
         <v/>
       </c>
-      <c r="K162" s="30" t="n"/>
+      <c r="K162" s="38" t="n"/>
       <c r="L162" s="32" t="n"/>
       <c r="M162" s="22">
         <f>IF(H162="","",IF(K162="No",0,H162*N(I162)/100*IF(L162="",100,L162)/100))</f>
@@ -24285,7 +24275,7 @@
         <f>IF(H163="","",ROUND(H163*N(I163)/100,2))</f>
         <v/>
       </c>
-      <c r="K163" s="30" t="n"/>
+      <c r="K163" s="38" t="n"/>
       <c r="L163" s="32" t="n"/>
       <c r="M163" s="22">
         <f>IF(H163="","",IF(K163="No",0,H163*N(I163)/100*IF(L163="",100,L163)/100))</f>
@@ -24317,7 +24307,7 @@
         <f>IF(H164="","",ROUND(H164*N(I164)/100,2))</f>
         <v/>
       </c>
-      <c r="K164" s="30" t="n"/>
+      <c r="K164" s="38" t="n"/>
       <c r="L164" s="32" t="n"/>
       <c r="M164" s="22">
         <f>IF(H164="","",IF(K164="No",0,H164*N(I164)/100*IF(L164="",100,L164)/100))</f>
@@ -24349,7 +24339,7 @@
         <f>IF(H165="","",ROUND(H165*N(I165)/100,2))</f>
         <v/>
       </c>
-      <c r="K165" s="30" t="n"/>
+      <c r="K165" s="38" t="n"/>
       <c r="L165" s="32" t="n"/>
       <c r="M165" s="22">
         <f>IF(H165="","",IF(K165="No",0,H165*N(I165)/100*IF(L165="",100,L165)/100))</f>
@@ -24381,7 +24371,7 @@
         <f>IF(H166="","",ROUND(H166*N(I166)/100,2))</f>
         <v/>
       </c>
-      <c r="K166" s="30" t="n"/>
+      <c r="K166" s="38" t="n"/>
       <c r="L166" s="32" t="n"/>
       <c r="M166" s="22">
         <f>IF(H166="","",IF(K166="No",0,H166*N(I166)/100*IF(L166="",100,L166)/100))</f>
@@ -24413,7 +24403,7 @@
         <f>IF(H167="","",ROUND(H167*N(I167)/100,2))</f>
         <v/>
       </c>
-      <c r="K167" s="30" t="n"/>
+      <c r="K167" s="38" t="n"/>
       <c r="L167" s="32" t="n"/>
       <c r="M167" s="22">
         <f>IF(H167="","",IF(K167="No",0,H167*N(I167)/100*IF(L167="",100,L167)/100))</f>
@@ -24445,7 +24435,7 @@
         <f>IF(H168="","",ROUND(H168*N(I168)/100,2))</f>
         <v/>
       </c>
-      <c r="K168" s="30" t="n"/>
+      <c r="K168" s="38" t="n"/>
       <c r="L168" s="32" t="n"/>
       <c r="M168" s="22">
         <f>IF(H168="","",IF(K168="No",0,H168*N(I168)/100*IF(L168="",100,L168)/100))</f>
@@ -24477,7 +24467,7 @@
         <f>IF(H169="","",ROUND(H169*N(I169)/100,2))</f>
         <v/>
       </c>
-      <c r="K169" s="30" t="n"/>
+      <c r="K169" s="38" t="n"/>
       <c r="L169" s="32" t="n"/>
       <c r="M169" s="22">
         <f>IF(H169="","",IF(K169="No",0,H169*N(I169)/100*IF(L169="",100,L169)/100))</f>
@@ -24509,7 +24499,7 @@
         <f>IF(H170="","",ROUND(H170*N(I170)/100,2))</f>
         <v/>
       </c>
-      <c r="K170" s="30" t="n"/>
+      <c r="K170" s="38" t="n"/>
       <c r="L170" s="32" t="n"/>
       <c r="M170" s="22">
         <f>IF(H170="","",IF(K170="No",0,H170*N(I170)/100*IF(L170="",100,L170)/100))</f>
@@ -24541,7 +24531,7 @@
         <f>IF(H171="","",ROUND(H171*N(I171)/100,2))</f>
         <v/>
       </c>
-      <c r="K171" s="30" t="n"/>
+      <c r="K171" s="38" t="n"/>
       <c r="L171" s="32" t="n"/>
       <c r="M171" s="22">
         <f>IF(H171="","",IF(K171="No",0,H171*N(I171)/100*IF(L171="",100,L171)/100))</f>
@@ -24573,7 +24563,7 @@
         <f>IF(H172="","",ROUND(H172*N(I172)/100,2))</f>
         <v/>
       </c>
-      <c r="K172" s="30" t="n"/>
+      <c r="K172" s="38" t="n"/>
       <c r="L172" s="32" t="n"/>
       <c r="M172" s="22">
         <f>IF(H172="","",IF(K172="No",0,H172*N(I172)/100*IF(L172="",100,L172)/100))</f>
@@ -24605,7 +24595,7 @@
         <f>IF(H173="","",ROUND(H173*N(I173)/100,2))</f>
         <v/>
       </c>
-      <c r="K173" s="30" t="n"/>
+      <c r="K173" s="38" t="n"/>
       <c r="L173" s="32" t="n"/>
       <c r="M173" s="22">
         <f>IF(H173="","",IF(K173="No",0,H173*N(I173)/100*IF(L173="",100,L173)/100))</f>
@@ -24637,7 +24627,7 @@
         <f>IF(H174="","",ROUND(H174*N(I174)/100,2))</f>
         <v/>
       </c>
-      <c r="K174" s="30" t="n"/>
+      <c r="K174" s="38" t="n"/>
       <c r="L174" s="32" t="n"/>
       <c r="M174" s="22">
         <f>IF(H174="","",IF(K174="No",0,H174*N(I174)/100*IF(L174="",100,L174)/100))</f>
@@ -24669,7 +24659,7 @@
         <f>IF(H175="","",ROUND(H175*N(I175)/100,2))</f>
         <v/>
       </c>
-      <c r="K175" s="30" t="n"/>
+      <c r="K175" s="38" t="n"/>
       <c r="L175" s="32" t="n"/>
       <c r="M175" s="22">
         <f>IF(H175="","",IF(K175="No",0,H175*N(I175)/100*IF(L175="",100,L175)/100))</f>
@@ -24701,7 +24691,7 @@
         <f>IF(H176="","",ROUND(H176*N(I176)/100,2))</f>
         <v/>
       </c>
-      <c r="K176" s="30" t="n"/>
+      <c r="K176" s="38" t="n"/>
       <c r="L176" s="32" t="n"/>
       <c r="M176" s="22">
         <f>IF(H176="","",IF(K176="No",0,H176*N(I176)/100*IF(L176="",100,L176)/100))</f>
@@ -24733,7 +24723,7 @@
         <f>IF(H177="","",ROUND(H177*N(I177)/100,2))</f>
         <v/>
       </c>
-      <c r="K177" s="30" t="n"/>
+      <c r="K177" s="38" t="n"/>
       <c r="L177" s="32" t="n"/>
       <c r="M177" s="22">
         <f>IF(H177="","",IF(K177="No",0,H177*N(I177)/100*IF(L177="",100,L177)/100))</f>
@@ -24765,7 +24755,7 @@
         <f>IF(H178="","",ROUND(H178*N(I178)/100,2))</f>
         <v/>
       </c>
-      <c r="K178" s="30" t="n"/>
+      <c r="K178" s="38" t="n"/>
       <c r="L178" s="32" t="n"/>
       <c r="M178" s="22">
         <f>IF(H178="","",IF(K178="No",0,H178*N(I178)/100*IF(L178="",100,L178)/100))</f>
@@ -24797,7 +24787,7 @@
         <f>IF(H179="","",ROUND(H179*N(I179)/100,2))</f>
         <v/>
       </c>
-      <c r="K179" s="30" t="n"/>
+      <c r="K179" s="38" t="n"/>
       <c r="L179" s="32" t="n"/>
       <c r="M179" s="22">
         <f>IF(H179="","",IF(K179="No",0,H179*N(I179)/100*IF(L179="",100,L179)/100))</f>
@@ -24829,7 +24819,7 @@
         <f>IF(H180="","",ROUND(H180*N(I180)/100,2))</f>
         <v/>
       </c>
-      <c r="K180" s="30" t="n"/>
+      <c r="K180" s="38" t="n"/>
       <c r="L180" s="32" t="n"/>
       <c r="M180" s="22">
         <f>IF(H180="","",IF(K180="No",0,H180*N(I180)/100*IF(L180="",100,L180)/100))</f>
@@ -24861,7 +24851,7 @@
         <f>IF(H181="","",ROUND(H181*N(I181)/100,2))</f>
         <v/>
       </c>
-      <c r="K181" s="30" t="n"/>
+      <c r="K181" s="38" t="n"/>
       <c r="L181" s="32" t="n"/>
       <c r="M181" s="22">
         <f>IF(H181="","",IF(K181="No",0,H181*N(I181)/100*IF(L181="",100,L181)/100))</f>
@@ -24893,7 +24883,7 @@
         <f>IF(H182="","",ROUND(H182*N(I182)/100,2))</f>
         <v/>
       </c>
-      <c r="K182" s="30" t="n"/>
+      <c r="K182" s="38" t="n"/>
       <c r="L182" s="32" t="n"/>
       <c r="M182" s="22">
         <f>IF(H182="","",IF(K182="No",0,H182*N(I182)/100*IF(L182="",100,L182)/100))</f>
@@ -24925,7 +24915,7 @@
         <f>IF(H183="","",ROUND(H183*N(I183)/100,2))</f>
         <v/>
       </c>
-      <c r="K183" s="30" t="n"/>
+      <c r="K183" s="38" t="n"/>
       <c r="L183" s="32" t="n"/>
       <c r="M183" s="22">
         <f>IF(H183="","",IF(K183="No",0,H183*N(I183)/100*IF(L183="",100,L183)/100))</f>
@@ -24957,7 +24947,7 @@
         <f>IF(H184="","",ROUND(H184*N(I184)/100,2))</f>
         <v/>
       </c>
-      <c r="K184" s="30" t="n"/>
+      <c r="K184" s="38" t="n"/>
       <c r="L184" s="32" t="n"/>
       <c r="M184" s="22">
         <f>IF(H184="","",IF(K184="No",0,H184*N(I184)/100*IF(L184="",100,L184)/100))</f>
@@ -24989,7 +24979,7 @@
         <f>IF(H185="","",ROUND(H185*N(I185)/100,2))</f>
         <v/>
       </c>
-      <c r="K185" s="30" t="n"/>
+      <c r="K185" s="38" t="n"/>
       <c r="L185" s="32" t="n"/>
       <c r="M185" s="22">
         <f>IF(H185="","",IF(K185="No",0,H185*N(I185)/100*IF(L185="",100,L185)/100))</f>
@@ -25021,7 +25011,7 @@
         <f>IF(H186="","",ROUND(H186*N(I186)/100,2))</f>
         <v/>
       </c>
-      <c r="K186" s="30" t="n"/>
+      <c r="K186" s="38" t="n"/>
       <c r="L186" s="32" t="n"/>
       <c r="M186" s="22">
         <f>IF(H186="","",IF(K186="No",0,H186*N(I186)/100*IF(L186="",100,L186)/100))</f>
@@ -25053,7 +25043,7 @@
         <f>IF(H187="","",ROUND(H187*N(I187)/100,2))</f>
         <v/>
       </c>
-      <c r="K187" s="30" t="n"/>
+      <c r="K187" s="38" t="n"/>
       <c r="L187" s="32" t="n"/>
       <c r="M187" s="22">
         <f>IF(H187="","",IF(K187="No",0,H187*N(I187)/100*IF(L187="",100,L187)/100))</f>
@@ -25085,7 +25075,7 @@
         <f>IF(H188="","",ROUND(H188*N(I188)/100,2))</f>
         <v/>
       </c>
-      <c r="K188" s="30" t="n"/>
+      <c r="K188" s="38" t="n"/>
       <c r="L188" s="32" t="n"/>
       <c r="M188" s="22">
         <f>IF(H188="","",IF(K188="No",0,H188*N(I188)/100*IF(L188="",100,L188)/100))</f>
@@ -25117,7 +25107,7 @@
         <f>IF(H189="","",ROUND(H189*N(I189)/100,2))</f>
         <v/>
       </c>
-      <c r="K189" s="30" t="n"/>
+      <c r="K189" s="38" t="n"/>
       <c r="L189" s="32" t="n"/>
       <c r="M189" s="22">
         <f>IF(H189="","",IF(K189="No",0,H189*N(I189)/100*IF(L189="",100,L189)/100))</f>
@@ -25149,7 +25139,7 @@
         <f>IF(H190="","",ROUND(H190*N(I190)/100,2))</f>
         <v/>
       </c>
-      <c r="K190" s="30" t="n"/>
+      <c r="K190" s="38" t="n"/>
       <c r="L190" s="32" t="n"/>
       <c r="M190" s="22">
         <f>IF(H190="","",IF(K190="No",0,H190*N(I190)/100*IF(L190="",100,L190)/100))</f>
@@ -25181,7 +25171,7 @@
         <f>IF(H191="","",ROUND(H191*N(I191)/100,2))</f>
         <v/>
       </c>
-      <c r="K191" s="30" t="n"/>
+      <c r="K191" s="38" t="n"/>
       <c r="L191" s="32" t="n"/>
       <c r="M191" s="22">
         <f>IF(H191="","",IF(K191="No",0,H191*N(I191)/100*IF(L191="",100,L191)/100))</f>
@@ -25213,7 +25203,7 @@
         <f>IF(H192="","",ROUND(H192*N(I192)/100,2))</f>
         <v/>
       </c>
-      <c r="K192" s="30" t="n"/>
+      <c r="K192" s="38" t="n"/>
       <c r="L192" s="32" t="n"/>
       <c r="M192" s="22">
         <f>IF(H192="","",IF(K192="No",0,H192*N(I192)/100*IF(L192="",100,L192)/100))</f>
@@ -25245,7 +25235,7 @@
         <f>IF(H193="","",ROUND(H193*N(I193)/100,2))</f>
         <v/>
       </c>
-      <c r="K193" s="30" t="n"/>
+      <c r="K193" s="38" t="n"/>
       <c r="L193" s="32" t="n"/>
       <c r="M193" s="22">
         <f>IF(H193="","",IF(K193="No",0,H193*N(I193)/100*IF(L193="",100,L193)/100))</f>
@@ -25277,7 +25267,7 @@
         <f>IF(H194="","",ROUND(H194*N(I194)/100,2))</f>
         <v/>
       </c>
-      <c r="K194" s="30" t="n"/>
+      <c r="K194" s="38" t="n"/>
       <c r="L194" s="32" t="n"/>
       <c r="M194" s="22">
         <f>IF(H194="","",IF(K194="No",0,H194*N(I194)/100*IF(L194="",100,L194)/100))</f>
@@ -25309,7 +25299,7 @@
         <f>IF(H195="","",ROUND(H195*N(I195)/100,2))</f>
         <v/>
       </c>
-      <c r="K195" s="30" t="n"/>
+      <c r="K195" s="38" t="n"/>
       <c r="L195" s="32" t="n"/>
       <c r="M195" s="22">
         <f>IF(H195="","",IF(K195="No",0,H195*N(I195)/100*IF(L195="",100,L195)/100))</f>
@@ -25341,7 +25331,7 @@
         <f>IF(H196="","",ROUND(H196*N(I196)/100,2))</f>
         <v/>
       </c>
-      <c r="K196" s="30" t="n"/>
+      <c r="K196" s="38" t="n"/>
       <c r="L196" s="32" t="n"/>
       <c r="M196" s="22">
         <f>IF(H196="","",IF(K196="No",0,H196*N(I196)/100*IF(L196="",100,L196)/100))</f>
@@ -25373,7 +25363,7 @@
         <f>IF(H197="","",ROUND(H197*N(I197)/100,2))</f>
         <v/>
       </c>
-      <c r="K197" s="30" t="n"/>
+      <c r="K197" s="38" t="n"/>
       <c r="L197" s="32" t="n"/>
       <c r="M197" s="22">
         <f>IF(H197="","",IF(K197="No",0,H197*N(I197)/100*IF(L197="",100,L197)/100))</f>
@@ -25405,7 +25395,7 @@
         <f>IF(H198="","",ROUND(H198*N(I198)/100,2))</f>
         <v/>
       </c>
-      <c r="K198" s="30" t="n"/>
+      <c r="K198" s="38" t="n"/>
       <c r="L198" s="32" t="n"/>
       <c r="M198" s="22">
         <f>IF(H198="","",IF(K198="No",0,H198*N(I198)/100*IF(L198="",100,L198)/100))</f>
@@ -25437,7 +25427,7 @@
         <f>IF(H199="","",ROUND(H199*N(I199)/100,2))</f>
         <v/>
       </c>
-      <c r="K199" s="30" t="n"/>
+      <c r="K199" s="38" t="n"/>
       <c r="L199" s="32" t="n"/>
       <c r="M199" s="22">
         <f>IF(H199="","",IF(K199="No",0,H199*N(I199)/100*IF(L199="",100,L199)/100))</f>
@@ -25469,7 +25459,7 @@
         <f>IF(H200="","",ROUND(H200*N(I200)/100,2))</f>
         <v/>
       </c>
-      <c r="K200" s="30" t="n"/>
+      <c r="K200" s="38" t="n"/>
       <c r="L200" s="32" t="n"/>
       <c r="M200" s="22">
         <f>IF(H200="","",IF(K200="No",0,H200*N(I200)/100*IF(L200="",100,L200)/100))</f>
@@ -25501,7 +25491,7 @@
         <f>IF(H201="","",ROUND(H201*N(I201)/100,2))</f>
         <v/>
       </c>
-      <c r="K201" s="30" t="n"/>
+      <c r="K201" s="38" t="n"/>
       <c r="L201" s="32" t="n"/>
       <c r="M201" s="22">
         <f>IF(H201="","",IF(K201="No",0,H201*N(I201)/100*IF(L201="",100,L201)/100))</f>
@@ -25533,7 +25523,7 @@
         <f>IF(H202="","",ROUND(H202*N(I202)/100,2))</f>
         <v/>
       </c>
-      <c r="K202" s="30" t="n"/>
+      <c r="K202" s="38" t="n"/>
       <c r="L202" s="32" t="n"/>
       <c r="M202" s="22">
         <f>IF(H202="","",IF(K202="No",0,H202*N(I202)/100*IF(L202="",100,L202)/100))</f>
@@ -25565,7 +25555,7 @@
         <f>IF(H203="","",ROUND(H203*N(I203)/100,2))</f>
         <v/>
       </c>
-      <c r="K203" s="30" t="n"/>
+      <c r="K203" s="38" t="n"/>
       <c r="L203" s="32" t="n"/>
       <c r="M203" s="22">
         <f>IF(H203="","",IF(K203="No",0,H203*N(I203)/100*IF(L203="",100,L203)/100))</f>
@@ -25597,7 +25587,7 @@
         <f>IF(H204="","",ROUND(H204*N(I204)/100,2))</f>
         <v/>
       </c>
-      <c r="K204" s="30" t="n"/>
+      <c r="K204" s="38" t="n"/>
       <c r="L204" s="32" t="n"/>
       <c r="M204" s="22">
         <f>IF(H204="","",IF(K204="No",0,H204*N(I204)/100*IF(L204="",100,L204)/100))</f>
@@ -25629,7 +25619,7 @@
         <f>IF(H205="","",ROUND(H205*N(I205)/100,2))</f>
         <v/>
       </c>
-      <c r="K205" s="30" t="n"/>
+      <c r="K205" s="38" t="n"/>
       <c r="L205" s="32" t="n"/>
       <c r="M205" s="22">
         <f>IF(H205="","",IF(K205="No",0,H205*N(I205)/100*IF(L205="",100,L205)/100))</f>
@@ -25661,7 +25651,7 @@
         <f>IF(H206="","",ROUND(H206*N(I206)/100,2))</f>
         <v/>
       </c>
-      <c r="K206" s="30" t="n"/>
+      <c r="K206" s="38" t="n"/>
       <c r="L206" s="32" t="n"/>
       <c r="M206" s="22">
         <f>IF(H206="","",IF(K206="No",0,H206*N(I206)/100*IF(L206="",100,L206)/100))</f>
@@ -25693,7 +25683,7 @@
         <f>IF(H207="","",ROUND(H207*N(I207)/100,2))</f>
         <v/>
       </c>
-      <c r="K207" s="30" t="n"/>
+      <c r="K207" s="38" t="n"/>
       <c r="L207" s="32" t="n"/>
       <c r="M207" s="22">
         <f>IF(H207="","",IF(K207="No",0,H207*N(I207)/100*IF(L207="",100,L207)/100))</f>
@@ -25725,7 +25715,7 @@
         <f>IF(H208="","",ROUND(H208*N(I208)/100,2))</f>
         <v/>
       </c>
-      <c r="K208" s="30" t="n"/>
+      <c r="K208" s="38" t="n"/>
       <c r="L208" s="32" t="n"/>
       <c r="M208" s="22">
         <f>IF(H208="","",IF(K208="No",0,H208*N(I208)/100*IF(L208="",100,L208)/100))</f>
@@ -25757,7 +25747,7 @@
         <f>IF(H209="","",ROUND(H209*N(I209)/100,2))</f>
         <v/>
       </c>
-      <c r="K209" s="30" t="n"/>
+      <c r="K209" s="38" t="n"/>
       <c r="L209" s="32" t="n"/>
       <c r="M209" s="22">
         <f>IF(H209="","",IF(K209="No",0,H209*N(I209)/100*IF(L209="",100,L209)/100))</f>
@@ -25789,7 +25779,7 @@
         <f>IF(H210="","",ROUND(H210*N(I210)/100,2))</f>
         <v/>
       </c>
-      <c r="K210" s="30" t="n"/>
+      <c r="K210" s="38" t="n"/>
       <c r="L210" s="32" t="n"/>
       <c r="M210" s="22">
         <f>IF(H210="","",IF(K210="No",0,H210*N(I210)/100*IF(L210="",100,L210)/100))</f>
@@ -25821,7 +25811,7 @@
         <f>IF(H211="","",ROUND(H211*N(I211)/100,2))</f>
         <v/>
       </c>
-      <c r="K211" s="30" t="n"/>
+      <c r="K211" s="38" t="n"/>
       <c r="L211" s="32" t="n"/>
       <c r="M211" s="22">
         <f>IF(H211="","",IF(K211="No",0,H211*N(I211)/100*IF(L211="",100,L211)/100))</f>
@@ -25853,7 +25843,7 @@
         <f>IF(H212="","",ROUND(H212*N(I212)/100,2))</f>
         <v/>
       </c>
-      <c r="K212" s="30" t="n"/>
+      <c r="K212" s="38" t="n"/>
       <c r="L212" s="32" t="n"/>
       <c r="M212" s="22">
         <f>IF(H212="","",IF(K212="No",0,H212*N(I212)/100*IF(L212="",100,L212)/100))</f>
@@ -25885,7 +25875,7 @@
         <f>IF(H213="","",ROUND(H213*N(I213)/100,2))</f>
         <v/>
       </c>
-      <c r="K213" s="30" t="n"/>
+      <c r="K213" s="38" t="n"/>
       <c r="L213" s="32" t="n"/>
       <c r="M213" s="22">
         <f>IF(H213="","",IF(K213="No",0,H213*N(I213)/100*IF(L213="",100,L213)/100))</f>
@@ -25917,7 +25907,7 @@
         <f>IF(H214="","",ROUND(H214*N(I214)/100,2))</f>
         <v/>
       </c>
-      <c r="K214" s="30" t="n"/>
+      <c r="K214" s="38" t="n"/>
       <c r="L214" s="32" t="n"/>
       <c r="M214" s="22">
         <f>IF(H214="","",IF(K214="No",0,H214*N(I214)/100*IF(L214="",100,L214)/100))</f>
@@ -25949,7 +25939,7 @@
         <f>IF(H215="","",ROUND(H215*N(I215)/100,2))</f>
         <v/>
       </c>
-      <c r="K215" s="30" t="n"/>
+      <c r="K215" s="38" t="n"/>
       <c r="L215" s="32" t="n"/>
       <c r="M215" s="22">
         <f>IF(H215="","",IF(K215="No",0,H215*N(I215)/100*IF(L215="",100,L215)/100))</f>
@@ -25981,7 +25971,7 @@
         <f>IF(H216="","",ROUND(H216*N(I216)/100,2))</f>
         <v/>
       </c>
-      <c r="K216" s="30" t="n"/>
+      <c r="K216" s="38" t="n"/>
       <c r="L216" s="32" t="n"/>
       <c r="M216" s="22">
         <f>IF(H216="","",IF(K216="No",0,H216*N(I216)/100*IF(L216="",100,L216)/100))</f>
@@ -26013,7 +26003,7 @@
         <f>IF(H217="","",ROUND(H217*N(I217)/100,2))</f>
         <v/>
       </c>
-      <c r="K217" s="30" t="n"/>
+      <c r="K217" s="38" t="n"/>
       <c r="L217" s="32" t="n"/>
       <c r="M217" s="22">
         <f>IF(H217="","",IF(K217="No",0,H217*N(I217)/100*IF(L217="",100,L217)/100))</f>
@@ -26045,7 +26035,7 @@
         <f>IF(H218="","",ROUND(H218*N(I218)/100,2))</f>
         <v/>
       </c>
-      <c r="K218" s="30" t="n"/>
+      <c r="K218" s="38" t="n"/>
       <c r="L218" s="32" t="n"/>
       <c r="M218" s="22">
         <f>IF(H218="","",IF(K218="No",0,H218*N(I218)/100*IF(L218="",100,L218)/100))</f>
@@ -26077,7 +26067,7 @@
         <f>IF(H219="","",ROUND(H219*N(I219)/100,2))</f>
         <v/>
       </c>
-      <c r="K219" s="30" t="n"/>
+      <c r="K219" s="38" t="n"/>
       <c r="L219" s="32" t="n"/>
       <c r="M219" s="22">
         <f>IF(H219="","",IF(K219="No",0,H219*N(I219)/100*IF(L219="",100,L219)/100))</f>
@@ -26109,7 +26099,7 @@
         <f>IF(H220="","",ROUND(H220*N(I220)/100,2))</f>
         <v/>
       </c>
-      <c r="K220" s="30" t="n"/>
+      <c r="K220" s="38" t="n"/>
       <c r="L220" s="32" t="n"/>
       <c r="M220" s="22">
         <f>IF(H220="","",IF(K220="No",0,H220*N(I220)/100*IF(L220="",100,L220)/100))</f>
@@ -26141,7 +26131,7 @@
         <f>IF(H221="","",ROUND(H221*N(I221)/100,2))</f>
         <v/>
       </c>
-      <c r="K221" s="30" t="n"/>
+      <c r="K221" s="38" t="n"/>
       <c r="L221" s="32" t="n"/>
       <c r="M221" s="22">
         <f>IF(H221="","",IF(K221="No",0,H221*N(I221)/100*IF(L221="",100,L221)/100))</f>
@@ -26173,7 +26163,7 @@
         <f>IF(H222="","",ROUND(H222*N(I222)/100,2))</f>
         <v/>
       </c>
-      <c r="K222" s="30" t="n"/>
+      <c r="K222" s="38" t="n"/>
       <c r="L222" s="32" t="n"/>
       <c r="M222" s="22">
         <f>IF(H222="","",IF(K222="No",0,H222*N(I222)/100*IF(L222="",100,L222)/100))</f>
@@ -26205,7 +26195,7 @@
         <f>IF(H223="","",ROUND(H223*N(I223)/100,2))</f>
         <v/>
       </c>
-      <c r="K223" s="30" t="n"/>
+      <c r="K223" s="38" t="n"/>
       <c r="L223" s="32" t="n"/>
       <c r="M223" s="22">
         <f>IF(H223="","",IF(K223="No",0,H223*N(I223)/100*IF(L223="",100,L223)/100))</f>
@@ -26237,7 +26227,7 @@
         <f>IF(H224="","",ROUND(H224*N(I224)/100,2))</f>
         <v/>
       </c>
-      <c r="K224" s="30" t="n"/>
+      <c r="K224" s="38" t="n"/>
       <c r="L224" s="32" t="n"/>
       <c r="M224" s="22">
         <f>IF(H224="","",IF(K224="No",0,H224*N(I224)/100*IF(L224="",100,L224)/100))</f>
@@ -26269,7 +26259,7 @@
         <f>IF(H225="","",ROUND(H225*N(I225)/100,2))</f>
         <v/>
       </c>
-      <c r="K225" s="30" t="n"/>
+      <c r="K225" s="38" t="n"/>
       <c r="L225" s="32" t="n"/>
       <c r="M225" s="22">
         <f>IF(H225="","",IF(K225="No",0,H225*N(I225)/100*IF(L225="",100,L225)/100))</f>
@@ -26301,7 +26291,7 @@
         <f>IF(H226="","",ROUND(H226*N(I226)/100,2))</f>
         <v/>
       </c>
-      <c r="K226" s="30" t="n"/>
+      <c r="K226" s="38" t="n"/>
       <c r="L226" s="32" t="n"/>
       <c r="M226" s="22">
         <f>IF(H226="","",IF(K226="No",0,H226*N(I226)/100*IF(L226="",100,L226)/100))</f>
@@ -26333,7 +26323,7 @@
         <f>IF(H227="","",ROUND(H227*N(I227)/100,2))</f>
         <v/>
       </c>
-      <c r="K227" s="30" t="n"/>
+      <c r="K227" s="38" t="n"/>
       <c r="L227" s="32" t="n"/>
       <c r="M227" s="22">
         <f>IF(H227="","",IF(K227="No",0,H227*N(I227)/100*IF(L227="",100,L227)/100))</f>
@@ -26365,7 +26355,7 @@
         <f>IF(H228="","",ROUND(H228*N(I228)/100,2))</f>
         <v/>
       </c>
-      <c r="K228" s="30" t="n"/>
+      <c r="K228" s="38" t="n"/>
       <c r="L228" s="32" t="n"/>
       <c r="M228" s="22">
         <f>IF(H228="","",IF(K228="No",0,H228*N(I228)/100*IF(L228="",100,L228)/100))</f>
@@ -26397,7 +26387,7 @@
         <f>IF(H229="","",ROUND(H229*N(I229)/100,2))</f>
         <v/>
       </c>
-      <c r="K229" s="30" t="n"/>
+      <c r="K229" s="38" t="n"/>
       <c r="L229" s="32" t="n"/>
       <c r="M229" s="22">
         <f>IF(H229="","",IF(K229="No",0,H229*N(I229)/100*IF(L229="",100,L229)/100))</f>
@@ -26429,7 +26419,7 @@
         <f>IF(H230="","",ROUND(H230*N(I230)/100,2))</f>
         <v/>
       </c>
-      <c r="K230" s="30" t="n"/>
+      <c r="K230" s="38" t="n"/>
       <c r="L230" s="32" t="n"/>
       <c r="M230" s="22">
         <f>IF(H230="","",IF(K230="No",0,H230*N(I230)/100*IF(L230="",100,L230)/100))</f>
@@ -26461,7 +26451,7 @@
         <f>IF(H231="","",ROUND(H231*N(I231)/100,2))</f>
         <v/>
       </c>
-      <c r="K231" s="30" t="n"/>
+      <c r="K231" s="38" t="n"/>
       <c r="L231" s="32" t="n"/>
       <c r="M231" s="22">
         <f>IF(H231="","",IF(K231="No",0,H231*N(I231)/100*IF(L231="",100,L231)/100))</f>
@@ -26493,7 +26483,7 @@
         <f>IF(H232="","",ROUND(H232*N(I232)/100,2))</f>
         <v/>
       </c>
-      <c r="K232" s="30" t="n"/>
+      <c r="K232" s="38" t="n"/>
       <c r="L232" s="32" t="n"/>
       <c r="M232" s="22">
         <f>IF(H232="","",IF(K232="No",0,H232*N(I232)/100*IF(L232="",100,L232)/100))</f>
@@ -26525,7 +26515,7 @@
         <f>IF(H233="","",ROUND(H233*N(I233)/100,2))</f>
         <v/>
       </c>
-      <c r="K233" s="30" t="n"/>
+      <c r="K233" s="38" t="n"/>
       <c r="L233" s="32" t="n"/>
       <c r="M233" s="22">
         <f>IF(H233="","",IF(K233="No",0,H233*N(I233)/100*IF(L233="",100,L233)/100))</f>
@@ -26557,7 +26547,7 @@
         <f>IF(H234="","",ROUND(H234*N(I234)/100,2))</f>
         <v/>
       </c>
-      <c r="K234" s="30" t="n"/>
+      <c r="K234" s="38" t="n"/>
       <c r="L234" s="32" t="n"/>
       <c r="M234" s="22">
         <f>IF(H234="","",IF(K234="No",0,H234*N(I234)/100*IF(L234="",100,L234)/100))</f>
@@ -26589,7 +26579,7 @@
         <f>IF(H235="","",ROUND(H235*N(I235)/100,2))</f>
         <v/>
       </c>
-      <c r="K235" s="30" t="n"/>
+      <c r="K235" s="38" t="n"/>
       <c r="L235" s="32" t="n"/>
       <c r="M235" s="22">
         <f>IF(H235="","",IF(K235="No",0,H235*N(I235)/100*IF(L235="",100,L235)/100))</f>
@@ -26621,7 +26611,7 @@
         <f>IF(H236="","",ROUND(H236*N(I236)/100,2))</f>
         <v/>
       </c>
-      <c r="K236" s="30" t="n"/>
+      <c r="K236" s="38" t="n"/>
       <c r="L236" s="32" t="n"/>
       <c r="M236" s="22">
         <f>IF(H236="","",IF(K236="No",0,H236*N(I236)/100*IF(L236="",100,L236)/100))</f>
@@ -26653,7 +26643,7 @@
         <f>IF(H237="","",ROUND(H237*N(I237)/100,2))</f>
         <v/>
       </c>
-      <c r="K237" s="30" t="n"/>
+      <c r="K237" s="38" t="n"/>
       <c r="L237" s="32" t="n"/>
       <c r="M237" s="22">
         <f>IF(H237="","",IF(K237="No",0,H237*N(I237)/100*IF(L237="",100,L237)/100))</f>
@@ -26685,7 +26675,7 @@
         <f>IF(H238="","",ROUND(H238*N(I238)/100,2))</f>
         <v/>
       </c>
-      <c r="K238" s="30" t="n"/>
+      <c r="K238" s="38" t="n"/>
       <c r="L238" s="32" t="n"/>
       <c r="M238" s="22">
         <f>IF(H238="","",IF(K238="No",0,H238*N(I238)/100*IF(L238="",100,L238)/100))</f>
@@ -26717,7 +26707,7 @@
         <f>IF(H239="","",ROUND(H239*N(I239)/100,2))</f>
         <v/>
       </c>
-      <c r="K239" s="30" t="n"/>
+      <c r="K239" s="38" t="n"/>
       <c r="L239" s="32" t="n"/>
       <c r="M239" s="22">
         <f>IF(H239="","",IF(K239="No",0,H239*N(I239)/100*IF(L239="",100,L239)/100))</f>
@@ -26749,7 +26739,7 @@
         <f>IF(H240="","",ROUND(H240*N(I240)/100,2))</f>
         <v/>
       </c>
-      <c r="K240" s="30" t="n"/>
+      <c r="K240" s="38" t="n"/>
       <c r="L240" s="32" t="n"/>
       <c r="M240" s="22">
         <f>IF(H240="","",IF(K240="No",0,H240*N(I240)/100*IF(L240="",100,L240)/100))</f>
@@ -26781,7 +26771,7 @@
         <f>IF(H241="","",ROUND(H241*N(I241)/100,2))</f>
         <v/>
       </c>
-      <c r="K241" s="30" t="n"/>
+      <c r="K241" s="38" t="n"/>
       <c r="L241" s="32" t="n"/>
       <c r="M241" s="22">
         <f>IF(H241="","",IF(K241="No",0,H241*N(I241)/100*IF(L241="",100,L241)/100))</f>
@@ -26813,7 +26803,7 @@
         <f>IF(H242="","",ROUND(H242*N(I242)/100,2))</f>
         <v/>
       </c>
-      <c r="K242" s="30" t="n"/>
+      <c r="K242" s="38" t="n"/>
       <c r="L242" s="32" t="n"/>
       <c r="M242" s="22">
         <f>IF(H242="","",IF(K242="No",0,H242*N(I242)/100*IF(L242="",100,L242)/100))</f>
@@ -26845,7 +26835,7 @@
         <f>IF(H243="","",ROUND(H243*N(I243)/100,2))</f>
         <v/>
       </c>
-      <c r="K243" s="30" t="n"/>
+      <c r="K243" s="38" t="n"/>
       <c r="L243" s="32" t="n"/>
       <c r="M243" s="22">
         <f>IF(H243="","",IF(K243="No",0,H243*N(I243)/100*IF(L243="",100,L243)/100))</f>
@@ -26877,7 +26867,7 @@
         <f>IF(H244="","",ROUND(H244*N(I244)/100,2))</f>
         <v/>
       </c>
-      <c r="K244" s="30" t="n"/>
+      <c r="K244" s="38" t="n"/>
       <c r="L244" s="32" t="n"/>
       <c r="M244" s="22">
         <f>IF(H244="","",IF(K244="No",0,H244*N(I244)/100*IF(L244="",100,L244)/100))</f>
@@ -26909,7 +26899,7 @@
         <f>IF(H245="","",ROUND(H245*N(I245)/100,2))</f>
         <v/>
       </c>
-      <c r="K245" s="30" t="n"/>
+      <c r="K245" s="38" t="n"/>
       <c r="L245" s="32" t="n"/>
       <c r="M245" s="22">
         <f>IF(H245="","",IF(K245="No",0,H245*N(I245)/100*IF(L245="",100,L245)/100))</f>
@@ -26941,7 +26931,7 @@
         <f>IF(H246="","",ROUND(H246*N(I246)/100,2))</f>
         <v/>
       </c>
-      <c r="K246" s="30" t="n"/>
+      <c r="K246" s="38" t="n"/>
       <c r="L246" s="32" t="n"/>
       <c r="M246" s="22">
         <f>IF(H246="","",IF(K246="No",0,H246*N(I246)/100*IF(L246="",100,L246)/100))</f>
@@ -26973,7 +26963,7 @@
         <f>IF(H247="","",ROUND(H247*N(I247)/100,2))</f>
         <v/>
       </c>
-      <c r="K247" s="30" t="n"/>
+      <c r="K247" s="38" t="n"/>
       <c r="L247" s="32" t="n"/>
       <c r="M247" s="22">
         <f>IF(H247="","",IF(K247="No",0,H247*N(I247)/100*IF(L247="",100,L247)/100))</f>
@@ -27005,7 +26995,7 @@
         <f>IF(H248="","",ROUND(H248*N(I248)/100,2))</f>
         <v/>
       </c>
-      <c r="K248" s="30" t="n"/>
+      <c r="K248" s="38" t="n"/>
       <c r="L248" s="32" t="n"/>
       <c r="M248" s="22">
         <f>IF(H248="","",IF(K248="No",0,H248*N(I248)/100*IF(L248="",100,L248)/100))</f>
@@ -27037,7 +27027,7 @@
         <f>IF(H249="","",ROUND(H249*N(I249)/100,2))</f>
         <v/>
       </c>
-      <c r="K249" s="30" t="n"/>
+      <c r="K249" s="38" t="n"/>
       <c r="L249" s="32" t="n"/>
       <c r="M249" s="22">
         <f>IF(H249="","",IF(K249="No",0,H249*N(I249)/100*IF(L249="",100,L249)/100))</f>
@@ -27069,7 +27059,7 @@
         <f>IF(H250="","",ROUND(H250*N(I250)/100,2))</f>
         <v/>
       </c>
-      <c r="K250" s="30" t="n"/>
+      <c r="K250" s="38" t="n"/>
       <c r="L250" s="32" t="n"/>
       <c r="M250" s="22">
         <f>IF(H250="","",IF(K250="No",0,H250*N(I250)/100*IF(L250="",100,L250)/100))</f>
@@ -27101,7 +27091,7 @@
         <f>IF(H251="","",ROUND(H251*N(I251)/100,2))</f>
         <v/>
       </c>
-      <c r="K251" s="30" t="n"/>
+      <c r="K251" s="38" t="n"/>
       <c r="L251" s="32" t="n"/>
       <c r="M251" s="22">
         <f>IF(H251="","",IF(K251="No",0,H251*N(I251)/100*IF(L251="",100,L251)/100))</f>
@@ -27133,7 +27123,7 @@
         <f>IF(H252="","",ROUND(H252*N(I252)/100,2))</f>
         <v/>
       </c>
-      <c r="K252" s="30" t="n"/>
+      <c r="K252" s="38" t="n"/>
       <c r="L252" s="32" t="n"/>
       <c r="M252" s="22">
         <f>IF(H252="","",IF(K252="No",0,H252*N(I252)/100*IF(L252="",100,L252)/100))</f>
@@ -27165,7 +27155,7 @@
         <f>IF(H253="","",ROUND(H253*N(I253)/100,2))</f>
         <v/>
       </c>
-      <c r="K253" s="30" t="n"/>
+      <c r="K253" s="38" t="n"/>
       <c r="L253" s="32" t="n"/>
       <c r="M253" s="22">
         <f>IF(H253="","",IF(K253="No",0,H253*N(I253)/100*IF(L253="",100,L253)/100))</f>
@@ -27197,7 +27187,7 @@
         <f>IF(H254="","",ROUND(H254*N(I254)/100,2))</f>
         <v/>
       </c>
-      <c r="K254" s="30" t="n"/>
+      <c r="K254" s="38" t="n"/>
       <c r="L254" s="32" t="n"/>
       <c r="M254" s="22">
         <f>IF(H254="","",IF(K254="No",0,H254*N(I254)/100*IF(L254="",100,L254)/100))</f>
@@ -27229,7 +27219,7 @@
         <f>IF(H255="","",ROUND(H255*N(I255)/100,2))</f>
         <v/>
       </c>
-      <c r="K255" s="30" t="n"/>
+      <c r="K255" s="38" t="n"/>
       <c r="L255" s="32" t="n"/>
       <c r="M255" s="22">
         <f>IF(H255="","",IF(K255="No",0,H255*N(I255)/100*IF(L255="",100,L255)/100))</f>
@@ -27261,7 +27251,7 @@
         <f>IF(H256="","",ROUND(H256*N(I256)/100,2))</f>
         <v/>
       </c>
-      <c r="K256" s="30" t="n"/>
+      <c r="K256" s="38" t="n"/>
       <c r="L256" s="32" t="n"/>
       <c r="M256" s="22">
         <f>IF(H256="","",IF(K256="No",0,H256*N(I256)/100*IF(L256="",100,L256)/100))</f>
@@ -27293,7 +27283,7 @@
         <f>IF(H257="","",ROUND(H257*N(I257)/100,2))</f>
         <v/>
       </c>
-      <c r="K257" s="30" t="n"/>
+      <c r="K257" s="38" t="n"/>
       <c r="L257" s="32" t="n"/>
       <c r="M257" s="22">
         <f>IF(H257="","",IF(K257="No",0,H257*N(I257)/100*IF(L257="",100,L257)/100))</f>
@@ -27325,7 +27315,7 @@
         <f>IF(H258="","",ROUND(H258*N(I258)/100,2))</f>
         <v/>
       </c>
-      <c r="K258" s="30" t="n"/>
+      <c r="K258" s="38" t="n"/>
       <c r="L258" s="32" t="n"/>
       <c r="M258" s="22">
         <f>IF(H258="","",IF(K258="No",0,H258*N(I258)/100*IF(L258="",100,L258)/100))</f>
@@ -27357,7 +27347,7 @@
         <f>IF(H259="","",ROUND(H259*N(I259)/100,2))</f>
         <v/>
       </c>
-      <c r="K259" s="30" t="n"/>
+      <c r="K259" s="38" t="n"/>
       <c r="L259" s="32" t="n"/>
       <c r="M259" s="22">
         <f>IF(H259="","",IF(K259="No",0,H259*N(I259)/100*IF(L259="",100,L259)/100))</f>
@@ -27389,7 +27379,7 @@
         <f>IF(H260="","",ROUND(H260*N(I260)/100,2))</f>
         <v/>
       </c>
-      <c r="K260" s="30" t="n"/>
+      <c r="K260" s="38" t="n"/>
       <c r="L260" s="32" t="n"/>
       <c r="M260" s="22">
         <f>IF(H260="","",IF(K260="No",0,H260*N(I260)/100*IF(L260="",100,L260)/100))</f>
@@ -27421,7 +27411,7 @@
         <f>IF(H261="","",ROUND(H261*N(I261)/100,2))</f>
         <v/>
       </c>
-      <c r="K261" s="30" t="n"/>
+      <c r="K261" s="38" t="n"/>
       <c r="L261" s="32" t="n"/>
       <c r="M261" s="22">
         <f>IF(H261="","",IF(K261="No",0,H261*N(I261)/100*IF(L261="",100,L261)/100))</f>
@@ -27453,7 +27443,7 @@
         <f>IF(H262="","",ROUND(H262*N(I262)/100,2))</f>
         <v/>
       </c>
-      <c r="K262" s="30" t="n"/>
+      <c r="K262" s="38" t="n"/>
       <c r="L262" s="32" t="n"/>
       <c r="M262" s="22">
         <f>IF(H262="","",IF(K262="No",0,H262*N(I262)/100*IF(L262="",100,L262)/100))</f>
@@ -27485,7 +27475,7 @@
         <f>IF(H263="","",ROUND(H263*N(I263)/100,2))</f>
         <v/>
       </c>
-      <c r="K263" s="30" t="n"/>
+      <c r="K263" s="38" t="n"/>
       <c r="L263" s="32" t="n"/>
       <c r="M263" s="22">
         <f>IF(H263="","",IF(K263="No",0,H263*N(I263)/100*IF(L263="",100,L263)/100))</f>
@@ -27517,7 +27507,7 @@
         <f>IF(H264="","",ROUND(H264*N(I264)/100,2))</f>
         <v/>
       </c>
-      <c r="K264" s="30" t="n"/>
+      <c r="K264" s="38" t="n"/>
       <c r="L264" s="32" t="n"/>
       <c r="M264" s="22">
         <f>IF(H264="","",IF(K264="No",0,H264*N(I264)/100*IF(L264="",100,L264)/100))</f>
@@ -27549,7 +27539,7 @@
         <f>IF(H265="","",ROUND(H265*N(I265)/100,2))</f>
         <v/>
       </c>
-      <c r="K265" s="30" t="n"/>
+      <c r="K265" s="38" t="n"/>
       <c r="L265" s="32" t="n"/>
       <c r="M265" s="22">
         <f>IF(H265="","",IF(K265="No",0,H265*N(I265)/100*IF(L265="",100,L265)/100))</f>
@@ -27581,7 +27571,7 @@
         <f>IF(H266="","",ROUND(H266*N(I266)/100,2))</f>
         <v/>
       </c>
-      <c r="K266" s="30" t="n"/>
+      <c r="K266" s="38" t="n"/>
       <c r="L266" s="32" t="n"/>
       <c r="M266" s="22">
         <f>IF(H266="","",IF(K266="No",0,H266*N(I266)/100*IF(L266="",100,L266)/100))</f>
@@ -27613,7 +27603,7 @@
         <f>IF(H267="","",ROUND(H267*N(I267)/100,2))</f>
         <v/>
       </c>
-      <c r="K267" s="30" t="n"/>
+      <c r="K267" s="38" t="n"/>
       <c r="L267" s="32" t="n"/>
       <c r="M267" s="22">
         <f>IF(H267="","",IF(K267="No",0,H267*N(I267)/100*IF(L267="",100,L267)/100))</f>
@@ -27645,7 +27635,7 @@
         <f>IF(H268="","",ROUND(H268*N(I268)/100,2))</f>
         <v/>
       </c>
-      <c r="K268" s="30" t="n"/>
+      <c r="K268" s="38" t="n"/>
       <c r="L268" s="32" t="n"/>
       <c r="M268" s="22">
         <f>IF(H268="","",IF(K268="No",0,H268*N(I268)/100*IF(L268="",100,L268)/100))</f>
@@ -27677,7 +27667,7 @@
         <f>IF(H269="","",ROUND(H269*N(I269)/100,2))</f>
         <v/>
       </c>
-      <c r="K269" s="30" t="n"/>
+      <c r="K269" s="38" t="n"/>
       <c r="L269" s="32" t="n"/>
       <c r="M269" s="22">
         <f>IF(H269="","",IF(K269="No",0,H269*N(I269)/100*IF(L269="",100,L269)/100))</f>
@@ -27709,7 +27699,7 @@
         <f>IF(H270="","",ROUND(H270*N(I270)/100,2))</f>
         <v/>
       </c>
-      <c r="K270" s="30" t="n"/>
+      <c r="K270" s="38" t="n"/>
       <c r="L270" s="32" t="n"/>
       <c r="M270" s="22">
         <f>IF(H270="","",IF(K270="No",0,H270*N(I270)/100*IF(L270="",100,L270)/100))</f>
@@ -27741,7 +27731,7 @@
         <f>IF(H271="","",ROUND(H271*N(I271)/100,2))</f>
         <v/>
       </c>
-      <c r="K271" s="30" t="n"/>
+      <c r="K271" s="38" t="n"/>
       <c r="L271" s="32" t="n"/>
       <c r="M271" s="22">
         <f>IF(H271="","",IF(K271="No",0,H271*N(I271)/100*IF(L271="",100,L271)/100))</f>
@@ -27773,7 +27763,7 @@
         <f>IF(H272="","",ROUND(H272*N(I272)/100,2))</f>
         <v/>
       </c>
-      <c r="K272" s="30" t="n"/>
+      <c r="K272" s="38" t="n"/>
       <c r="L272" s="32" t="n"/>
       <c r="M272" s="22">
         <f>IF(H272="","",IF(K272="No",0,H272*N(I272)/100*IF(L272="",100,L272)/100))</f>
@@ -27805,7 +27795,7 @@
         <f>IF(H273="","",ROUND(H273*N(I273)/100,2))</f>
         <v/>
       </c>
-      <c r="K273" s="30" t="n"/>
+      <c r="K273" s="38" t="n"/>
       <c r="L273" s="32" t="n"/>
       <c r="M273" s="22">
         <f>IF(H273="","",IF(K273="No",0,H273*N(I273)/100*IF(L273="",100,L273)/100))</f>
@@ -27837,7 +27827,7 @@
         <f>IF(H274="","",ROUND(H274*N(I274)/100,2))</f>
         <v/>
       </c>
-      <c r="K274" s="30" t="n"/>
+      <c r="K274" s="38" t="n"/>
       <c r="L274" s="32" t="n"/>
       <c r="M274" s="22">
         <f>IF(H274="","",IF(K274="No",0,H274*N(I274)/100*IF(L274="",100,L274)/100))</f>
@@ -27869,7 +27859,7 @@
         <f>IF(H275="","",ROUND(H275*N(I275)/100,2))</f>
         <v/>
       </c>
-      <c r="K275" s="30" t="n"/>
+      <c r="K275" s="38" t="n"/>
       <c r="L275" s="32" t="n"/>
       <c r="M275" s="22">
         <f>IF(H275="","",IF(K275="No",0,H275*N(I275)/100*IF(L275="",100,L275)/100))</f>
@@ -27901,7 +27891,7 @@
         <f>IF(H276="","",ROUND(H276*N(I276)/100,2))</f>
         <v/>
       </c>
-      <c r="K276" s="30" t="n"/>
+      <c r="K276" s="38" t="n"/>
       <c r="L276" s="32" t="n"/>
       <c r="M276" s="22">
         <f>IF(H276="","",IF(K276="No",0,H276*N(I276)/100*IF(L276="",100,L276)/100))</f>
@@ -27933,7 +27923,7 @@
         <f>IF(H277="","",ROUND(H277*N(I277)/100,2))</f>
         <v/>
       </c>
-      <c r="K277" s="30" t="n"/>
+      <c r="K277" s="38" t="n"/>
       <c r="L277" s="32" t="n"/>
       <c r="M277" s="22">
         <f>IF(H277="","",IF(K277="No",0,H277*N(I277)/100*IF(L277="",100,L277)/100))</f>
@@ -27965,7 +27955,7 @@
         <f>IF(H278="","",ROUND(H278*N(I278)/100,2))</f>
         <v/>
       </c>
-      <c r="K278" s="30" t="n"/>
+      <c r="K278" s="38" t="n"/>
       <c r="L278" s="32" t="n"/>
       <c r="M278" s="22">
         <f>IF(H278="","",IF(K278="No",0,H278*N(I278)/100*IF(L278="",100,L278)/100))</f>
@@ -27997,7 +27987,7 @@
         <f>IF(H279="","",ROUND(H279*N(I279)/100,2))</f>
         <v/>
       </c>
-      <c r="K279" s="30" t="n"/>
+      <c r="K279" s="38" t="n"/>
       <c r="L279" s="32" t="n"/>
       <c r="M279" s="22">
         <f>IF(H279="","",IF(K279="No",0,H279*N(I279)/100*IF(L279="",100,L279)/100))</f>
@@ -28029,7 +28019,7 @@
         <f>IF(H280="","",ROUND(H280*N(I280)/100,2))</f>
         <v/>
       </c>
-      <c r="K280" s="30" t="n"/>
+      <c r="K280" s="38" t="n"/>
       <c r="L280" s="32" t="n"/>
       <c r="M280" s="22">
         <f>IF(H280="","",IF(K280="No",0,H280*N(I280)/100*IF(L280="",100,L280)/100))</f>
@@ -28061,7 +28051,7 @@
         <f>IF(H281="","",ROUND(H281*N(I281)/100,2))</f>
         <v/>
       </c>
-      <c r="K281" s="30" t="n"/>
+      <c r="K281" s="38" t="n"/>
       <c r="L281" s="32" t="n"/>
       <c r="M281" s="22">
         <f>IF(H281="","",IF(K281="No",0,H281*N(I281)/100*IF(L281="",100,L281)/100))</f>
@@ -28093,7 +28083,7 @@
         <f>IF(H282="","",ROUND(H282*N(I282)/100,2))</f>
         <v/>
       </c>
-      <c r="K282" s="30" t="n"/>
+      <c r="K282" s="38" t="n"/>
       <c r="L282" s="32" t="n"/>
       <c r="M282" s="22">
         <f>IF(H282="","",IF(K282="No",0,H282*N(I282)/100*IF(L282="",100,L282)/100))</f>
@@ -28125,7 +28115,7 @@
         <f>IF(H283="","",ROUND(H283*N(I283)/100,2))</f>
         <v/>
       </c>
-      <c r="K283" s="30" t="n"/>
+      <c r="K283" s="38" t="n"/>
       <c r="L283" s="32" t="n"/>
       <c r="M283" s="22">
         <f>IF(H283="","",IF(K283="No",0,H283*N(I283)/100*IF(L283="",100,L283)/100))</f>
@@ -28157,7 +28147,7 @@
         <f>IF(H284="","",ROUND(H284*N(I284)/100,2))</f>
         <v/>
       </c>
-      <c r="K284" s="30" t="n"/>
+      <c r="K284" s="38" t="n"/>
       <c r="L284" s="32" t="n"/>
       <c r="M284" s="22">
         <f>IF(H284="","",IF(K284="No",0,H284*N(I284)/100*IF(L284="",100,L284)/100))</f>
@@ -28189,7 +28179,7 @@
         <f>IF(H285="","",ROUND(H285*N(I285)/100,2))</f>
         <v/>
       </c>
-      <c r="K285" s="30" t="n"/>
+      <c r="K285" s="38" t="n"/>
       <c r="L285" s="32" t="n"/>
       <c r="M285" s="22">
         <f>IF(H285="","",IF(K285="No",0,H285*N(I285)/100*IF(L285="",100,L285)/100))</f>
@@ -28221,7 +28211,7 @@
         <f>IF(H286="","",ROUND(H286*N(I286)/100,2))</f>
         <v/>
       </c>
-      <c r="K286" s="30" t="n"/>
+      <c r="K286" s="38" t="n"/>
       <c r="L286" s="32" t="n"/>
       <c r="M286" s="22">
         <f>IF(H286="","",IF(K286="No",0,H286*N(I286)/100*IF(L286="",100,L286)/100))</f>
@@ -28253,7 +28243,7 @@
         <f>IF(H287="","",ROUND(H287*N(I287)/100,2))</f>
         <v/>
       </c>
-      <c r="K287" s="30" t="n"/>
+      <c r="K287" s="38" t="n"/>
       <c r="L287" s="32" t="n"/>
       <c r="M287" s="22">
         <f>IF(H287="","",IF(K287="No",0,H287*N(I287)/100*IF(L287="",100,L287)/100))</f>
@@ -28285,7 +28275,7 @@
         <f>IF(H288="","",ROUND(H288*N(I288)/100,2))</f>
         <v/>
       </c>
-      <c r="K288" s="30" t="n"/>
+      <c r="K288" s="38" t="n"/>
       <c r="L288" s="32" t="n"/>
       <c r="M288" s="22">
         <f>IF(H288="","",IF(K288="No",0,H288*N(I288)/100*IF(L288="",100,L288)/100))</f>
@@ -28317,7 +28307,7 @@
         <f>IF(H289="","",ROUND(H289*N(I289)/100,2))</f>
         <v/>
       </c>
-      <c r="K289" s="30" t="n"/>
+      <c r="K289" s="38" t="n"/>
       <c r="L289" s="32" t="n"/>
       <c r="M289" s="22">
         <f>IF(H289="","",IF(K289="No",0,H289*N(I289)/100*IF(L289="",100,L289)/100))</f>
@@ -28349,7 +28339,7 @@
         <f>IF(H290="","",ROUND(H290*N(I290)/100,2))</f>
         <v/>
       </c>
-      <c r="K290" s="30" t="n"/>
+      <c r="K290" s="38" t="n"/>
       <c r="L290" s="32" t="n"/>
       <c r="M290" s="22">
         <f>IF(H290="","",IF(K290="No",0,H290*N(I290)/100*IF(L290="",100,L290)/100))</f>
@@ -28381,7 +28371,7 @@
         <f>IF(H291="","",ROUND(H291*N(I291)/100,2))</f>
         <v/>
       </c>
-      <c r="K291" s="30" t="n"/>
+      <c r="K291" s="38" t="n"/>
       <c r="L291" s="32" t="n"/>
       <c r="M291" s="22">
         <f>IF(H291="","",IF(K291="No",0,H291*N(I291)/100*IF(L291="",100,L291)/100))</f>
@@ -28413,7 +28403,7 @@
         <f>IF(H292="","",ROUND(H292*N(I292)/100,2))</f>
         <v/>
       </c>
-      <c r="K292" s="30" t="n"/>
+      <c r="K292" s="38" t="n"/>
       <c r="L292" s="32" t="n"/>
       <c r="M292" s="22">
         <f>IF(H292="","",IF(K292="No",0,H292*N(I292)/100*IF(L292="",100,L292)/100))</f>
@@ -28445,7 +28435,7 @@
         <f>IF(H293="","",ROUND(H293*N(I293)/100,2))</f>
         <v/>
       </c>
-      <c r="K293" s="30" t="n"/>
+      <c r="K293" s="38" t="n"/>
       <c r="L293" s="32" t="n"/>
       <c r="M293" s="22">
         <f>IF(H293="","",IF(K293="No",0,H293*N(I293)/100*IF(L293="",100,L293)/100))</f>
@@ -28477,7 +28467,7 @@
         <f>IF(H294="","",ROUND(H294*N(I294)/100,2))</f>
         <v/>
       </c>
-      <c r="K294" s="30" t="n"/>
+      <c r="K294" s="38" t="n"/>
       <c r="L294" s="32" t="n"/>
       <c r="M294" s="22">
         <f>IF(H294="","",IF(K294="No",0,H294*N(I294)/100*IF(L294="",100,L294)/100))</f>
@@ -28509,7 +28499,7 @@
         <f>IF(H295="","",ROUND(H295*N(I295)/100,2))</f>
         <v/>
       </c>
-      <c r="K295" s="30" t="n"/>
+      <c r="K295" s="38" t="n"/>
       <c r="L295" s="32" t="n"/>
       <c r="M295" s="22">
         <f>IF(H295="","",IF(K295="No",0,H295*N(I295)/100*IF(L295="",100,L295)/100))</f>
@@ -28541,7 +28531,7 @@
         <f>IF(H296="","",ROUND(H296*N(I296)/100,2))</f>
         <v/>
       </c>
-      <c r="K296" s="30" t="n"/>
+      <c r="K296" s="38" t="n"/>
       <c r="L296" s="32" t="n"/>
       <c r="M296" s="22">
         <f>IF(H296="","",IF(K296="No",0,H296*N(I296)/100*IF(L296="",100,L296)/100))</f>
@@ -28573,7 +28563,7 @@
         <f>IF(H297="","",ROUND(H297*N(I297)/100,2))</f>
         <v/>
       </c>
-      <c r="K297" s="30" t="n"/>
+      <c r="K297" s="38" t="n"/>
       <c r="L297" s="32" t="n"/>
       <c r="M297" s="22">
         <f>IF(H297="","",IF(K297="No",0,H297*N(I297)/100*IF(L297="",100,L297)/100))</f>
@@ -28605,7 +28595,7 @@
         <f>IF(H298="","",ROUND(H298*N(I298)/100,2))</f>
         <v/>
       </c>
-      <c r="K298" s="30" t="n"/>
+      <c r="K298" s="38" t="n"/>
       <c r="L298" s="32" t="n"/>
       <c r="M298" s="22">
         <f>IF(H298="","",IF(K298="No",0,H298*N(I298)/100*IF(L298="",100,L298)/100))</f>
@@ -28637,7 +28627,7 @@
         <f>IF(H299="","",ROUND(H299*N(I299)/100,2))</f>
         <v/>
       </c>
-      <c r="K299" s="30" t="n"/>
+      <c r="K299" s="38" t="n"/>
       <c r="L299" s="32" t="n"/>
       <c r="M299" s="22">
         <f>IF(H299="","",IF(K299="No",0,H299*N(I299)/100*IF(L299="",100,L299)/100))</f>
@@ -28669,7 +28659,7 @@
         <f>IF(H300="","",ROUND(H300*N(I300)/100,2))</f>
         <v/>
       </c>
-      <c r="K300" s="30" t="n"/>
+      <c r="K300" s="38" t="n"/>
       <c r="L300" s="32" t="n"/>
       <c r="M300" s="22">
         <f>IF(H300="","",IF(K300="No",0,H300*N(I300)/100*IF(L300="",100,L300)/100))</f>
@@ -28701,7 +28691,7 @@
         <f>IF(H301="","",ROUND(H301*N(I301)/100,2))</f>
         <v/>
       </c>
-      <c r="K301" s="30" t="n"/>
+      <c r="K301" s="38" t="n"/>
       <c r="L301" s="32" t="n"/>
       <c r="M301" s="22">
         <f>IF(H301="","",IF(K301="No",0,H301*N(I301)/100*IF(L301="",100,L301)/100))</f>
@@ -28733,7 +28723,7 @@
         <f>IF(H302="","",ROUND(H302*N(I302)/100,2))</f>
         <v/>
       </c>
-      <c r="K302" s="30" t="n"/>
+      <c r="K302" s="38" t="n"/>
       <c r="L302" s="32" t="n"/>
       <c r="M302" s="22">
         <f>IF(H302="","",IF(K302="No",0,H302*N(I302)/100*IF(L302="",100,L302)/100))</f>
@@ -28765,7 +28755,7 @@
         <f>IF(H303="","",ROUND(H303*N(I303)/100,2))</f>
         <v/>
       </c>
-      <c r="K303" s="30" t="n"/>
+      <c r="K303" s="38" t="n"/>
       <c r="L303" s="32" t="n"/>
       <c r="M303" s="22">
         <f>IF(H303="","",IF(K303="No",0,H303*N(I303)/100*IF(L303="",100,L303)/100))</f>
@@ -28797,7 +28787,7 @@
         <f>IF(H304="","",ROUND(H304*N(I304)/100,2))</f>
         <v/>
       </c>
-      <c r="K304" s="30" t="n"/>
+      <c r="K304" s="38" t="n"/>
       <c r="L304" s="32" t="n"/>
       <c r="M304" s="22">
         <f>IF(H304="","",IF(K304="No",0,H304*N(I304)/100*IF(L304="",100,L304)/100))</f>
@@ -28829,7 +28819,7 @@
         <f>IF(H305="","",ROUND(H305*N(I305)/100,2))</f>
         <v/>
       </c>
-      <c r="K305" s="30" t="n"/>
+      <c r="K305" s="38" t="n"/>
       <c r="L305" s="32" t="n"/>
       <c r="M305" s="22">
         <f>IF(H305="","",IF(K305="No",0,H305*N(I305)/100*IF(L305="",100,L305)/100))</f>
@@ -28861,7 +28851,7 @@
         <f>IF(H306="","",ROUND(H306*N(I306)/100,2))</f>
         <v/>
       </c>
-      <c r="K306" s="30" t="n"/>
+      <c r="K306" s="38" t="n"/>
       <c r="L306" s="32" t="n"/>
       <c r="M306" s="22">
         <f>IF(H306="","",IF(K306="No",0,H306*N(I306)/100*IF(L306="",100,L306)/100))</f>
@@ -28893,7 +28883,7 @@
         <f>IF(H307="","",ROUND(H307*N(I307)/100,2))</f>
         <v/>
       </c>
-      <c r="K307" s="30" t="n"/>
+      <c r="K307" s="38" t="n"/>
       <c r="L307" s="32" t="n"/>
       <c r="M307" s="22">
         <f>IF(H307="","",IF(K307="No",0,H307*N(I307)/100*IF(L307="",100,L307)/100))</f>
@@ -28925,7 +28915,7 @@
         <f>IF(H308="","",ROUND(H308*N(I308)/100,2))</f>
         <v/>
       </c>
-      <c r="K308" s="30" t="n"/>
+      <c r="K308" s="38" t="n"/>
       <c r="L308" s="32" t="n"/>
       <c r="M308" s="22">
         <f>IF(H308="","",IF(K308="No",0,H308*N(I308)/100*IF(L308="",100,L308)/100))</f>
@@ -28957,7 +28947,7 @@
         <f>IF(H309="","",ROUND(H309*N(I309)/100,2))</f>
         <v/>
       </c>
-      <c r="K309" s="30" t="n"/>
+      <c r="K309" s="38" t="n"/>
       <c r="L309" s="32" t="n"/>
       <c r="M309" s="22">
         <f>IF(H309="","",IF(K309="No",0,H309*N(I309)/100*IF(L309="",100,L309)/100))</f>
@@ -28989,7 +28979,7 @@
         <f>IF(H310="","",ROUND(H310*N(I310)/100,2))</f>
         <v/>
       </c>
-      <c r="K310" s="30" t="n"/>
+      <c r="K310" s="38" t="n"/>
       <c r="L310" s="32" t="n"/>
       <c r="M310" s="22">
         <f>IF(H310="","",IF(K310="No",0,H310*N(I310)/100*IF(L310="",100,L310)/100))</f>
@@ -29021,7 +29011,7 @@
         <f>IF(H311="","",ROUND(H311*N(I311)/100,2))</f>
         <v/>
       </c>
-      <c r="K311" s="30" t="n"/>
+      <c r="K311" s="38" t="n"/>
       <c r="L311" s="32" t="n"/>
       <c r="M311" s="22">
         <f>IF(H311="","",IF(K311="No",0,H311*N(I311)/100*IF(L311="",100,L311)/100))</f>
@@ -29053,7 +29043,7 @@
         <f>IF(H312="","",ROUND(H312*N(I312)/100,2))</f>
         <v/>
       </c>
-      <c r="K312" s="30" t="n"/>
+      <c r="K312" s="38" t="n"/>
       <c r="L312" s="32" t="n"/>
       <c r="M312" s="22">
         <f>IF(H312="","",IF(K312="No",0,H312*N(I312)/100*IF(L312="",100,L312)/100))</f>
@@ -29085,7 +29075,7 @@
         <f>IF(H313="","",ROUND(H313*N(I313)/100,2))</f>
         <v/>
       </c>
-      <c r="K313" s="30" t="n"/>
+      <c r="K313" s="38" t="n"/>
       <c r="L313" s="32" t="n"/>
       <c r="M313" s="22">
         <f>IF(H313="","",IF(K313="No",0,H313*N(I313)/100*IF(L313="",100,L313)/100))</f>
@@ -29117,7 +29107,7 @@
         <f>IF(H314="","",ROUND(H314*N(I314)/100,2))</f>
         <v/>
       </c>
-      <c r="K314" s="30" t="n"/>
+      <c r="K314" s="38" t="n"/>
       <c r="L314" s="32" t="n"/>
       <c r="M314" s="22">
         <f>IF(H314="","",IF(K314="No",0,H314*N(I314)/100*IF(L314="",100,L314)/100))</f>
@@ -29149,7 +29139,7 @@
         <f>IF(H315="","",ROUND(H315*N(I315)/100,2))</f>
         <v/>
       </c>
-      <c r="K315" s="30" t="n"/>
+      <c r="K315" s="38" t="n"/>
       <c r="L315" s="32" t="n"/>
       <c r="M315" s="22">
         <f>IF(H315="","",IF(K315="No",0,H315*N(I315)/100*IF(L315="",100,L315)/100))</f>
@@ -29181,7 +29171,7 @@
         <f>IF(H316="","",ROUND(H316*N(I316)/100,2))</f>
         <v/>
       </c>
-      <c r="K316" s="30" t="n"/>
+      <c r="K316" s="38" t="n"/>
       <c r="L316" s="32" t="n"/>
       <c r="M316" s="22">
         <f>IF(H316="","",IF(K316="No",0,H316*N(I316)/100*IF(L316="",100,L316)/100))</f>
@@ -29213,7 +29203,7 @@
         <f>IF(H317="","",ROUND(H317*N(I317)/100,2))</f>
         <v/>
       </c>
-      <c r="K317" s="30" t="n"/>
+      <c r="K317" s="38" t="n"/>
       <c r="L317" s="32" t="n"/>
       <c r="M317" s="22">
         <f>IF(H317="","",IF(K317="No",0,H317*N(I317)/100*IF(L317="",100,L317)/100))</f>
@@ -29245,7 +29235,7 @@
         <f>IF(H318="","",ROUND(H318*N(I318)/100,2))</f>
         <v/>
       </c>
-      <c r="K318" s="30" t="n"/>
+      <c r="K318" s="38" t="n"/>
       <c r="L318" s="32" t="n"/>
       <c r="M318" s="22">
         <f>IF(H318="","",IF(K318="No",0,H318*N(I318)/100*IF(L318="",100,L318)/100))</f>
@@ -29277,7 +29267,7 @@
         <f>IF(H319="","",ROUND(H319*N(I319)/100,2))</f>
         <v/>
       </c>
-      <c r="K319" s="30" t="n"/>
+      <c r="K319" s="38" t="n"/>
       <c r="L319" s="32" t="n"/>
       <c r="M319" s="22">
         <f>IF(H319="","",IF(K319="No",0,H319*N(I319)/100*IF(L319="",100,L319)/100))</f>
@@ -29309,7 +29299,7 @@
         <f>IF(H320="","",ROUND(H320*N(I320)/100,2))</f>
         <v/>
       </c>
-      <c r="K320" s="30" t="n"/>
+      <c r="K320" s="38" t="n"/>
       <c r="L320" s="32" t="n"/>
       <c r="M320" s="22">
         <f>IF(H320="","",IF(K320="No",0,H320*N(I320)/100*IF(L320="",100,L320)/100))</f>
@@ -29341,7 +29331,7 @@
         <f>IF(H321="","",ROUND(H321*N(I321)/100,2))</f>
         <v/>
       </c>
-      <c r="K321" s="30" t="n"/>
+      <c r="K321" s="38" t="n"/>
       <c r="L321" s="32" t="n"/>
       <c r="M321" s="22">
         <f>IF(H321="","",IF(K321="No",0,H321*N(I321)/100*IF(L321="",100,L321)/100))</f>
@@ -29373,7 +29363,7 @@
         <f>IF(H322="","",ROUND(H322*N(I322)/100,2))</f>
         <v/>
       </c>
-      <c r="K322" s="30" t="n"/>
+      <c r="K322" s="38" t="n"/>
       <c r="L322" s="32" t="n"/>
       <c r="M322" s="22">
         <f>IF(H322="","",IF(K322="No",0,H322*N(I322)/100*IF(L322="",100,L322)/100))</f>
@@ -29405,7 +29395,7 @@
         <f>IF(H323="","",ROUND(H323*N(I323)/100,2))</f>
         <v/>
       </c>
-      <c r="K323" s="30" t="n"/>
+      <c r="K323" s="38" t="n"/>
       <c r="L323" s="32" t="n"/>
       <c r="M323" s="22">
         <f>IF(H323="","",IF(K323="No",0,H323*N(I323)/100*IF(L323="",100,L323)/100))</f>
@@ -29437,7 +29427,7 @@
         <f>IF(H324="","",ROUND(H324*N(I324)/100,2))</f>
         <v/>
       </c>
-      <c r="K324" s="30" t="n"/>
+      <c r="K324" s="38" t="n"/>
       <c r="L324" s="32" t="n"/>
       <c r="M324" s="22">
         <f>IF(H324="","",IF(K324="No",0,H324*N(I324)/100*IF(L324="",100,L324)/100))</f>
@@ -29469,7 +29459,7 @@
         <f>IF(H325="","",ROUND(H325*N(I325)/100,2))</f>
         <v/>
       </c>
-      <c r="K325" s="30" t="n"/>
+      <c r="K325" s="38" t="n"/>
       <c r="L325" s="32" t="n"/>
       <c r="M325" s="22">
         <f>IF(H325="","",IF(K325="No",0,H325*N(I325)/100*IF(L325="",100,L325)/100))</f>
@@ -29501,7 +29491,7 @@
         <f>IF(H326="","",ROUND(H326*N(I326)/100,2))</f>
         <v/>
       </c>
-      <c r="K326" s="30" t="n"/>
+      <c r="K326" s="38" t="n"/>
       <c r="L326" s="32" t="n"/>
       <c r="M326" s="22">
         <f>IF(H326="","",IF(K326="No",0,H326*N(I326)/100*IF(L326="",100,L326)/100))</f>
@@ -29533,7 +29523,7 @@
         <f>IF(H327="","",ROUND(H327*N(I327)/100,2))</f>
         <v/>
       </c>
-      <c r="K327" s="30" t="n"/>
+      <c r="K327" s="38" t="n"/>
       <c r="L327" s="32" t="n"/>
       <c r="M327" s="22">
         <f>IF(H327="","",IF(K327="No",0,H327*N(I327)/100*IF(L327="",100,L327)/100))</f>
@@ -29565,7 +29555,7 @@
         <f>IF(H328="","",ROUND(H328*N(I328)/100,2))</f>
         <v/>
       </c>
-      <c r="K328" s="30" t="n"/>
+      <c r="K328" s="38" t="n"/>
       <c r="L328" s="32" t="n"/>
       <c r="M328" s="22">
         <f>IF(H328="","",IF(K328="No",0,H328*N(I328)/100*IF(L328="",100,L328)/100))</f>
@@ -29597,7 +29587,7 @@
         <f>IF(H329="","",ROUND(H329*N(I329)/100,2))</f>
         <v/>
       </c>
-      <c r="K329" s="30" t="n"/>
+      <c r="K329" s="38" t="n"/>
       <c r="L329" s="32" t="n"/>
       <c r="M329" s="22">
         <f>IF(H329="","",IF(K329="No",0,H329*N(I329)/100*IF(L329="",100,L329)/100))</f>
@@ -29629,7 +29619,7 @@
         <f>IF(H330="","",ROUND(H330*N(I330)/100,2))</f>
         <v/>
       </c>
-      <c r="K330" s="30" t="n"/>
+      <c r="K330" s="38" t="n"/>
       <c r="L330" s="32" t="n"/>
       <c r="M330" s="22">
         <f>IF(H330="","",IF(K330="No",0,H330*N(I330)/100*IF(L330="",100,L330)/100))</f>
@@ -29661,7 +29651,7 @@
         <f>IF(H331="","",ROUND(H331*N(I331)/100,2))</f>
         <v/>
       </c>
-      <c r="K331" s="30" t="n"/>
+      <c r="K331" s="38" t="n"/>
       <c r="L331" s="32" t="n"/>
       <c r="M331" s="22">
         <f>IF(H331="","",IF(K331="No",0,H331*N(I331)/100*IF(L331="",100,L331)/100))</f>
@@ -29693,7 +29683,7 @@
         <f>IF(H332="","",ROUND(H332*N(I332)/100,2))</f>
         <v/>
       </c>
-      <c r="K332" s="30" t="n"/>
+      <c r="K332" s="38" t="n"/>
       <c r="L332" s="32" t="n"/>
       <c r="M332" s="22">
         <f>IF(H332="","",IF(K332="No",0,H332*N(I332)/100*IF(L332="",100,L332)/100))</f>
@@ -29725,7 +29715,7 @@
         <f>IF(H333="","",ROUND(H333*N(I333)/100,2))</f>
         <v/>
       </c>
-      <c r="K333" s="30" t="n"/>
+      <c r="K333" s="38" t="n"/>
       <c r="L333" s="32" t="n"/>
       <c r="M333" s="22">
         <f>IF(H333="","",IF(K333="No",0,H333*N(I333)/100*IF(L333="",100,L333)/100))</f>
@@ -29757,7 +29747,7 @@
         <f>IF(H334="","",ROUND(H334*N(I334)/100,2))</f>
         <v/>
       </c>
-      <c r="K334" s="30" t="n"/>
+      <c r="K334" s="38" t="n"/>
       <c r="L334" s="32" t="n"/>
       <c r="M334" s="22">
         <f>IF(H334="","",IF(K334="No",0,H334*N(I334)/100*IF(L334="",100,L334)/100))</f>
@@ -29789,7 +29779,7 @@
         <f>IF(H335="","",ROUND(H335*N(I335)/100,2))</f>
         <v/>
       </c>
-      <c r="K335" s="30" t="n"/>
+      <c r="K335" s="38" t="n"/>
       <c r="L335" s="32" t="n"/>
       <c r="M335" s="22">
         <f>IF(H335="","",IF(K335="No",0,H335*N(I335)/100*IF(L335="",100,L335)/100))</f>
@@ -29821,7 +29811,7 @@
         <f>IF(H336="","",ROUND(H336*N(I336)/100,2))</f>
         <v/>
       </c>
-      <c r="K336" s="30" t="n"/>
+      <c r="K336" s="38" t="n"/>
       <c r="L336" s="32" t="n"/>
       <c r="M336" s="22">
         <f>IF(H336="","",IF(K336="No",0,H336*N(I336)/100*IF(L336="",100,L336)/100))</f>
@@ -29853,7 +29843,7 @@
         <f>IF(H337="","",ROUND(H337*N(I337)/100,2))</f>
         <v/>
       </c>
-      <c r="K337" s="30" t="n"/>
+      <c r="K337" s="38" t="n"/>
       <c r="L337" s="32" t="n"/>
       <c r="M337" s="22">
         <f>IF(H337="","",IF(K337="No",0,H337*N(I337)/100*IF(L337="",100,L337)/100))</f>
@@ -29885,7 +29875,7 @@
         <f>IF(H338="","",ROUND(H338*N(I338)/100,2))</f>
         <v/>
       </c>
-      <c r="K338" s="30" t="n"/>
+      <c r="K338" s="38" t="n"/>
       <c r="L338" s="32" t="n"/>
       <c r="M338" s="22">
         <f>IF(H338="","",IF(K338="No",0,H338*N(I338)/100*IF(L338="",100,L338)/100))</f>
@@ -29917,7 +29907,7 @@
         <f>IF(H339="","",ROUND(H339*N(I339)/100,2))</f>
         <v/>
       </c>
-      <c r="K339" s="30" t="n"/>
+      <c r="K339" s="38" t="n"/>
       <c r="L339" s="32" t="n"/>
       <c r="M339" s="22">
         <f>IF(H339="","",IF(K339="No",0,H339*N(I339)/100*IF(L339="",100,L339)/100))</f>
@@ -29949,7 +29939,7 @@
         <f>IF(H340="","",ROUND(H340*N(I340)/100,2))</f>
         <v/>
       </c>
-      <c r="K340" s="30" t="n"/>
+      <c r="K340" s="38" t="n"/>
       <c r="L340" s="32" t="n"/>
       <c r="M340" s="22">
         <f>IF(H340="","",IF(K340="No",0,H340*N(I340)/100*IF(L340="",100,L340)/100))</f>
@@ -29981,7 +29971,7 @@
         <f>IF(H341="","",ROUND(H341*N(I341)/100,2))</f>
         <v/>
       </c>
-      <c r="K341" s="30" t="n"/>
+      <c r="K341" s="38" t="n"/>
       <c r="L341" s="32" t="n"/>
       <c r="M341" s="22">
         <f>IF(H341="","",IF(K341="No",0,H341*N(I341)/100*IF(L341="",100,L341)/100))</f>
@@ -30013,7 +30003,7 @@
         <f>IF(H342="","",ROUND(H342*N(I342)/100,2))</f>
         <v/>
       </c>
-      <c r="K342" s="30" t="n"/>
+      <c r="K342" s="38" t="n"/>
       <c r="L342" s="32" t="n"/>
       <c r="M342" s="22">
         <f>IF(H342="","",IF(K342="No",0,H342*N(I342)/100*IF(L342="",100,L342)/100))</f>
@@ -30045,7 +30035,7 @@
         <f>IF(H343="","",ROUND(H343*N(I343)/100,2))</f>
         <v/>
       </c>
-      <c r="K343" s="30" t="n"/>
+      <c r="K343" s="38" t="n"/>
       <c r="L343" s="32" t="n"/>
       <c r="M343" s="22">
         <f>IF(H343="","",IF(K343="No",0,H343*N(I343)/100*IF(L343="",100,L343)/100))</f>
@@ -30077,7 +30067,7 @@
         <f>IF(H344="","",ROUND(H344*N(I344)/100,2))</f>
         <v/>
       </c>
-      <c r="K344" s="30" t="n"/>
+      <c r="K344" s="38" t="n"/>
       <c r="L344" s="32" t="n"/>
       <c r="M344" s="22">
         <f>IF(H344="","",IF(K344="No",0,H344*N(I344)/100*IF(L344="",100,L344)/100))</f>
@@ -30109,7 +30099,7 @@
         <f>IF(H345="","",ROUND(H345*N(I345)/100,2))</f>
         <v/>
       </c>
-      <c r="K345" s="30" t="n"/>
+      <c r="K345" s="38" t="n"/>
       <c r="L345" s="32" t="n"/>
       <c r="M345" s="22">
         <f>IF(H345="","",IF(K345="No",0,H345*N(I345)/100*IF(L345="",100,L345)/100))</f>
@@ -30141,7 +30131,7 @@
         <f>IF(H346="","",ROUND(H346*N(I346)/100,2))</f>
         <v/>
       </c>
-      <c r="K346" s="30" t="n"/>
+      <c r="K346" s="38" t="n"/>
       <c r="L346" s="32" t="n"/>
       <c r="M346" s="22">
         <f>IF(H346="","",IF(K346="No",0,H346*N(I346)/100*IF(L346="",100,L346)/100))</f>
@@ -30173,7 +30163,7 @@
         <f>IF(H347="","",ROUND(H347*N(I347)/100,2))</f>
         <v/>
       </c>
-      <c r="K347" s="30" t="n"/>
+      <c r="K347" s="38" t="n"/>
       <c r="L347" s="32" t="n"/>
       <c r="M347" s="22">
         <f>IF(H347="","",IF(K347="No",0,H347*N(I347)/100*IF(L347="",100,L347)/100))</f>
@@ -30205,7 +30195,7 @@
         <f>IF(H348="","",ROUND(H348*N(I348)/100,2))</f>
         <v/>
       </c>
-      <c r="K348" s="30" t="n"/>
+      <c r="K348" s="38" t="n"/>
       <c r="L348" s="32" t="n"/>
       <c r="M348" s="22">
         <f>IF(H348="","",IF(K348="No",0,H348*N(I348)/100*IF(L348="",100,L348)/100))</f>
@@ -30237,7 +30227,7 @@
         <f>IF(H349="","",ROUND(H349*N(I349)/100,2))</f>
         <v/>
       </c>
-      <c r="K349" s="30" t="n"/>
+      <c r="K349" s="38" t="n"/>
       <c r="L349" s="32" t="n"/>
       <c r="M349" s="22">
         <f>IF(H349="","",IF(K349="No",0,H349*N(I349)/100*IF(L349="",100,L349)/100))</f>
@@ -30269,7 +30259,7 @@
         <f>IF(H350="","",ROUND(H350*N(I350)/100,2))</f>
         <v/>
       </c>
-      <c r="K350" s="30" t="n"/>
+      <c r="K350" s="38" t="n"/>
       <c r="L350" s="32" t="n"/>
       <c r="M350" s="22">
         <f>IF(H350="","",IF(K350="No",0,H350*N(I350)/100*IF(L350="",100,L350)/100))</f>
@@ -30301,7 +30291,7 @@
         <f>IF(H351="","",ROUND(H351*N(I351)/100,2))</f>
         <v/>
       </c>
-      <c r="K351" s="30" t="n"/>
+      <c r="K351" s="38" t="n"/>
       <c r="L351" s="32" t="n"/>
       <c r="M351" s="22">
         <f>IF(H351="","",IF(K351="No",0,H351*N(I351)/100*IF(L351="",100,L351)/100))</f>
@@ -30333,7 +30323,7 @@
         <f>IF(H352="","",ROUND(H352*N(I352)/100,2))</f>
         <v/>
       </c>
-      <c r="K352" s="30" t="n"/>
+      <c r="K352" s="38" t="n"/>
       <c r="L352" s="32" t="n"/>
       <c r="M352" s="22">
         <f>IF(H352="","",IF(K352="No",0,H352*N(I352)/100*IF(L352="",100,L352)/100))</f>
@@ -30365,7 +30355,7 @@
         <f>IF(H353="","",ROUND(H353*N(I353)/100,2))</f>
         <v/>
       </c>
-      <c r="K353" s="30" t="n"/>
+      <c r="K353" s="38" t="n"/>
       <c r="L353" s="32" t="n"/>
       <c r="M353" s="22">
         <f>IF(H353="","",IF(K353="No",0,H353*N(I353)/100*IF(L353="",100,L353)/100))</f>
@@ -30397,7 +30387,7 @@
         <f>IF(H354="","",ROUND(H354*N(I354)/100,2))</f>
         <v/>
       </c>
-      <c r="K354" s="30" t="n"/>
+      <c r="K354" s="38" t="n"/>
       <c r="L354" s="32" t="n"/>
       <c r="M354" s="22">
         <f>IF(H354="","",IF(K354="No",0,H354*N(I354)/100*IF(L354="",100,L354)/100))</f>
@@ -30429,7 +30419,7 @@
         <f>IF(H355="","",ROUND(H355*N(I355)/100,2))</f>
         <v/>
       </c>
-      <c r="K355" s="30" t="n"/>
+      <c r="K355" s="38" t="n"/>
       <c r="L355" s="32" t="n"/>
       <c r="M355" s="22">
         <f>IF(H355="","",IF(K355="No",0,H355*N(I355)/100*IF(L355="",100,L355)/100))</f>
@@ -30461,7 +30451,7 @@
         <f>IF(H356="","",ROUND(H356*N(I356)/100,2))</f>
         <v/>
       </c>
-      <c r="K356" s="30" t="n"/>
+      <c r="K356" s="38" t="n"/>
       <c r="L356" s="32" t="n"/>
       <c r="M356" s="22">
         <f>IF(H356="","",IF(K356="No",0,H356*N(I356)/100*IF(L356="",100,L356)/100))</f>
@@ -30493,7 +30483,7 @@
         <f>IF(H357="","",ROUND(H357*N(I357)/100,2))</f>
         <v/>
       </c>
-      <c r="K357" s="30" t="n"/>
+      <c r="K357" s="38" t="n"/>
       <c r="L357" s="32" t="n"/>
       <c r="M357" s="22">
         <f>IF(H357="","",IF(K357="No",0,H357*N(I357)/100*IF(L357="",100,L357)/100))</f>
@@ -30525,7 +30515,7 @@
         <f>IF(H358="","",ROUND(H358*N(I358)/100,2))</f>
         <v/>
       </c>
-      <c r="K358" s="30" t="n"/>
+      <c r="K358" s="38" t="n"/>
       <c r="L358" s="32" t="n"/>
       <c r="M358" s="22">
         <f>IF(H358="","",IF(K358="No",0,H358*N(I358)/100*IF(L358="",100,L358)/100))</f>
@@ -30557,7 +30547,7 @@
         <f>IF(H359="","",ROUND(H359*N(I359)/100,2))</f>
         <v/>
       </c>
-      <c r="K359" s="30" t="n"/>
+      <c r="K359" s="38" t="n"/>
       <c r="L359" s="32" t="n"/>
       <c r="M359" s="22">
         <f>IF(H359="","",IF(K359="No",0,H359*N(I359)/100*IF(L359="",100,L359)/100))</f>
@@ -30589,7 +30579,7 @@
         <f>IF(H360="","",ROUND(H360*N(I360)/100,2))</f>
         <v/>
       </c>
-      <c r="K360" s="30" t="n"/>
+      <c r="K360" s="38" t="n"/>
       <c r="L360" s="32" t="n"/>
       <c r="M360" s="22">
         <f>IF(H360="","",IF(K360="No",0,H360*N(I360)/100*IF(L360="",100,L360)/100))</f>
@@ -30621,7 +30611,7 @@
         <f>IF(H361="","",ROUND(H361*N(I361)/100,2))</f>
         <v/>
       </c>
-      <c r="K361" s="30" t="n"/>
+      <c r="K361" s="38" t="n"/>
       <c r="L361" s="32" t="n"/>
       <c r="M361" s="22">
         <f>IF(H361="","",IF(K361="No",0,H361*N(I361)/100*IF(L361="",100,L361)/100))</f>
@@ -30653,7 +30643,7 @@
         <f>IF(H362="","",ROUND(H362*N(I362)/100,2))</f>
         <v/>
       </c>
-      <c r="K362" s="30" t="n"/>
+      <c r="K362" s="38" t="n"/>
       <c r="L362" s="32" t="n"/>
       <c r="M362" s="22">
         <f>IF(H362="","",IF(K362="No",0,H362*N(I362)/100*IF(L362="",100,L362)/100))</f>
@@ -30685,7 +30675,7 @@
         <f>IF(H363="","",ROUND(H363*N(I363)/100,2))</f>
         <v/>
       </c>
-      <c r="K363" s="30" t="n"/>
+      <c r="K363" s="38" t="n"/>
       <c r="L363" s="32" t="n"/>
       <c r="M363" s="22">
         <f>IF(H363="","",IF(K363="No",0,H363*N(I363)/100*IF(L363="",100,L363)/100))</f>
@@ -30717,7 +30707,7 @@
         <f>IF(H364="","",ROUND(H364*N(I364)/100,2))</f>
         <v/>
       </c>
-      <c r="K364" s="30" t="n"/>
+      <c r="K364" s="38" t="n"/>
       <c r="L364" s="32" t="n"/>
       <c r="M364" s="22">
         <f>IF(H364="","",IF(K364="No",0,H364*N(I364)/100*IF(L364="",100,L364)/100))</f>
@@ -30749,7 +30739,7 @@
         <f>IF(H365="","",ROUND(H365*N(I365)/100,2))</f>
         <v/>
       </c>
-      <c r="K365" s="30" t="n"/>
+      <c r="K365" s="38" t="n"/>
       <c r="L365" s="32" t="n"/>
       <c r="M365" s="22">
         <f>IF(H365="","",IF(K365="No",0,H365*N(I365)/100*IF(L365="",100,L365)/100))</f>
@@ -30781,7 +30771,7 @@
         <f>IF(H366="","",ROUND(H366*N(I366)/100,2))</f>
         <v/>
       </c>
-      <c r="K366" s="30" t="n"/>
+      <c r="K366" s="38" t="n"/>
       <c r="L366" s="32" t="n"/>
       <c r="M366" s="22">
         <f>IF(H366="","",IF(K366="No",0,H366*N(I366)/100*IF(L366="",100,L366)/100))</f>
@@ -30813,7 +30803,7 @@
         <f>IF(H367="","",ROUND(H367*N(I367)/100,2))</f>
         <v/>
       </c>
-      <c r="K367" s="30" t="n"/>
+      <c r="K367" s="38" t="n"/>
       <c r="L367" s="32" t="n"/>
       <c r="M367" s="22">
         <f>IF(H367="","",IF(K367="No",0,H367*N(I367)/100*IF(L367="",100,L367)/100))</f>
@@ -30845,7 +30835,7 @@
         <f>IF(H368="","",ROUND(H368*N(I368)/100,2))</f>
         <v/>
       </c>
-      <c r="K368" s="30" t="n"/>
+      <c r="K368" s="38" t="n"/>
       <c r="L368" s="32" t="n"/>
       <c r="M368" s="22">
         <f>IF(H368="","",IF(K368="No",0,H368*N(I368)/100*IF(L368="",100,L368)/100))</f>
@@ -30877,7 +30867,7 @@
         <f>IF(H369="","",ROUND(H369*N(I369)/100,2))</f>
         <v/>
       </c>
-      <c r="K369" s="30" t="n"/>
+      <c r="K369" s="38" t="n"/>
       <c r="L369" s="32" t="n"/>
       <c r="M369" s="22">
         <f>IF(H369="","",IF(K369="No",0,H369*N(I369)/100*IF(L369="",100,L369)/100))</f>
@@ -30909,7 +30899,7 @@
         <f>IF(H370="","",ROUND(H370*N(I370)/100,2))</f>
         <v/>
       </c>
-      <c r="K370" s="30" t="n"/>
+      <c r="K370" s="38" t="n"/>
       <c r="L370" s="32" t="n"/>
       <c r="M370" s="22">
         <f>IF(H370="","",IF(K370="No",0,H370*N(I370)/100*IF(L370="",100,L370)/100))</f>
@@ -30941,7 +30931,7 @@
         <f>IF(H371="","",ROUND(H371*N(I371)/100,2))</f>
         <v/>
       </c>
-      <c r="K371" s="30" t="n"/>
+      <c r="K371" s="38" t="n"/>
       <c r="L371" s="32" t="n"/>
       <c r="M371" s="22">
         <f>IF(H371="","",IF(K371="No",0,H371*N(I371)/100*IF(L371="",100,L371)/100))</f>
@@ -30973,7 +30963,7 @@
         <f>IF(H372="","",ROUND(H372*N(I372)/100,2))</f>
         <v/>
       </c>
-      <c r="K372" s="30" t="n"/>
+      <c r="K372" s="38" t="n"/>
       <c r="L372" s="32" t="n"/>
       <c r="M372" s="22">
         <f>IF(H372="","",IF(K372="No",0,H372*N(I372)/100*IF(L372="",100,L372)/100))</f>
@@ -31005,7 +30995,7 @@
         <f>IF(H373="","",ROUND(H373*N(I373)/100,2))</f>
         <v/>
       </c>
-      <c r="K373" s="30" t="n"/>
+      <c r="K373" s="38" t="n"/>
       <c r="L373" s="32" t="n"/>
       <c r="M373" s="22">
         <f>IF(H373="","",IF(K373="No",0,H373*N(I373)/100*IF(L373="",100,L373)/100))</f>
@@ -31037,7 +31027,7 @@
         <f>IF(H374="","",ROUND(H374*N(I374)/100,2))</f>
         <v/>
       </c>
-      <c r="K374" s="30" t="n"/>
+      <c r="K374" s="38" t="n"/>
       <c r="L374" s="32" t="n"/>
       <c r="M374" s="22">
         <f>IF(H374="","",IF(K374="No",0,H374*N(I374)/100*IF(L374="",100,L374)/100))</f>
@@ -31069,7 +31059,7 @@
         <f>IF(H375="","",ROUND(H375*N(I375)/100,2))</f>
         <v/>
       </c>
-      <c r="K375" s="30" t="n"/>
+      <c r="K375" s="38" t="n"/>
       <c r="L375" s="32" t="n"/>
       <c r="M375" s="22">
         <f>IF(H375="","",IF(K375="No",0,H375*N(I375)/100*IF(L375="",100,L375)/100))</f>
@@ -31101,7 +31091,7 @@
         <f>IF(H376="","",ROUND(H376*N(I376)/100,2))</f>
         <v/>
       </c>
-      <c r="K376" s="30" t="n"/>
+      <c r="K376" s="38" t="n"/>
       <c r="L376" s="32" t="n"/>
       <c r="M376" s="22">
         <f>IF(H376="","",IF(K376="No",0,H376*N(I376)/100*IF(L376="",100,L376)/100))</f>
@@ -31133,7 +31123,7 @@
         <f>IF(H377="","",ROUND(H377*N(I377)/100,2))</f>
         <v/>
       </c>
-      <c r="K377" s="30" t="n"/>
+      <c r="K377" s="38" t="n"/>
       <c r="L377" s="32" t="n"/>
       <c r="M377" s="22">
         <f>IF(H377="","",IF(K377="No",0,H377*N(I377)/100*IF(L377="",100,L377)/100))</f>
@@ -31165,7 +31155,7 @@
         <f>IF(H378="","",ROUND(H378*N(I378)/100,2))</f>
         <v/>
       </c>
-      <c r="K378" s="30" t="n"/>
+      <c r="K378" s="38" t="n"/>
       <c r="L378" s="32" t="n"/>
       <c r="M378" s="22">
         <f>IF(H378="","",IF(K378="No",0,H378*N(I378)/100*IF(L378="",100,L378)/100))</f>
@@ -31197,7 +31187,7 @@
         <f>IF(H379="","",ROUND(H379*N(I379)/100,2))</f>
         <v/>
       </c>
-      <c r="K379" s="30" t="n"/>
+      <c r="K379" s="38" t="n"/>
       <c r="L379" s="32" t="n"/>
       <c r="M379" s="22">
         <f>IF(H379="","",IF(K379="No",0,H379*N(I379)/100*IF(L379="",100,L379)/100))</f>
@@ -31229,7 +31219,7 @@
         <f>IF(H380="","",ROUND(H380*N(I380)/100,2))</f>
         <v/>
       </c>
-      <c r="K380" s="30" t="n"/>
+      <c r="K380" s="38" t="n"/>
       <c r="L380" s="32" t="n"/>
       <c r="M380" s="22">
         <f>IF(H380="","",IF(K380="No",0,H380*N(I380)/100*IF(L380="",100,L380)/100))</f>
@@ -31261,7 +31251,7 @@
         <f>IF(H381="","",ROUND(H381*N(I381)/100,2))</f>
         <v/>
       </c>
-      <c r="K381" s="30" t="n"/>
+      <c r="K381" s="38" t="n"/>
       <c r="L381" s="32" t="n"/>
       <c r="M381" s="22">
         <f>IF(H381="","",IF(K381="No",0,H381*N(I381)/100*IF(L381="",100,L381)/100))</f>
@@ -31293,7 +31283,7 @@
         <f>IF(H382="","",ROUND(H382*N(I382)/100,2))</f>
         <v/>
       </c>
-      <c r="K382" s="30" t="n"/>
+      <c r="K382" s="38" t="n"/>
       <c r="L382" s="32" t="n"/>
       <c r="M382" s="22">
         <f>IF(H382="","",IF(K382="No",0,H382*N(I382)/100*IF(L382="",100,L382)/100))</f>
@@ -31325,7 +31315,7 @@
         <f>IF(H383="","",ROUND(H383*N(I383)/100,2))</f>
         <v/>
       </c>
-      <c r="K383" s="30" t="n"/>
+      <c r="K383" s="38" t="n"/>
       <c r="L383" s="32" t="n"/>
       <c r="M383" s="22">
         <f>IF(H383="","",IF(K383="No",0,H383*N(I383)/100*IF(L383="",100,L383)/100))</f>
@@ -31357,7 +31347,7 @@
         <f>IF(H384="","",ROUND(H384*N(I384)/100,2))</f>
         <v/>
       </c>
-      <c r="K384" s="30" t="n"/>
+      <c r="K384" s="38" t="n"/>
       <c r="L384" s="32" t="n"/>
       <c r="M384" s="22">
         <f>IF(H384="","",IF(K384="No",0,H384*N(I384)/100*IF(L384="",100,L384)/100))</f>
@@ -31389,7 +31379,7 @@
         <f>IF(H385="","",ROUND(H385*N(I385)/100,2))</f>
         <v/>
       </c>
-      <c r="K385" s="30" t="n"/>
+      <c r="K385" s="38" t="n"/>
       <c r="L385" s="32" t="n"/>
       <c r="M385" s="22">
         <f>IF(H385="","",IF(K385="No",0,H385*N(I385)/100*IF(L385="",100,L385)/100))</f>
@@ -31421,7 +31411,7 @@
         <f>IF(H386="","",ROUND(H386*N(I386)/100,2))</f>
         <v/>
       </c>
-      <c r="K386" s="30" t="n"/>
+      <c r="K386" s="38" t="n"/>
       <c r="L386" s="32" t="n"/>
       <c r="M386" s="22">
         <f>IF(H386="","",IF(K386="No",0,H386*N(I386)/100*IF(L386="",100,L386)/100))</f>
@@ -31453,7 +31443,7 @@
         <f>IF(H387="","",ROUND(H387*N(I387)/100,2))</f>
         <v/>
       </c>
-      <c r="K387" s="30" t="n"/>
+      <c r="K387" s="38" t="n"/>
       <c r="L387" s="32" t="n"/>
       <c r="M387" s="22">
         <f>IF(H387="","",IF(K387="No",0,H387*N(I387)/100*IF(L387="",100,L387)/100))</f>
@@ -31485,7 +31475,7 @@
         <f>IF(H388="","",ROUND(H388*N(I388)/100,2))</f>
         <v/>
       </c>
-      <c r="K388" s="30" t="n"/>
+      <c r="K388" s="38" t="n"/>
       <c r="L388" s="32" t="n"/>
       <c r="M388" s="22">
         <f>IF(H388="","",IF(K388="No",0,H388*N(I388)/100*IF(L388="",100,L388)/100))</f>
@@ -31517,7 +31507,7 @@
         <f>IF(H389="","",ROUND(H389*N(I389)/100,2))</f>
         <v/>
       </c>
-      <c r="K389" s="30" t="n"/>
+      <c r="K389" s="38" t="n"/>
       <c r="L389" s="32" t="n"/>
       <c r="M389" s="22">
         <f>IF(H389="","",IF(K389="No",0,H389*N(I389)/100*IF(L389="",100,L389)/100))</f>
@@ -31549,7 +31539,7 @@
         <f>IF(H390="","",ROUND(H390*N(I390)/100,2))</f>
         <v/>
       </c>
-      <c r="K390" s="30" t="n"/>
+      <c r="K390" s="38" t="n"/>
       <c r="L390" s="32" t="n"/>
       <c r="M390" s="22">
         <f>IF(H390="","",IF(K390="No",0,H390*N(I390)/100*IF(L390="",100,L390)/100))</f>
@@ -31581,7 +31571,7 @@
         <f>IF(H391="","",ROUND(H391*N(I391)/100,2))</f>
         <v/>
       </c>
-      <c r="K391" s="30" t="n"/>
+      <c r="K391" s="38" t="n"/>
       <c r="L391" s="32" t="n"/>
       <c r="M391" s="22">
         <f>IF(H391="","",IF(K391="No",0,H391*N(I391)/100*IF(L391="",100,L391)/100))</f>
@@ -31613,7 +31603,7 @@
         <f>IF(H392="","",ROUND(H392*N(I392)/100,2))</f>
         <v/>
       </c>
-      <c r="K392" s="30" t="n"/>
+      <c r="K392" s="38" t="n"/>
       <c r="L392" s="32" t="n"/>
       <c r="M392" s="22">
         <f>IF(H392="","",IF(K392="No",0,H392*N(I392)/100*IF(L392="",100,L392)/100))</f>
@@ -31645,7 +31635,7 @@
         <f>IF(H393="","",ROUND(H393*N(I393)/100,2))</f>
         <v/>
       </c>
-      <c r="K393" s="30" t="n"/>
+      <c r="K393" s="38" t="n"/>
       <c r="L393" s="32" t="n"/>
       <c r="M393" s="22">
         <f>IF(H393="","",IF(K393="No",0,H393*N(I393)/100*IF(L393="",100,L393)/100))</f>
@@ -31677,7 +31667,7 @@
         <f>IF(H394="","",ROUND(H394*N(I394)/100,2))</f>
         <v/>
       </c>
-      <c r="K394" s="30" t="n"/>
+      <c r="K394" s="38" t="n"/>
       <c r="L394" s="32" t="n"/>
       <c r="M394" s="22">
         <f>IF(H394="","",IF(K394="No",0,H394*N(I394)/100*IF(L394="",100,L394)/100))</f>
@@ -31709,7 +31699,7 @@
         <f>IF(H395="","",ROUND(H395*N(I395)/100,2))</f>
         <v/>
       </c>
-      <c r="K395" s="30" t="n"/>
+      <c r="K395" s="38" t="n"/>
       <c r="L395" s="32" t="n"/>
       <c r="M395" s="22">
         <f>IF(H395="","",IF(K395="No",0,H395*N(I395)/100*IF(L395="",100,L395)/100))</f>
@@ -31741,7 +31731,7 @@
         <f>IF(H396="","",ROUND(H396*N(I396)/100,2))</f>
         <v/>
       </c>
-      <c r="K396" s="30" t="n"/>
+      <c r="K396" s="38" t="n"/>
       <c r="L396" s="32" t="n"/>
       <c r="M396" s="22">
         <f>IF(H396="","",IF(K396="No",0,H396*N(I396)/100*IF(L396="",100,L396)/100))</f>
@@ -31773,7 +31763,7 @@
         <f>IF(H397="","",ROUND(H397*N(I397)/100,2))</f>
         <v/>
       </c>
-      <c r="K397" s="30" t="n"/>
+      <c r="K397" s="38" t="n"/>
       <c r="L397" s="32" t="n"/>
       <c r="M397" s="22">
         <f>IF(H397="","",IF(K397="No",0,H397*N(I397)/100*IF(L397="",100,L397)/100))</f>
@@ -31805,7 +31795,7 @@
         <f>IF(H398="","",ROUND(H398*N(I398)/100,2))</f>
         <v/>
       </c>
-      <c r="K398" s="30" t="n"/>
+      <c r="K398" s="38" t="n"/>
       <c r="L398" s="32" t="n"/>
       <c r="M398" s="22">
         <f>IF(H398="","",IF(K398="No",0,H398*N(I398)/100*IF(L398="",100,L398)/100))</f>
@@ -31837,7 +31827,7 @@
         <f>IF(H399="","",ROUND(H399*N(I399)/100,2))</f>
         <v/>
       </c>
-      <c r="K399" s="30" t="n"/>
+      <c r="K399" s="38" t="n"/>
       <c r="L399" s="32" t="n"/>
       <c r="M399" s="22">
         <f>IF(H399="","",IF(K399="No",0,H399*N(I399)/100*IF(L399="",100,L399)/100))</f>
@@ -31869,7 +31859,7 @@
         <f>IF(H400="","",ROUND(H400*N(I400)/100,2))</f>
         <v/>
       </c>
-      <c r="K400" s="30" t="n"/>
+      <c r="K400" s="38" t="n"/>
       <c r="L400" s="32" t="n"/>
       <c r="M400" s="22">
         <f>IF(H400="","",IF(K400="No",0,H400*N(I400)/100*IF(L400="",100,L400)/100))</f>
@@ -31901,7 +31891,7 @@
         <f>IF(H401="","",ROUND(H401*N(I401)/100,2))</f>
         <v/>
       </c>
-      <c r="K401" s="30" t="n"/>
+      <c r="K401" s="38" t="n"/>
       <c r="L401" s="32" t="n"/>
       <c r="M401" s="22">
         <f>IF(H401="","",IF(K401="No",0,H401*N(I401)/100*IF(L401="",100,L401)/100))</f>
@@ -31933,7 +31923,7 @@
         <f>IF(H402="","",ROUND(H402*N(I402)/100,2))</f>
         <v/>
       </c>
-      <c r="K402" s="30" t="n"/>
+      <c r="K402" s="38" t="n"/>
       <c r="L402" s="32" t="n"/>
       <c r="M402" s="22">
         <f>IF(H402="","",IF(K402="No",0,H402*N(I402)/100*IF(L402="",100,L402)/100))</f>
@@ -31965,7 +31955,7 @@
         <f>IF(H403="","",ROUND(H403*N(I403)/100,2))</f>
         <v/>
       </c>
-      <c r="K403" s="30" t="n"/>
+      <c r="K403" s="38" t="n"/>
       <c r="L403" s="32" t="n"/>
       <c r="M403" s="22">
         <f>IF(H403="","",IF(K403="No",0,H403*N(I403)/100*IF(L403="",100,L403)/100))</f>
@@ -31997,7 +31987,7 @@
         <f>IF(H404="","",ROUND(H404*N(I404)/100,2))</f>
         <v/>
       </c>
-      <c r="K404" s="30" t="n"/>
+      <c r="K404" s="38" t="n"/>
       <c r="L404" s="32" t="n"/>
       <c r="M404" s="22">
         <f>IF(H404="","",IF(K404="No",0,H404*N(I404)/100*IF(L404="",100,L404)/100))</f>
@@ -32029,7 +32019,7 @@
         <f>IF(H405="","",ROUND(H405*N(I405)/100,2))</f>
         <v/>
       </c>
-      <c r="K405" s="30" t="n"/>
+      <c r="K405" s="38" t="n"/>
       <c r="L405" s="32" t="n"/>
       <c r="M405" s="22">
         <f>IF(H405="","",IF(K405="No",0,H405*N(I405)/100*IF(L405="",100,L405)/100))</f>
@@ -32061,7 +32051,7 @@
         <f>IF(H406="","",ROUND(H406*N(I406)/100,2))</f>
         <v/>
       </c>
-      <c r="K406" s="30" t="n"/>
+      <c r="K406" s="38" t="n"/>
       <c r="L406" s="32" t="n"/>
       <c r="M406" s="22">
         <f>IF(H406="","",IF(K406="No",0,H406*N(I406)/100*IF(L406="",100,L406)/100))</f>
@@ -32093,7 +32083,7 @@
         <f>IF(H407="","",ROUND(H407*N(I407)/100,2))</f>
         <v/>
       </c>
-      <c r="K407" s="30" t="n"/>
+      <c r="K407" s="38" t="n"/>
       <c r="L407" s="32" t="n"/>
       <c r="M407" s="22">
         <f>IF(H407="","",IF(K407="No",0,H407*N(I407)/100*IF(L407="",100,L407)/100))</f>
@@ -32683,16 +32673,16 @@
           <t>Último día (si cae en fin de semana, el lunes)</t>
         </is>
       </c>
-      <c r="D26" s="38" t="n">
+      <c r="D26" s="39" t="n">
         <v>46497</v>
       </c>
-      <c r="E26" s="38" t="n">
+      <c r="E26" s="39" t="n">
         <v>46588</v>
       </c>
-      <c r="F26" s="38" t="n">
+      <c r="F26" s="39" t="n">
         <v>46680</v>
       </c>
-      <c r="G26" s="38" t="n">
+      <c r="G26" s="39" t="n">
         <v>46783</v>
       </c>
     </row>
@@ -32992,19 +32982,19 @@
         </is>
       </c>
       <c r="D15" s="22">
-        <f>IF(REND_ANTERIOR&lt;=MIN130_H1,MIN130_E1,IF(REND_ANTERIOR&lt;=MIN130_H2,MIN130_E2,IF(REND_ANTERIOR&lt;=MIN130_H3,MIN130_E3,IF(REND_ANTERIOR&lt;=MIN130_H4,MIN130_E4,0))))*1</f>
+        <f>IF(REND_ANTERIOR&lt;=MINOR_H1,MINOR_E1,IF(REND_ANTERIOR&lt;=MINOR_H2,MINOR_E2,IF(REND_ANTERIOR&lt;=MINOR_H3,MINOR_E3,IF(REND_ANTERIOR&lt;=MINOR_H4,MINOR_E4,0))))*1</f>
         <v/>
       </c>
       <c r="E15" s="22">
-        <f>IF(REND_ANTERIOR&lt;=MIN130_H1,MIN130_E1,IF(REND_ANTERIOR&lt;=MIN130_H2,MIN130_E2,IF(REND_ANTERIOR&lt;=MIN130_H3,MIN130_E3,IF(REND_ANTERIOR&lt;=MIN130_H4,MIN130_E4,0))))*2</f>
+        <f>IF(REND_ANTERIOR&lt;=MINOR_H1,MINOR_E1,IF(REND_ANTERIOR&lt;=MINOR_H2,MINOR_E2,IF(REND_ANTERIOR&lt;=MINOR_H3,MINOR_E3,IF(REND_ANTERIOR&lt;=MINOR_H4,MINOR_E4,0))))*2</f>
         <v/>
       </c>
       <c r="F15" s="22">
-        <f>IF(REND_ANTERIOR&lt;=MIN130_H1,MIN130_E1,IF(REND_ANTERIOR&lt;=MIN130_H2,MIN130_E2,IF(REND_ANTERIOR&lt;=MIN130_H3,MIN130_E3,IF(REND_ANTERIOR&lt;=MIN130_H4,MIN130_E4,0))))*3</f>
+        <f>IF(REND_ANTERIOR&lt;=MINOR_H1,MINOR_E1,IF(REND_ANTERIOR&lt;=MINOR_H2,MINOR_E2,IF(REND_ANTERIOR&lt;=MINOR_H3,MINOR_E3,IF(REND_ANTERIOR&lt;=MINOR_H4,MINOR_E4,0))))*3</f>
         <v/>
       </c>
       <c r="G15" s="22">
-        <f>IF(REND_ANTERIOR&lt;=MIN130_H1,MIN130_E1,IF(REND_ANTERIOR&lt;=MIN130_H2,MIN130_E2,IF(REND_ANTERIOR&lt;=MIN130_H3,MIN130_E3,IF(REND_ANTERIOR&lt;=MIN130_H4,MIN130_E4,0))))*4</f>
+        <f>IF(REND_ANTERIOR&lt;=MINOR_H1,MINOR_E1,IF(REND_ANTERIOR&lt;=MINOR_H2,MINOR_E2,IF(REND_ANTERIOR&lt;=MINOR_H3,MINOR_E3,IF(REND_ANTERIOR&lt;=MINOR_H4,MINOR_E4,0))))*4</f>
         <v/>
       </c>
     </row>
@@ -33060,16 +33050,16 @@
           <t>Último día de presentación</t>
         </is>
       </c>
-      <c r="D19" s="38" t="n">
+      <c r="D19" s="39" t="n">
         <v>46497</v>
       </c>
-      <c r="E19" s="38" t="n">
+      <c r="E19" s="39" t="n">
         <v>46588</v>
       </c>
-      <c r="F19" s="38" t="n">
+      <c r="F19" s="39" t="n">
         <v>46680</v>
       </c>
-      <c r="G19" s="38" t="n">
+      <c r="G19" s="39" t="n">
         <v>46783</v>
       </c>
     </row>
@@ -33078,11 +33068,11 @@
         <f>IF(PRESENTA_130="No","Has indicado que no presentas el 130 (más del 70 % de tus ingresos de 2026 llevaron retención): los importes son solo informativos.","Un resultado negativo no se devuelve: se resta solo en los trimestres siguientes, porque el cálculo es acumulado.")</f>
         <v/>
       </c>
-      <c r="C21" s="39" t="n"/>
-      <c r="D21" s="39" t="n"/>
-      <c r="E21" s="39" t="n"/>
-      <c r="F21" s="39" t="n"/>
-      <c r="G21" s="40" t="n"/>
+      <c r="C21" s="40" t="n"/>
+      <c r="D21" s="40" t="n"/>
+      <c r="E21" s="40" t="n"/>
+      <c r="F21" s="40" t="n"/>
+      <c r="G21" s="41" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="12" t="inlineStr">
@@ -33185,15 +33175,10 @@
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="20" customHeight="1">
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Amarillo</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Escribe tú en las celdas amarillas. Las demás se calculan solas: no hace falta tocarlas.</t>
+          <t>✎  Las celdas amarillas las rellenas tú; el resto se calcula solo.</t>
         </is>
       </c>
     </row>
@@ -33243,7 +33228,7 @@
           <t>Tramo</t>
         </is>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="42">
         <f>MIN(COUNT(T_RMIN),COUNTIF(T_RMAX,"&lt;"&amp;COMPUTABLE_MES)+1)</f>
         <v/>
       </c>
@@ -33341,7 +33326,7 @@
           <t>Enero</t>
         </is>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33370,7 +33355,7 @@
           <t>Febrero</t>
         </is>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33399,7 +33384,7 @@
           <t>Marzo</t>
         </is>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33428,7 +33413,7 @@
           <t>Abril</t>
         </is>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33457,7 +33442,7 @@
           <t>Mayo</t>
         </is>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33486,7 +33471,7 @@
           <t>Junio</t>
         </is>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33515,7 +33500,7 @@
           <t>Julio</t>
         </is>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33544,7 +33529,7 @@
           <t>Agosto</t>
         </is>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33573,7 +33558,7 @@
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33602,7 +33587,7 @@
           <t>Octubre</t>
         </is>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33631,7 +33616,7 @@
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33660,7 +33645,7 @@
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="38">
         <f>TARIFA_PLANA</f>
         <v/>
       </c>
@@ -33684,7 +33669,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="42" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>Total del año</t>
         </is>
